--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128790634</v>
+        <v>128784544</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>107505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723928</v>
+        <v>723794</v>
       </c>
       <c r="R2" t="n">
-        <v>6384313</v>
+        <v>6384290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,50 +743,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128790598</v>
+        <v>128791651</v>
       </c>
       <c r="B3" t="n">
-        <v>86927</v>
+        <v>90928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723992</v>
+        <v>723674</v>
       </c>
       <c r="R3" t="n">
-        <v>6384372</v>
+        <v>6384225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,85 +840,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128791651</v>
+        <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>90927</v>
+        <v>92771</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723674</v>
+        <v>723641</v>
       </c>
       <c r="R4" t="n">
-        <v>6384225</v>
+        <v>6384196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,53 +950,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>92770</v>
+        <v>86927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R5" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,39 +1030,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128784548</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86984</v>
+        <v>86775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,30 +1081,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723687</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384221</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,9 +1138,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,57 +1165,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128784544</v>
+        <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>107500</v>
+        <v>86843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723794</v>
+        <v>723771</v>
       </c>
       <c r="R7" t="n">
-        <v>6384290</v>
+        <v>6384299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,19 +1262,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128784517</v>
+        <v>128785784</v>
       </c>
       <c r="B8" t="n">
         <v>86927</v>
@@ -1302,14 +1305,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723612</v>
+        <v>723969</v>
       </c>
       <c r="R8" t="n">
-        <v>6384274</v>
+        <v>6384430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,19 +1360,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128785784</v>
+        <v>128784517</v>
       </c>
       <c r="B9" t="n">
         <v>86927</v>
@@ -1400,14 +1403,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723969</v>
+        <v>723612</v>
       </c>
       <c r="R9" t="n">
-        <v>6384430</v>
+        <v>6384274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,44 +1458,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791638</v>
+        <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86843</v>
+        <v>86927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723771</v>
+        <v>723609</v>
       </c>
       <c r="R10" t="n">
-        <v>6384299</v>
+        <v>6384278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,36 +1538,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790574</v>
+        <v>128785783</v>
       </c>
       <c r="B11" t="n">
         <v>86927</v>
@@ -1595,14 +1609,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723609</v>
+        <v>723974</v>
       </c>
       <c r="R11" t="n">
-        <v>6384278</v>
+        <v>6384345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,19 +1646,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,44 +1664,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790645</v>
+        <v>128790554</v>
       </c>
       <c r="B12" t="n">
-        <v>86775</v>
+        <v>86729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723788</v>
+        <v>723848</v>
       </c>
       <c r="R12" t="n">
-        <v>6384286</v>
+        <v>6384240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1746,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1752,7 +1756,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,6 +1765,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,34 +1881,30 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790554</v>
+        <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>86729</v>
+        <v>86984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723848</v>
+        <v>723971</v>
       </c>
       <c r="R14" t="n">
-        <v>6384240</v>
+        <v>6384460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,85 +1945,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128785783</v>
+        <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723974</v>
+        <v>723618</v>
       </c>
       <c r="R15" t="n">
-        <v>6384345</v>
+        <v>6384286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,29 +2053,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784511</v>
+        <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>92770</v>
+        <v>88662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2093,19 +2082,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6047725</v>
+        <v>4379</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2113,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723600</v>
+        <v>723922</v>
       </c>
       <c r="R16" t="n">
-        <v>6384247</v>
+        <v>6384266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,45 +2168,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128784506</v>
+        <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>88662</v>
+        <v>86927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723922</v>
+        <v>723931</v>
       </c>
       <c r="R17" t="n">
-        <v>6384266</v>
+        <v>6384427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,63 +2236,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784509</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>86775</v>
+        <v>92771</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723618</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384286</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790595</v>
+        <v>128790583</v>
       </c>
       <c r="B19" t="n">
         <v>86927</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723931</v>
+        <v>723986</v>
       </c>
       <c r="R19" t="n">
-        <v>6384427</v>
+        <v>6384358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128790583</v>
+        <v>128784520</v>
       </c>
       <c r="B20" t="n">
         <v>86927</v>
@@ -2508,14 +2508,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723986</v>
+        <v>723922</v>
       </c>
       <c r="R20" t="n">
-        <v>6384358</v>
+        <v>6384266</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,19 +2545,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,42 +2563,46 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791663</v>
+        <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2616,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723971</v>
+        <v>723779</v>
       </c>
       <c r="R21" t="n">
-        <v>6384460</v>
+        <v>6384209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,61 +2643,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784520</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86927</v>
+        <v>86815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723922</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384266</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,7 +2762,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2769,48 +2773,52 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790626</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86984</v>
+        <v>98594</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723767</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384283</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,19 +2848,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,19 +2865,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790590</v>
+        <v>128790581</v>
       </c>
       <c r="B24" t="n">
         <v>86927</v>
@@ -2914,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723779</v>
+        <v>723930</v>
       </c>
       <c r="R24" t="n">
-        <v>6384209</v>
+        <v>6384314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,7 +2947,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2959,7 +2957,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2987,45 +2985,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128784553</v>
+        <v>128790594</v>
       </c>
       <c r="B25" t="n">
-        <v>98593</v>
+        <v>86927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723659</v>
+        <v>723948</v>
       </c>
       <c r="R25" t="n">
-        <v>6384257</v>
+        <v>6384417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,39 +3053,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128784550</v>
+        <v>128791624</v>
       </c>
       <c r="B26" t="n">
-        <v>86815</v>
+        <v>86843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,34 +3104,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723644</v>
+        <v>723724</v>
       </c>
       <c r="R26" t="n">
-        <v>6384278</v>
+        <v>6384209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,44 +3178,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790594</v>
+        <v>128791633</v>
       </c>
       <c r="B27" t="n">
-        <v>86927</v>
+        <v>86843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3216,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723948</v>
+        <v>723767</v>
       </c>
       <c r="R27" t="n">
-        <v>6384417</v>
+        <v>6384282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,72 +3258,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790581</v>
+        <v>128791629</v>
       </c>
       <c r="B28" t="n">
-        <v>86927</v>
+        <v>86843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723930</v>
+        <v>723745</v>
       </c>
       <c r="R28" t="n">
-        <v>6384314</v>
+        <v>6384273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,47 +3355,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128791633</v>
+        <v>128791642</v>
       </c>
       <c r="B29" t="n">
         <v>86843</v>
@@ -3432,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723767</v>
+        <v>723745</v>
       </c>
       <c r="R29" t="n">
-        <v>6384282</v>
+        <v>6384321</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3481,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791629</v>
+        <v>128790627</v>
       </c>
       <c r="B30" t="n">
-        <v>86843</v>
+        <v>86984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,23 +3492,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3529,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723745</v>
+        <v>723660</v>
       </c>
       <c r="R30" t="n">
-        <v>6384273</v>
+        <v>6384309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,9 +3545,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3579,57 +3572,53 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791624</v>
+        <v>128785780</v>
       </c>
       <c r="B31" t="n">
-        <v>86843</v>
+        <v>92771</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723724</v>
+        <v>723935</v>
       </c>
       <c r="R31" t="n">
-        <v>6384209</v>
+        <v>6384247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3670,18 +3659,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3785,10 +3775,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785780</v>
+        <v>128791591</v>
       </c>
       <c r="B33" t="n">
-        <v>92770</v>
+        <v>86729</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,27 +3786,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723935</v>
+        <v>723617</v>
       </c>
       <c r="R33" t="n">
         <v>6384247</v>
@@ -3860,51 +3854,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790644</v>
+        <v>128791631</v>
       </c>
       <c r="B34" t="n">
-        <v>106911</v>
+        <v>86843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>248956</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3914,10 +3907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723604</v>
+        <v>723764</v>
       </c>
       <c r="R34" t="n">
-        <v>6384282</v>
+        <v>6384279</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3947,19 +3940,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3974,19 +3957,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790627</v>
+        <v>128791566</v>
       </c>
       <c r="B35" t="n">
         <v>86984</v>
@@ -4017,10 +4000,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723660</v>
+        <v>723725</v>
       </c>
       <c r="R35" t="n">
-        <v>6384309</v>
+        <v>6384258</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,19 +4033,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4077,22 +4050,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790622</v>
+        <v>128785776</v>
       </c>
       <c r="B36" t="n">
-        <v>86984</v>
+        <v>86775</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4100,30 +4073,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723743</v>
+        <v>723727</v>
       </c>
       <c r="R36" t="n">
-        <v>6384262</v>
+        <v>6384228</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,90 +4130,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>3st, en liten i väska</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128791591</v>
+        <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723617</v>
+        <v>724024</v>
       </c>
       <c r="R37" t="n">
-        <v>6384247</v>
+        <v>6384488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4277,50 +4238,51 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128791642</v>
+        <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86843</v>
+        <v>86927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723745</v>
+        <v>723815</v>
       </c>
       <c r="R38" t="n">
-        <v>6384321</v>
+        <v>6384231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4363,36 +4325,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784530</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
         <v>86927</v>
@@ -4427,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>724024</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384488</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,45 +4463,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128784518</v>
+        <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723642</v>
+        <v>723737</v>
       </c>
       <c r="R40" t="n">
-        <v>6384222</v>
+        <v>6384262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,53 +4542,48 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785776</v>
+        <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>86775</v>
+        <v>92771</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4623,10 +4591,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723727</v>
+        <v>723675</v>
       </c>
       <c r="R41" t="n">
-        <v>6384228</v>
+        <v>6384246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,6 +4635,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4685,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128790612</v>
+        <v>128791593</v>
       </c>
       <c r="B42" t="n">
-        <v>107500</v>
+        <v>86729</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220079</v>
+        <v>3762</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4720,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723605</v>
+        <v>723736</v>
       </c>
       <c r="R42" t="n">
-        <v>6384273</v>
+        <v>6384250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4753,19 +4722,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4780,44 +4739,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790577</v>
+        <v>128791646</v>
       </c>
       <c r="B43" t="n">
-        <v>86927</v>
+        <v>86843</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723815</v>
+        <v>723732</v>
       </c>
       <c r="R43" t="n">
-        <v>6384231</v>
+        <v>6384330</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4860,72 +4819,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128791631</v>
+        <v>128790580</v>
       </c>
       <c r="B44" t="n">
-        <v>86843</v>
+        <v>86927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4935,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723764</v>
+        <v>723964</v>
       </c>
       <c r="R44" t="n">
-        <v>6384279</v>
+        <v>6384262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4968,59 +4916,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128791566</v>
+        <v>128790593</v>
       </c>
       <c r="B45" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5028,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723725</v>
+        <v>723955</v>
       </c>
       <c r="R45" t="n">
-        <v>6384258</v>
+        <v>6384354</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,61 +5024,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791595</v>
+        <v>128790578</v>
       </c>
       <c r="B46" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5125,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723737</v>
+        <v>723890</v>
       </c>
       <c r="R46" t="n">
-        <v>6384262</v>
+        <v>6384224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,39 +5132,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128790619</v>
+        <v>128791576</v>
       </c>
       <c r="B47" t="n">
-        <v>86984</v>
+        <v>86775</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,19 +5183,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5218,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723956</v>
+        <v>723743</v>
       </c>
       <c r="R47" t="n">
-        <v>6384354</v>
+        <v>6384328</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5251,86 +5240,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I påse, en fruktkropp halvätna skivor</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128785770</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>92770</v>
+        <v>86775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723675</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384246</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,64 +5348,63 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128791576</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86775</v>
+        <v>106916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723743</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384328</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,57 +5451,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128791593</v>
+        <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86729</v>
+        <v>86927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723736</v>
+        <v>723955</v>
       </c>
       <c r="R50" t="n">
-        <v>6384250</v>
+        <v>6384252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5566,63 +5542,64 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128791646</v>
+        <v>128784549</v>
       </c>
       <c r="B51" t="n">
-        <v>86843</v>
+        <v>92757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>248956</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723732</v>
+        <v>723958</v>
       </c>
       <c r="R51" t="n">
-        <v>6384330</v>
+        <v>6384364</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5669,53 +5646,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128790630</v>
+        <v>128784554</v>
       </c>
       <c r="B52" t="n">
-        <v>86984</v>
+        <v>98594</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723733</v>
+        <v>723982</v>
       </c>
       <c r="R52" t="n">
-        <v>6384264</v>
+        <v>6384442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5745,19 +5726,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5772,19 +5743,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128790578</v>
+        <v>128790589</v>
       </c>
       <c r="B53" t="n">
         <v>86927</v>
@@ -5819,10 +5790,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723890</v>
+        <v>723770</v>
       </c>
       <c r="R53" t="n">
-        <v>6384224</v>
+        <v>6384248</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5854,7 +5825,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5864,7 +5835,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5892,34 +5863,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128790593</v>
+        <v>128790629</v>
       </c>
       <c r="B54" t="n">
-        <v>86927</v>
+        <v>86984</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5927,10 +5894,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723955</v>
+        <v>723637</v>
       </c>
       <c r="R54" t="n">
-        <v>6384354</v>
+        <v>6384245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5962,7 +5929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -5972,7 +5939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,7 +5948,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6000,45 +5966,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128790580</v>
+        <v>128784539</v>
       </c>
       <c r="B55" t="n">
-        <v>86927</v>
+        <v>91002</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723964</v>
+        <v>723615</v>
       </c>
       <c r="R55" t="n">
-        <v>6384262</v>
+        <v>6384240</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6068,50 +6034,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784562</v>
+        <v>128791648</v>
       </c>
       <c r="B56" t="n">
-        <v>106911</v>
+        <v>90928</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,34 +6074,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723639</v>
+        <v>723664</v>
       </c>
       <c r="R56" t="n">
-        <v>6384269</v>
+        <v>6384233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6193,57 +6148,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128784521</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723955</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384252</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6284,51 +6239,50 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128791574</v>
+        <v>128790565</v>
       </c>
       <c r="B58" t="n">
-        <v>86775</v>
+        <v>86753</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6338,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723611</v>
+        <v>723921</v>
       </c>
       <c r="R58" t="n">
-        <v>6384260</v>
+        <v>6384444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,9 +6325,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6388,53 +6352,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128790631</v>
+        <v>128784551</v>
       </c>
       <c r="B59" t="n">
-        <v>86984</v>
+        <v>98594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723881</v>
+        <v>723631</v>
       </c>
       <c r="R59" t="n">
-        <v>6384222</v>
+        <v>6384236</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6464,77 +6432,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I väska, 1 fk, hål i ena foten</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784561</v>
+        <v>128784545</v>
       </c>
       <c r="B60" t="n">
-        <v>86961</v>
+        <v>107505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248939</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6544,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723677</v>
+        <v>723768</v>
       </c>
       <c r="R60" t="n">
-        <v>6384262</v>
+        <v>6384301</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6588,7 +6540,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6607,32 +6558,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784554</v>
+        <v>128784526</v>
       </c>
       <c r="B61" t="n">
-        <v>98593</v>
+        <v>86927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6642,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723982</v>
+        <v>723962</v>
       </c>
       <c r="R61" t="n">
-        <v>6384442</v>
+        <v>6384357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6686,6 +6637,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6704,32 +6656,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784539</v>
+        <v>128784523</v>
       </c>
       <c r="B62" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6739,10 +6691,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723615</v>
+        <v>723878</v>
       </c>
       <c r="R62" t="n">
-        <v>6384240</v>
+        <v>6384241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,6 +6735,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6794,17 +6747,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128784549</v>
+        <v>128790556</v>
       </c>
       <c r="B63" t="n">
-        <v>92756</v>
+        <v>86729</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,34 +6765,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723958</v>
+        <v>723703</v>
       </c>
       <c r="R63" t="n">
-        <v>6384364</v>
+        <v>6384275</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,9 +6822,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6886,44 +6849,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791648</v>
+        <v>128791601</v>
       </c>
       <c r="B64" t="n">
-        <v>90927</v>
+        <v>86729</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6933,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723664</v>
+        <v>723723</v>
       </c>
       <c r="R64" t="n">
-        <v>6384233</v>
+        <v>6384387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6995,45 +6958,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128790589</v>
+        <v>128785779</v>
       </c>
       <c r="B65" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723770</v>
+        <v>723790</v>
       </c>
       <c r="R65" t="n">
-        <v>6384248</v>
+        <v>6384287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,81 +7026,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128790629</v>
+        <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723637</v>
+        <v>723945</v>
       </c>
       <c r="R66" t="n">
-        <v>6384245</v>
+        <v>6384300</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7167,84 +7123,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128790570</v>
+        <v>128784516</v>
       </c>
       <c r="B67" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723614</v>
+        <v>723922</v>
       </c>
       <c r="R67" t="n">
-        <v>6384244</v>
+        <v>6384267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7274,49 +7221,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128784545</v>
+        <v>128784527</v>
       </c>
       <c r="B68" t="n">
-        <v>107500</v>
+        <v>86927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7324,21 +7262,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7348,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723768</v>
+        <v>723949</v>
       </c>
       <c r="R68" t="n">
-        <v>6384301</v>
+        <v>6384442</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,6 +7330,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7410,7 +7349,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128784526</v>
+        <v>128785782</v>
       </c>
       <c r="B69" t="n">
         <v>86927</v>
@@ -7441,14 +7380,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723962</v>
+        <v>723777</v>
       </c>
       <c r="R69" t="n">
-        <v>6384357</v>
+        <v>6384287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,44 +7435,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128784551</v>
+        <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>98593</v>
+        <v>86775</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7543,10 +7482,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723631</v>
+        <v>723610</v>
       </c>
       <c r="R70" t="n">
-        <v>6384236</v>
+        <v>6384274</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7605,45 +7544,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784523</v>
+        <v>128791626</v>
       </c>
       <c r="B71" t="n">
-        <v>86927</v>
+        <v>86843</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723878</v>
+        <v>723741</v>
       </c>
       <c r="R71" t="n">
-        <v>6384241</v>
+        <v>6384216</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7684,64 +7623,63 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785778</v>
+        <v>128790555</v>
       </c>
       <c r="B72" t="n">
-        <v>86775</v>
+        <v>86729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723760</v>
+        <v>723944</v>
       </c>
       <c r="R72" t="n">
-        <v>6384211</v>
+        <v>6384278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,74 +7709,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790565</v>
+        <v>128785795</v>
       </c>
       <c r="B73" t="n">
-        <v>86753</v>
+        <v>90928</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723921</v>
+        <v>723789</v>
       </c>
       <c r="R73" t="n">
-        <v>6384444</v>
+        <v>6384213</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,19 +7817,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7895,22 +7834,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791601</v>
+        <v>128790611</v>
       </c>
       <c r="B74" t="n">
-        <v>86729</v>
+        <v>105641</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7918,21 +7857,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>224098</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7942,10 +7881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723723</v>
+        <v>723942</v>
       </c>
       <c r="R74" t="n">
-        <v>6384387</v>
+        <v>6384482</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7975,9 +7914,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7992,57 +7941,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128785779</v>
+        <v>128784542</v>
       </c>
       <c r="B75" t="n">
-        <v>86775</v>
+        <v>105641</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>224098</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723790</v>
+        <v>723833</v>
       </c>
       <c r="R75" t="n">
-        <v>6384287</v>
+        <v>6384211</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8089,19 +8038,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128785782</v>
+        <v>128784529</v>
       </c>
       <c r="B76" t="n">
         <v>86927</v>
@@ -8132,14 +8081,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723777</v>
+        <v>723953</v>
       </c>
       <c r="R76" t="n">
-        <v>6384287</v>
+        <v>6384442</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8187,19 +8136,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128784527</v>
+        <v>128790592</v>
       </c>
       <c r="B77" t="n">
         <v>86927</v>
@@ -8230,14 +8179,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723949</v>
+        <v>723955</v>
       </c>
       <c r="R77" t="n">
-        <v>6384442</v>
+        <v>6384283</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8267,9 +8216,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8285,19 +8244,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128784525</v>
+        <v>128790597</v>
       </c>
       <c r="B78" t="n">
         <v>86927</v>
@@ -8328,14 +8287,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723945</v>
+        <v>723990</v>
       </c>
       <c r="R78" t="n">
-        <v>6384300</v>
+        <v>6384408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8365,9 +8324,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,19 +8352,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128784516</v>
+        <v>128790588</v>
       </c>
       <c r="B79" t="n">
         <v>86927</v>
@@ -8426,14 +8395,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723922</v>
+        <v>723605</v>
       </c>
       <c r="R79" t="n">
-        <v>6384267</v>
+        <v>6384276</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8463,9 +8432,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8481,44 +8460,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128790556</v>
+        <v>128791643</v>
       </c>
       <c r="B80" t="n">
-        <v>86729</v>
+        <v>86843</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8528,10 +8507,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723703</v>
+        <v>723739</v>
       </c>
       <c r="R80" t="n">
-        <v>6384275</v>
+        <v>6384326</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8561,19 +8540,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8588,57 +8557,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128784529</v>
+        <v>128785788</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723953</v>
+        <v>723850</v>
       </c>
       <c r="R81" t="n">
-        <v>6384442</v>
+        <v>6384251</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8679,51 +8648,50 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128784510</v>
+        <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86775</v>
+        <v>86927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8733,10 +8701,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723610</v>
+        <v>723763</v>
       </c>
       <c r="R82" t="n">
-        <v>6384274</v>
+        <v>6384295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8777,6 +8745,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8788,52 +8757,52 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård, Anna Helmersson, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128784542</v>
+        <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>105638</v>
+        <v>86927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723833</v>
+        <v>723628</v>
       </c>
       <c r="R83" t="n">
-        <v>6384211</v>
+        <v>6384239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8863,39 +8832,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128785795</v>
+        <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>90927</v>
+        <v>99345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8903,34 +8883,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3286</v>
+        <v>222361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723789</v>
+        <v>723956</v>
       </c>
       <c r="R84" t="n">
-        <v>6384213</v>
+        <v>6384330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8977,22 +8957,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128790638</v>
+        <v>128791635</v>
       </c>
       <c r="B85" t="n">
-        <v>87054</v>
+        <v>86843</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9000,21 +8980,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3563</v>
+        <v>248956</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9024,10 +9004,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723726</v>
+        <v>723782</v>
       </c>
       <c r="R85" t="n">
-        <v>6384251</v>
+        <v>6384293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9057,47 +9037,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128790597</v>
+        <v>128784524</v>
       </c>
       <c r="B86" t="n">
         <v>86927</v>
@@ -9128,14 +9097,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723990</v>
+        <v>723940</v>
       </c>
       <c r="R86" t="n">
-        <v>6384408</v>
+        <v>6384281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9165,19 +9134,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9193,57 +9152,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128790611</v>
+        <v>128784522</v>
       </c>
       <c r="B87" t="n">
-        <v>105638</v>
+        <v>86927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723942</v>
+        <v>723865</v>
       </c>
       <c r="R87" t="n">
-        <v>6384482</v>
+        <v>6384223</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9273,84 +9232,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128790555</v>
+        <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86729</v>
+        <v>86775</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723944</v>
+        <v>723658</v>
       </c>
       <c r="R88" t="n">
-        <v>6384278</v>
+        <v>6384251</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9380,72 +9330,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128790592</v>
+        <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9455,10 +9394,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723955</v>
+        <v>723767</v>
       </c>
       <c r="R89" t="n">
-        <v>6384283</v>
+        <v>6384288</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9488,72 +9427,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791626</v>
+        <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>86843</v>
+        <v>90928</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723741</v>
+        <v>723728</v>
       </c>
       <c r="R90" t="n">
-        <v>6384216</v>
+        <v>6384262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9553,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128790568</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>91001</v>
+        <v>86775</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,34 +9564,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5747</v>
+        <v>424</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723615</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384242</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9693,19 +9621,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9720,44 +9638,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128790588</v>
+        <v>128791578</v>
       </c>
       <c r="B92" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9767,10 +9685,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723605</v>
+        <v>723775</v>
       </c>
       <c r="R92" t="n">
-        <v>6384276</v>
+        <v>6384432</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9800,19 +9718,14 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:08</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9821,53 +9734,48 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784519</v>
+        <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>86927</v>
+        <v>86984</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -9875,10 +9783,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723763</v>
+        <v>723687</v>
       </c>
       <c r="R93" t="n">
-        <v>6384295</v>
+        <v>6384221</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9919,7 +9827,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9938,10 +9845,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128785788</v>
+        <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>98594</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9949,34 +9856,38 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723850</v>
+        <v>723928</v>
       </c>
       <c r="R94" t="n">
-        <v>6384251</v>
+        <v>6384313</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10006,63 +9917,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128790576</v>
+        <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>86927</v>
+        <v>86984</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10070,10 +9988,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723628</v>
+        <v>723701</v>
       </c>
       <c r="R95" t="n">
-        <v>6384239</v>
+        <v>6384244</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10105,7 +10023,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10115,7 +10033,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10124,7 +10042,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10143,10 +10060,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791643</v>
+        <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>86843</v>
+        <v>86984</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10154,23 +10071,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10178,10 +10091,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723739</v>
+        <v>723767</v>
       </c>
       <c r="R96" t="n">
-        <v>6384326</v>
+        <v>6384283</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10211,9 +10124,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10228,57 +10151,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128784524</v>
+        <v>128814781</v>
       </c>
       <c r="B97" t="n">
-        <v>86927</v>
+        <v>86961</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
+        <v>248939</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723940</v>
+        <v>723628</v>
       </c>
       <c r="R97" t="n">
-        <v>6384281</v>
+        <v>6384239</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10308,75 +10231,80 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128784540</v>
+        <v>128790622</v>
       </c>
       <c r="B98" t="n">
-        <v>99344</v>
+        <v>86984</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222361</v>
+        <v>433</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723956</v>
+        <v>723743</v>
       </c>
       <c r="R98" t="n">
-        <v>6384330</v>
+        <v>6384262</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10406,39 +10334,55 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>3st, en liten i väska</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128784522</v>
+        <v>128790644</v>
       </c>
       <c r="B99" t="n">
-        <v>86927</v>
+        <v>106916</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10446,34 +10390,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723865</v>
+        <v>723604</v>
       </c>
       <c r="R99" t="n">
-        <v>6384223</v>
+        <v>6384282</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10503,60 +10447,73 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128790569</v>
+        <v>128790612</v>
       </c>
       <c r="B100" t="n">
-        <v>92770</v>
+        <v>107505</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6047725</v>
+        <v>220079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10564,10 +10521,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723948</v>
+        <v>723605</v>
       </c>
       <c r="R100" t="n">
-        <v>6384259</v>
+        <v>6384273</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10599,7 +10556,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10609,7 +10566,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10636,10 +10593,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128791635</v>
+        <v>128790619</v>
       </c>
       <c r="B101" t="n">
-        <v>86843</v>
+        <v>86984</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,23 +10604,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10671,10 +10624,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723782</v>
+        <v>723956</v>
       </c>
       <c r="R101" t="n">
-        <v>6384293</v>
+        <v>6384354</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10704,39 +10657,55 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I påse, en fruktkropp halvätna skivor</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128785775</v>
+        <v>128790630</v>
       </c>
       <c r="B102" t="n">
-        <v>86775</v>
+        <v>86984</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10744,34 +10713,30 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723658</v>
+        <v>723733</v>
       </c>
       <c r="R102" t="n">
-        <v>6384251</v>
+        <v>6384264</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10801,9 +10766,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10818,46 +10793,42 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128791597</v>
+        <v>128790631</v>
       </c>
       <c r="B103" t="n">
-        <v>86729</v>
+        <v>86984</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -10865,10 +10836,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723767</v>
+        <v>723881</v>
       </c>
       <c r="R103" t="n">
-        <v>6384288</v>
+        <v>6384222</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10898,39 +10869,55 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I väska, 1 fk, hål i ena foten</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128784508</v>
+        <v>128784561</v>
       </c>
       <c r="B104" t="n">
-        <v>86775</v>
+        <v>86961</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10938,21 +10925,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>248939</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10962,10 +10949,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723789</v>
+        <v>723677</v>
       </c>
       <c r="R104" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11006,6 +10993,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11024,45 +11012,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128791655</v>
+        <v>128790570</v>
       </c>
       <c r="B105" t="n">
-        <v>90927</v>
+        <v>91002</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723728</v>
+        <v>723614</v>
       </c>
       <c r="R105" t="n">
-        <v>6384262</v>
+        <v>6384244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11092,39 +11083,55 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Via Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128791578</v>
+        <v>128814749</v>
       </c>
       <c r="B106" t="n">
-        <v>86775</v>
+        <v>86815</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11132,21 +11139,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11156,10 +11163,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723775</v>
+        <v>723637</v>
       </c>
       <c r="R106" t="n">
-        <v>6384432</v>
+        <v>6384245</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11189,14 +11196,24 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>Dubbelrapport. Bilddokumentation av Liams fynd några meter bort.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11211,44 +11228,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128790561</v>
+        <v>128814809</v>
       </c>
       <c r="B107" t="n">
-        <v>90234</v>
+        <v>86775</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>245042</v>
+        <v>424</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11258,10 +11275,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723960</v>
+        <v>723615</v>
       </c>
       <c r="R107" t="n">
-        <v>6384272</v>
+        <v>6384242</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11293,7 +11310,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11303,7 +11320,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11312,7 +11329,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11331,10 +11347,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128790618</v>
+        <v>128790638</v>
       </c>
       <c r="B108" t="n">
-        <v>86843</v>
+        <v>87121</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11342,34 +11358,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>248956</v>
+        <v>451</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723602</v>
+        <v>723726</v>
       </c>
       <c r="R108" t="n">
-        <v>6384277</v>
+        <v>6384251</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11401,7 +11420,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11411,7 +11430,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11420,6 +11439,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11435,6 +11455,444 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128790568</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91002</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Gothem Vaters, Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>723615</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6384242</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128790569</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92771</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Gothem Vaters, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>723948</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6384259</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128790561</v>
+      </c>
+      <c r="B111" t="n">
+        <v>90234</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Gothem Vaters, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>723960</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6384272</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128790618</v>
+      </c>
+      <c r="B112" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Gothem Vaters, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>723602</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6384277</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>107505</v>
+        <v>90955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B3" t="n">
-        <v>90928</v>
+        <v>107533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R3" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>128785784</v>
       </c>
       <c r="B8" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128784517</v>
       </c>
       <c r="B9" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,45 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128785783</v>
+        <v>128790554</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>86756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723974</v>
+        <v>723848</v>
       </c>
       <c r="R11" t="n">
-        <v>6384345</v>
+        <v>6384240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,22 +1674,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790554</v>
+        <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723848</v>
+        <v>723734</v>
       </c>
       <c r="R12" t="n">
-        <v>6384240</v>
+        <v>6384367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,85 +1754,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791599</v>
+        <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86729</v>
+        <v>86954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723734</v>
+        <v>723974</v>
       </c>
       <c r="R13" t="n">
-        <v>6384367</v>
+        <v>6384345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,18 +1862,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>88662</v>
+        <v>88689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128791624</v>
       </c>
       <c r="B22" t="n">
-        <v>86815</v>
+        <v>86870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723724</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,57 +2768,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128791633</v>
       </c>
       <c r="B23" t="n">
-        <v>98594</v>
+        <v>86870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723767</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,44 +2865,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790581</v>
+        <v>128791629</v>
       </c>
       <c r="B24" t="n">
-        <v>86927</v>
+        <v>86870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723930</v>
+        <v>723745</v>
       </c>
       <c r="R24" t="n">
-        <v>6384314</v>
+        <v>6384273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,50 +2945,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790594</v>
+        <v>128790581</v>
       </c>
       <c r="B25" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723948</v>
+        <v>723930</v>
       </c>
       <c r="R25" t="n">
-        <v>6384417</v>
+        <v>6384314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,7 +3044,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3065,7 +3054,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,32 +3082,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128790594</v>
       </c>
       <c r="B26" t="n">
-        <v>86843</v>
+        <v>86954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723948</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384417</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,39 +3150,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791633</v>
+        <v>128784550</v>
       </c>
       <c r="B27" t="n">
-        <v>86843</v>
+        <v>86842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723767</v>
+        <v>723644</v>
       </c>
       <c r="R27" t="n">
-        <v>6384282</v>
+        <v>6384278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,57 +3275,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791629</v>
+        <v>128784553</v>
       </c>
       <c r="B28" t="n">
-        <v>86843</v>
+        <v>98621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723745</v>
+        <v>723659</v>
       </c>
       <c r="R28" t="n">
-        <v>6384273</v>
+        <v>6384257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,22 +3372,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128791642</v>
+        <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>86843</v>
+        <v>87011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,23 +3395,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3419,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723745</v>
+        <v>723660</v>
       </c>
       <c r="R29" t="n">
-        <v>6384321</v>
+        <v>6384309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3448,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,53 +3475,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
-        <v>86984</v>
+        <v>86756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3545,19 +3555,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3572,22 +3572,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128785780</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>92771</v>
+        <v>86756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,27 +3595,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723935</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
         <v>6384247</v>
@@ -3659,64 +3663,63 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785781</v>
+        <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>86729</v>
+        <v>86870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723744</v>
+        <v>723745</v>
       </c>
       <c r="R32" t="n">
-        <v>6384205</v>
+        <v>6384321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,22 +3766,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791591</v>
+        <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>86729</v>
+        <v>92798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3786,31 +3789,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723617</v>
+        <v>723935</v>
       </c>
       <c r="R33" t="n">
         <v>6384247</v>
@@ -3854,28 +3853,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128791631</v>
+        <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>86843</v>
+        <v>87011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3883,23 +3883,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3907,10 +3903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723764</v>
+        <v>723725</v>
       </c>
       <c r="R34" t="n">
-        <v>6384279</v>
+        <v>6384258</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,10 +3965,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128791566</v>
+        <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86984</v>
+        <v>86802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3980,30 +3976,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723725</v>
+        <v>723727</v>
       </c>
       <c r="R35" t="n">
-        <v>6384258</v>
+        <v>6384228</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,22 +4050,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128785776</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86775</v>
+        <v>86870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,34 +4073,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723727</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384228</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4147,12 +4147,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86729</v>
+        <v>86802</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791646</v>
+        <v>128790580</v>
       </c>
       <c r="B43" t="n">
-        <v>86843</v>
+        <v>86954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723732</v>
+        <v>723964</v>
       </c>
       <c r="R43" t="n">
-        <v>6384330</v>
+        <v>6384262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,39 +4819,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B44" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4918,7 +4929,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4928,7 +4939,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,10 +4967,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790593</v>
+        <v>128790578</v>
       </c>
       <c r="B45" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,10 +5002,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723955</v>
+        <v>723890</v>
       </c>
       <c r="R45" t="n">
-        <v>6384354</v>
+        <v>6384224</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,7 +5037,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5036,7 +5047,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790578</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86927</v>
+        <v>86756</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5099,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723890</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384224</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5132,50 +5143,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791576</v>
+        <v>128791646</v>
       </c>
       <c r="B47" t="n">
-        <v>86775</v>
+        <v>86870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723743</v>
+        <v>723732</v>
       </c>
       <c r="R47" t="n">
-        <v>6384328</v>
+        <v>6384330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5272,7 +5272,7 @@
         <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784562</v>
+        <v>128784521</v>
       </c>
       <c r="B49" t="n">
-        <v>106916</v>
+        <v>86954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5377,21 +5377,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723639</v>
+        <v>723955</v>
       </c>
       <c r="R49" t="n">
-        <v>6384269</v>
+        <v>6384252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5445,6 +5445,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5463,10 +5464,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128784521</v>
+        <v>128784562</v>
       </c>
       <c r="B50" t="n">
-        <v>86927</v>
+        <v>106944</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5474,21 +5475,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5498,10 +5499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723955</v>
+        <v>723639</v>
       </c>
       <c r="R50" t="n">
-        <v>6384252</v>
+        <v>6384269</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5542,7 +5543,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5554,52 +5554,48 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784549</v>
+        <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>92757</v>
+        <v>87011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723958</v>
+        <v>723637</v>
       </c>
       <c r="R51" t="n">
-        <v>6384364</v>
+        <v>6384245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,9 +5625,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5646,44 +5652,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784554</v>
+        <v>128784539</v>
       </c>
       <c r="B52" t="n">
-        <v>98594</v>
+        <v>91029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219811</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5699,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723982</v>
+        <v>723615</v>
       </c>
       <c r="R52" t="n">
-        <v>6384442</v>
+        <v>6384240</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5761,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128790589</v>
+        <v>128784549</v>
       </c>
       <c r="B53" t="n">
-        <v>86927</v>
+        <v>92784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723770</v>
+        <v>723958</v>
       </c>
       <c r="R53" t="n">
-        <v>6384248</v>
+        <v>6384364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5823,70 +5829,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128790629</v>
+        <v>128791648</v>
       </c>
       <c r="B54" t="n">
-        <v>86984</v>
+        <v>90955</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>433</v>
+        <v>3286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5894,10 +5893,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723637</v>
+        <v>723664</v>
       </c>
       <c r="R54" t="n">
-        <v>6384245</v>
+        <v>6384233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5927,19 +5926,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5954,57 +5943,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128784539</v>
+        <v>128790589</v>
       </c>
       <c r="B55" t="n">
-        <v>91002</v>
+        <v>86954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723615</v>
+        <v>723770</v>
       </c>
       <c r="R55" t="n">
-        <v>6384240</v>
+        <v>6384248</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6034,74 +6023,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128791648</v>
+        <v>128784554</v>
       </c>
       <c r="B56" t="n">
-        <v>90928</v>
+        <v>98621</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>219811</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723664</v>
+        <v>723982</v>
       </c>
       <c r="R56" t="n">
-        <v>6384233</v>
+        <v>6384442</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6148,12 +6148,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6163,7 +6163,7 @@
         <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>128790565</v>
       </c>
       <c r="B58" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,32 +6364,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784551</v>
+        <v>128784545</v>
       </c>
       <c r="B59" t="n">
-        <v>98594</v>
+        <v>107533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723631</v>
+        <v>723768</v>
       </c>
       <c r="R59" t="n">
-        <v>6384236</v>
+        <v>6384301</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784545</v>
+        <v>128784551</v>
       </c>
       <c r="B60" t="n">
-        <v>107505</v>
+        <v>98621</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>219811</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723768</v>
+        <v>723631</v>
       </c>
       <c r="R60" t="n">
-        <v>6384301</v>
+        <v>6384236</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6561,7 +6561,7 @@
         <v>128784526</v>
       </c>
       <c r="B61" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>128784523</v>
       </c>
       <c r="B62" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6747,52 +6747,52 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén, Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128790556</v>
+        <v>128785779</v>
       </c>
       <c r="B63" t="n">
-        <v>86729</v>
+        <v>86802</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723703</v>
+        <v>723790</v>
       </c>
       <c r="R63" t="n">
-        <v>6384275</v>
+        <v>6384287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,19 +6822,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6849,22 +6839,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791601</v>
+        <v>128790556</v>
       </c>
       <c r="B64" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723723</v>
+        <v>723703</v>
       </c>
       <c r="R64" t="n">
-        <v>6384387</v>
+        <v>6384275</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6929,9 +6919,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6946,57 +6946,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128785779</v>
+        <v>128791601</v>
       </c>
       <c r="B65" t="n">
-        <v>86775</v>
+        <v>86756</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723790</v>
+        <v>723723</v>
       </c>
       <c r="R65" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,12 +7043,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
         <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>128784516</v>
       </c>
       <c r="B67" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>128784527</v>
       </c>
       <c r="B68" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128785782</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7544,32 +7544,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128791626</v>
+        <v>128790555</v>
       </c>
       <c r="B71" t="n">
-        <v>86843</v>
+        <v>86756</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723741</v>
+        <v>723944</v>
       </c>
       <c r="R71" t="n">
-        <v>6384216</v>
+        <v>6384278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,74 +7612,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B72" t="n">
-        <v>86729</v>
+        <v>90955</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R72" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,85 +7720,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128785795</v>
+        <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>90928</v>
+        <v>105669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3286</v>
+        <v>224098</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723789</v>
+        <v>723942</v>
       </c>
       <c r="R73" t="n">
-        <v>6384213</v>
+        <v>6384482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,9 +7817,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7834,22 +7844,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128790611</v>
+        <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>105641</v>
+        <v>105669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7877,14 +7887,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723942</v>
+        <v>723833</v>
       </c>
       <c r="R74" t="n">
-        <v>6384482</v>
+        <v>6384211</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7914,19 +7924,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7941,44 +7941,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128784542</v>
+        <v>128784529</v>
       </c>
       <c r="B75" t="n">
-        <v>105641</v>
+        <v>86954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723833</v>
+        <v>723953</v>
       </c>
       <c r="R75" t="n">
-        <v>6384211</v>
+        <v>6384442</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8032,6 +8032,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8050,10 +8051,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128784529</v>
+        <v>128790592</v>
       </c>
       <c r="B76" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8081,14 +8082,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723953</v>
+        <v>723955</v>
       </c>
       <c r="R76" t="n">
-        <v>6384442</v>
+        <v>6384283</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8118,9 +8119,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8136,22 +8147,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790592</v>
+        <v>128790597</v>
       </c>
       <c r="B77" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8183,10 +8194,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723955</v>
+        <v>723990</v>
       </c>
       <c r="R77" t="n">
-        <v>6384283</v>
+        <v>6384408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8218,7 +8229,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8228,7 +8239,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8256,32 +8267,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B78" t="n">
-        <v>86927</v>
+        <v>86870</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8291,10 +8302,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R78" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8324,40 +8335,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>128791643</v>
       </c>
       <c r="B80" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård, Anna Helmersson, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
         <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>128791635</v>
       </c>
       <c r="B85" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>128784524</v>
       </c>
       <c r="B86" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>128784522</v>
       </c>
       <c r="B87" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9265,7 +9265,7 @@
         <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9553,10 +9553,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9638,22 +9643,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B92" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9681,14 +9686,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R92" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,11 +9728,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
         <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128790626</v>
+        <v>128814781</v>
       </c>
       <c r="B96" t="n">
-        <v>86984</v>
+        <v>86988</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10071,19 +10071,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>433</v>
+        <v>248939</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Cortinarius terpsichores</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Melot</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10091,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723767</v>
+        <v>723628</v>
       </c>
       <c r="R96" t="n">
-        <v>6384283</v>
+        <v>6384239</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10126,7 +10130,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10136,7 +10140,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10163,10 +10167,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814781</v>
+        <v>128790626</v>
       </c>
       <c r="B97" t="n">
-        <v>86961</v>
+        <v>87011</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10174,23 +10178,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>248939</v>
+        <v>433</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Melot</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723628</v>
+        <v>723767</v>
       </c>
       <c r="R97" t="n">
-        <v>6384239</v>
+        <v>6384283</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10273,7 +10273,7 @@
         <v>128790622</v>
       </c>
       <c r="B98" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>128790644</v>
       </c>
       <c r="B99" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>128790612</v>
       </c>
       <c r="B100" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>128790619</v>
       </c>
       <c r="B101" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>128790630</v>
       </c>
       <c r="B102" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>128790631</v>
       </c>
       <c r="B103" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10914,10 +10914,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128784561</v>
+        <v>128790570</v>
       </c>
       <c r="B104" t="n">
-        <v>86961</v>
+        <v>91029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10925,34 +10925,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>248939</v>
+        <v>5747</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723677</v>
+        <v>723614</v>
       </c>
       <c r="R104" t="n">
-        <v>6384262</v>
+        <v>6384244</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10982,9 +10985,24 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11000,22 +11018,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Via Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128790570</v>
+        <v>128784561</v>
       </c>
       <c r="B105" t="n">
-        <v>91002</v>
+        <v>86988</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11023,37 +11041,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5747</v>
+        <v>248939</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723614</v>
+        <v>723677</v>
       </c>
       <c r="R105" t="n">
-        <v>6384244</v>
+        <v>6384262</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11083,24 +11098,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11116,12 +11116,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Via Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11131,7 +11131,7 @@
         <v>128814749</v>
       </c>
       <c r="B106" t="n">
-        <v>86815</v>
+        <v>86842</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>128814809</v>
       </c>
       <c r="B107" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128790638</v>
       </c>
       <c r="B108" t="n">
-        <v>87121</v>
+        <v>87148</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>128790568</v>
       </c>
       <c r="B109" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>128790569</v>
       </c>
       <c r="B110" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>128790561</v>
       </c>
       <c r="B111" t="n">
-        <v>90234</v>
+        <v>90261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>128790618</v>
       </c>
       <c r="B112" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -1177,45 +1177,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128791638</v>
+        <v>128785784</v>
       </c>
       <c r="B7" t="n">
-        <v>86870</v>
+        <v>86954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723771</v>
+        <v>723969</v>
       </c>
       <c r="R7" t="n">
-        <v>6384299</v>
+        <v>6384430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,25 +1256,26 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128785784</v>
+        <v>128784517</v>
       </c>
       <c r="B8" t="n">
         <v>86954</v>
@@ -1305,14 +1306,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723969</v>
+        <v>723612</v>
       </c>
       <c r="R8" t="n">
-        <v>6384430</v>
+        <v>6384274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,19 +1361,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128784517</v>
+        <v>128790574</v>
       </c>
       <c r="B9" t="n">
         <v>86954</v>
@@ -1403,14 +1404,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723612</v>
+        <v>723609</v>
       </c>
       <c r="R9" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,9 +1441,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1458,44 +1469,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790574</v>
+        <v>128791638</v>
       </c>
       <c r="B10" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723609</v>
+        <v>723771</v>
       </c>
       <c r="R10" t="n">
-        <v>6384278</v>
+        <v>6384299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,85 +1549,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B11" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R11" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,19 +1664,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B12" t="n">
         <v>86756</v>
@@ -1721,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R12" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,74 +1744,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86954</v>
+        <v>86756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R13" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,19 +1863,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128791624</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86870</v>
+        <v>86842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248956</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723724</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384209</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,57 +2768,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791633</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86870</v>
+        <v>98621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723767</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384282</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,44 +2865,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B24" t="n">
-        <v>86870</v>
+        <v>86954</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R24" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,36 +2945,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790581</v>
+        <v>128790594</v>
       </c>
       <c r="B25" t="n">
         <v>86954</v>
@@ -3009,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723930</v>
+        <v>723948</v>
       </c>
       <c r="R25" t="n">
-        <v>6384314</v>
+        <v>6384417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3044,7 +3055,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3054,7 +3065,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3082,32 +3093,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790594</v>
+        <v>128791624</v>
       </c>
       <c r="B26" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3117,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723948</v>
+        <v>723724</v>
       </c>
       <c r="R26" t="n">
-        <v>6384417</v>
+        <v>6384209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,50 +3161,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128784550</v>
+        <v>128791633</v>
       </c>
       <c r="B27" t="n">
-        <v>86842</v>
+        <v>86870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723644</v>
+        <v>723767</v>
       </c>
       <c r="R27" t="n">
-        <v>6384278</v>
+        <v>6384282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,57 +3275,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128784553</v>
+        <v>128791629</v>
       </c>
       <c r="B28" t="n">
-        <v>98621</v>
+        <v>86870</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723659</v>
+        <v>723745</v>
       </c>
       <c r="R28" t="n">
-        <v>6384257</v>
+        <v>6384273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,53 +3372,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>87011</v>
+        <v>86756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R29" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,19 +3452,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,19 +3469,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128791591</v>
       </c>
       <c r="B30" t="n">
         <v>86756</v>
@@ -3518,14 +3512,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723617</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,46 +3566,42 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128790627</v>
       </c>
       <c r="B31" t="n">
-        <v>86756</v>
+        <v>87011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3619,10 +3609,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723660</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3652,9 +3642,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,12 +3669,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4062,45 +4062,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128791631</v>
+        <v>128784530</v>
       </c>
       <c r="B36" t="n">
-        <v>86870</v>
+        <v>86954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723764</v>
+        <v>724024</v>
       </c>
       <c r="R36" t="n">
-        <v>6384279</v>
+        <v>6384488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,25 +4141,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128784530</v>
+        <v>128790577</v>
       </c>
       <c r="B37" t="n">
         <v>86954</v>
@@ -4190,14 +4191,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>724024</v>
+        <v>723815</v>
       </c>
       <c r="R37" t="n">
-        <v>6384488</v>
+        <v>6384231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,9 +4228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4245,19 +4256,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128790577</v>
+        <v>128784518</v>
       </c>
       <c r="B38" t="n">
         <v>86954</v>
@@ -4288,14 +4299,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723815</v>
+        <v>723642</v>
       </c>
       <c r="R38" t="n">
-        <v>6384231</v>
+        <v>6384222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,19 +4336,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4353,57 +4354,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B39" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R39" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,19 +4445,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791576</v>
+        <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86802</v>
+        <v>86954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723743</v>
+        <v>723964</v>
       </c>
       <c r="R42" t="n">
-        <v>6384328</v>
+        <v>6384262</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,36 +4722,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B43" t="n">
         <v>86954</v>
@@ -4786,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R43" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4821,7 +4832,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4831,7 +4842,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,7 +4870,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790593</v>
+        <v>128790578</v>
       </c>
       <c r="B44" t="n">
         <v>86954</v>
@@ -4894,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723955</v>
+        <v>723890</v>
       </c>
       <c r="R44" t="n">
-        <v>6384354</v>
+        <v>6384224</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4929,7 +4940,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4939,7 +4950,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4967,32 +4978,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790578</v>
+        <v>128791646</v>
       </c>
       <c r="B45" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5002,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723890</v>
+        <v>723732</v>
       </c>
       <c r="R45" t="n">
-        <v>6384224</v>
+        <v>6384330</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5035,72 +5046,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B46" t="n">
-        <v>86756</v>
+        <v>86802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R46" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5172,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791646</v>
+        <v>128791593</v>
       </c>
       <c r="B47" t="n">
-        <v>86870</v>
+        <v>86756</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723732</v>
+        <v>723736</v>
       </c>
       <c r="R47" t="n">
-        <v>6384330</v>
+        <v>6384250</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784521</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86954</v>
+        <v>106944</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5377,21 +5377,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723955</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384252</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5445,7 +5445,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5464,10 +5463,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128784562</v>
+        <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>106944</v>
+        <v>86954</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5475,21 +5474,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5499,10 +5498,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723639</v>
+        <v>723955</v>
       </c>
       <c r="R50" t="n">
-        <v>6384269</v>
+        <v>6384252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,6 +5542,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5664,32 +5664,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784539</v>
+        <v>128784549</v>
       </c>
       <c r="B52" t="n">
-        <v>91029</v>
+        <v>92784</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723615</v>
+        <v>723958</v>
       </c>
       <c r="R52" t="n">
-        <v>6384240</v>
+        <v>6384364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5761,45 +5761,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784549</v>
+        <v>128791648</v>
       </c>
       <c r="B53" t="n">
-        <v>92784</v>
+        <v>90955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>3286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723958</v>
+        <v>723664</v>
       </c>
       <c r="R53" t="n">
-        <v>6384364</v>
+        <v>6384233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,57 +5846,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128791648</v>
+        <v>128784539</v>
       </c>
       <c r="B54" t="n">
-        <v>90955</v>
+        <v>91029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723664</v>
+        <v>723615</v>
       </c>
       <c r="R54" t="n">
-        <v>6384233</v>
+        <v>6384240</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5943,57 +5943,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128790589</v>
+        <v>128784554</v>
       </c>
       <c r="B55" t="n">
-        <v>86954</v>
+        <v>98621</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723770</v>
+        <v>723982</v>
       </c>
       <c r="R55" t="n">
-        <v>6384248</v>
+        <v>6384442</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6023,85 +6023,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784554</v>
+        <v>128790589</v>
       </c>
       <c r="B56" t="n">
-        <v>98621</v>
+        <v>86954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723982</v>
+        <v>723770</v>
       </c>
       <c r="R56" t="n">
-        <v>6384442</v>
+        <v>6384248</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6131,29 +6120,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128785779</v>
+        <v>128790556</v>
       </c>
       <c r="B63" t="n">
-        <v>86802</v>
+        <v>86756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723790</v>
+        <v>723703</v>
       </c>
       <c r="R63" t="n">
-        <v>6384287</v>
+        <v>6384275</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,9 +6822,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6839,19 +6849,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128790556</v>
+        <v>128791601</v>
       </c>
       <c r="B64" t="n">
         <v>86756</v>
@@ -6886,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723703</v>
+        <v>723723</v>
       </c>
       <c r="R64" t="n">
-        <v>6384275</v>
+        <v>6384387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6919,19 +6929,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6946,57 +6946,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791601</v>
+        <v>128785779</v>
       </c>
       <c r="B65" t="n">
-        <v>86756</v>
+        <v>86802</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723723</v>
+        <v>723790</v>
       </c>
       <c r="R65" t="n">
-        <v>6384387</v>
+        <v>6384287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,12 +7043,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791643</v>
+        <v>128785788</v>
       </c>
       <c r="B80" t="n">
-        <v>86870</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>248956</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723739</v>
+        <v>723850</v>
       </c>
       <c r="R80" t="n">
-        <v>6384326</v>
+        <v>6384251</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,57 +8557,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128785788</v>
+        <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>86954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723850</v>
+        <v>723763</v>
       </c>
       <c r="R81" t="n">
-        <v>6384251</v>
+        <v>6384295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,25 +8648,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128784519</v>
+        <v>128790576</v>
       </c>
       <c r="B82" t="n">
         <v>86954</v>
@@ -8697,14 +8698,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723763</v>
+        <v>723628</v>
       </c>
       <c r="R82" t="n">
-        <v>6384295</v>
+        <v>6384239</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8734,9 +8735,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8752,44 +8763,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128790576</v>
+        <v>128791643</v>
       </c>
       <c r="B83" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8799,10 +8810,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723628</v>
+        <v>723739</v>
       </c>
       <c r="R83" t="n">
-        <v>6384239</v>
+        <v>6384326</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,40 +8843,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8969,45 +8969,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86870</v>
+        <v>86954</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R85" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9048,25 +9048,26 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B86" t="n">
         <v>86954</v>
@@ -9101,10 +9102,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R86" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9164,45 +9165,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86954</v>
+        <v>86870</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R87" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9243,19 +9244,18 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9456,32 +9456,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791655</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
-        <v>90955</v>
+        <v>86802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723728</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384262</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,6 +9527,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9553,7 +9558,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
         <v>86802</v>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784508</v>
+        <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>86802</v>
+        <v>90955</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723789</v>
+        <v>723728</v>
       </c>
       <c r="R92" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814781</v>
+        <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>86988</v>
+        <v>87011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10071,23 +10071,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>248939</v>
+        <v>433</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Melot</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10095,10 +10091,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723628</v>
+        <v>723767</v>
       </c>
       <c r="R96" t="n">
-        <v>6384239</v>
+        <v>6384283</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10130,7 +10126,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10140,7 +10136,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10167,7 +10163,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128790626</v>
+        <v>128790622</v>
       </c>
       <c r="B97" t="n">
         <v>87011</v>
@@ -10198,10 +10194,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723767</v>
+        <v>723743</v>
       </c>
       <c r="R97" t="n">
-        <v>6384283</v>
+        <v>6384262</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10233,7 +10229,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10243,7 +10239,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>3st, en liten i väska</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10252,6 +10253,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10270,30 +10272,34 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128790622</v>
+        <v>128790644</v>
       </c>
       <c r="B98" t="n">
-        <v>87011</v>
+        <v>106944</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>433</v>
+        <v>221849</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10301,10 +10307,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723743</v>
+        <v>723604</v>
       </c>
       <c r="R98" t="n">
-        <v>6384262</v>
+        <v>6384282</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10336,7 +10342,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10346,12 +10352,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>3st, en liten i väska</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10360,7 +10361,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128790644</v>
+        <v>128790612</v>
       </c>
       <c r="B99" t="n">
-        <v>106944</v>
+        <v>107533</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723604</v>
+        <v>723605</v>
       </c>
       <c r="R99" t="n">
-        <v>6384282</v>
+        <v>6384273</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10486,34 +10486,30 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128790612</v>
+        <v>128790619</v>
       </c>
       <c r="B100" t="n">
-        <v>107533</v>
+        <v>87011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220079</v>
+        <v>433</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10521,10 +10517,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723605</v>
+        <v>723956</v>
       </c>
       <c r="R100" t="n">
-        <v>6384273</v>
+        <v>6384354</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10556,7 +10552,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10566,7 +10562,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I påse, en fruktkropp halvätna skivor</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10575,6 +10576,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10593,7 +10595,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128790619</v>
+        <v>128790630</v>
       </c>
       <c r="B101" t="n">
         <v>87011</v>
@@ -10624,10 +10626,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723956</v>
+        <v>723733</v>
       </c>
       <c r="R101" t="n">
-        <v>6384354</v>
+        <v>6384264</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,7 +10661,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10669,12 +10671,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I påse, en fruktkropp halvätna skivor</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10683,7 +10680,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10702,7 +10698,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128790630</v>
+        <v>128790631</v>
       </c>
       <c r="B102" t="n">
         <v>87011</v>
@@ -10733,10 +10729,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723733</v>
+        <v>723881</v>
       </c>
       <c r="R102" t="n">
-        <v>6384264</v>
+        <v>6384222</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10768,7 +10764,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10778,7 +10774,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>I väska, 1 fk, hål i ena foten</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10787,6 +10788,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10805,10 +10807,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128790631</v>
+        <v>128790570</v>
       </c>
       <c r="B103" t="n">
-        <v>87011</v>
+        <v>91029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10816,30 +10818,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723881</v>
+        <v>723614</v>
       </c>
       <c r="R103" t="n">
-        <v>6384222</v>
+        <v>6384244</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10871,7 +10880,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10881,12 +10890,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>I väska, 1 fk, hål i ena foten</t>
+          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10907,17 +10916,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Via Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128790570</v>
+        <v>128784561</v>
       </c>
       <c r="B104" t="n">
-        <v>91029</v>
+        <v>86988</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10925,37 +10934,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5747</v>
+        <v>248939</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tallpraktspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723614</v>
+        <v>723677</v>
       </c>
       <c r="R104" t="n">
-        <v>6384244</v>
+        <v>6384262</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10985,24 +10991,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11018,22 +11009,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784561</v>
+        <v>128814749</v>
       </c>
       <c r="B105" t="n">
-        <v>86988</v>
+        <v>86842</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11041,34 +11032,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>248939</v>
+        <v>442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723677</v>
+        <v>723637</v>
       </c>
       <c r="R105" t="n">
-        <v>6384262</v>
+        <v>6384245</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11098,40 +11089,54 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Dubbelrapport. Bilddokumentation av Liams fynd några meter bort.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814749</v>
+        <v>128814809</v>
       </c>
       <c r="B106" t="n">
-        <v>86842</v>
+        <v>86802</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11139,21 +11144,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11163,10 +11168,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R106" t="n">
-        <v>6384245</v>
+        <v>6384242</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11198,7 +11203,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11208,12 +11213,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Dubbelrapport. Bilddokumentation av Liams fynd några meter bort.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11240,10 +11240,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814809</v>
+        <v>128790638</v>
       </c>
       <c r="B107" t="n">
-        <v>86802</v>
+        <v>87148</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11251,34 +11251,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723615</v>
+        <v>723726</v>
       </c>
       <c r="R107" t="n">
-        <v>6384242</v>
+        <v>6384251</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11310,7 +11313,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11320,7 +11323,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11329,6 +11332,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11347,10 +11351,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128790638</v>
+        <v>128790568</v>
       </c>
       <c r="B108" t="n">
-        <v>87148</v>
+        <v>91029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11358,37 +11362,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>451</v>
+        <v>5747</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723726</v>
+        <v>723615</v>
       </c>
       <c r="R108" t="n">
-        <v>6384251</v>
+        <v>6384242</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11420,7 +11421,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11430,7 +11431,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11439,7 +11440,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11458,45 +11458,44 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128790568</v>
+        <v>128790569</v>
       </c>
       <c r="B109" t="n">
-        <v>91029</v>
+        <v>92798</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5747</v>
+        <v>6047725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723615</v>
+        <v>723948</v>
       </c>
       <c r="R109" t="n">
-        <v>6384242</v>
+        <v>6384259</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11528,7 +11527,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11538,7 +11537,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11547,6 +11546,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11565,10 +11565,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128790569</v>
+        <v>128790561</v>
       </c>
       <c r="B110" t="n">
-        <v>92798</v>
+        <v>90261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11576,33 +11576,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6047725</v>
+        <v>245042</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723948</v>
+        <v>723960</v>
       </c>
       <c r="R110" t="n">
-        <v>6384259</v>
+        <v>6384272</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11634,7 +11635,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11644,7 +11645,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11672,45 +11673,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128790561</v>
+        <v>128790618</v>
       </c>
       <c r="B111" t="n">
-        <v>90261</v>
+        <v>86870</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723960</v>
+        <v>723602</v>
       </c>
       <c r="R111" t="n">
-        <v>6384272</v>
+        <v>6384277</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11742,7 +11746,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11752,7 +11756,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11780,32 +11789,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128790618</v>
+        <v>128814781</v>
       </c>
       <c r="B112" t="n">
-        <v>86870</v>
+        <v>86920</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>248956</v>
+        <v>6037417</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11818,10 +11827,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723602</v>
+        <v>723628</v>
       </c>
       <c r="R112" t="n">
-        <v>6384277</v>
+        <v>6384239</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11853,7 +11862,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11863,12 +11872,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,34 +772,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784544</v>
+        <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>107533</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>6047725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723794</v>
+        <v>723641</v>
       </c>
       <c r="R3" t="n">
-        <v>6384290</v>
+        <v>6384196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,41 +865,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>86958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R4" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -933,39 +933,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128790598</v>
+        <v>128784544</v>
       </c>
       <c r="B5" t="n">
-        <v>86954</v>
+        <v>107539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,34 +984,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723992</v>
+        <v>723794</v>
       </c>
       <c r="R5" t="n">
-        <v>6384372</v>
+        <v>6384290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1030,85 +1041,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128790645</v>
+        <v>128784517</v>
       </c>
       <c r="B6" t="n">
-        <v>86802</v>
+        <v>86958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723788</v>
+        <v>723612</v>
       </c>
       <c r="R6" t="n">
-        <v>6384286</v>
+        <v>6384274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,49 +1138,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128785784</v>
+        <v>128790574</v>
       </c>
       <c r="B7" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,14 +1199,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723969</v>
+        <v>723609</v>
       </c>
       <c r="R7" t="n">
-        <v>6384430</v>
+        <v>6384278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,9 +1236,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,57 +1264,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128784517</v>
+        <v>128790645</v>
       </c>
       <c r="B8" t="n">
-        <v>86954</v>
+        <v>86806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723612</v>
+        <v>723788</v>
       </c>
       <c r="R8" t="n">
-        <v>6384274</v>
+        <v>6384286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,62 +1344,71 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128790574</v>
+        <v>128791638</v>
       </c>
       <c r="B9" t="n">
-        <v>86954</v>
+        <v>86874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723609</v>
+        <v>723771</v>
       </c>
       <c r="R9" t="n">
-        <v>6384278</v>
+        <v>6384299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,85 +1451,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791638</v>
+        <v>128785784</v>
       </c>
       <c r="B10" t="n">
-        <v>86870</v>
+        <v>86958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723771</v>
+        <v>723969</v>
       </c>
       <c r="R10" t="n">
-        <v>6384299</v>
+        <v>6384430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,63 +1559,64 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128785783</v>
+        <v>128790554</v>
       </c>
       <c r="B11" t="n">
-        <v>86954</v>
+        <v>86760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723974</v>
+        <v>723848</v>
       </c>
       <c r="R11" t="n">
-        <v>6384345</v>
+        <v>6384240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,22 +1674,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790554</v>
+        <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723848</v>
+        <v>723734</v>
       </c>
       <c r="R12" t="n">
-        <v>6384240</v>
+        <v>6384367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,85 +1754,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791599</v>
+        <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86756</v>
+        <v>86958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723734</v>
+        <v>723974</v>
       </c>
       <c r="R13" t="n">
-        <v>6384367</v>
+        <v>6384345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,18 +1862,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>88689</v>
+        <v>88693</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86842</v>
+        <v>86846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,32 +2877,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790581</v>
+        <v>128791624</v>
       </c>
       <c r="B24" t="n">
-        <v>86954</v>
+        <v>86874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723930</v>
+        <v>723724</v>
       </c>
       <c r="R24" t="n">
-        <v>6384314</v>
+        <v>6384209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,72 +2945,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790594</v>
+        <v>128791633</v>
       </c>
       <c r="B25" t="n">
-        <v>86954</v>
+        <v>86874</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723948</v>
+        <v>723767</v>
       </c>
       <c r="R25" t="n">
-        <v>6384417</v>
+        <v>6384282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,50 +3042,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B26" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,32 +3168,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791633</v>
+        <v>128790581</v>
       </c>
       <c r="B27" t="n">
-        <v>86870</v>
+        <v>86958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723767</v>
+        <v>723930</v>
       </c>
       <c r="R27" t="n">
-        <v>6384282</v>
+        <v>6384314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,61 +3236,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791629</v>
+        <v>128790594</v>
       </c>
       <c r="B28" t="n">
-        <v>86870</v>
+        <v>86958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723745</v>
+        <v>723948</v>
       </c>
       <c r="R28" t="n">
-        <v>6384273</v>
+        <v>6384417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,74 +3344,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785781</v>
+        <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>86756</v>
+        <v>87015</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723744</v>
+        <v>723660</v>
       </c>
       <c r="R29" t="n">
-        <v>6384205</v>
+        <v>6384309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3448,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,22 +3475,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,14 +3518,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,42 +3572,46 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128790627</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>87011</v>
+        <v>86760</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3609,10 +3619,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723660</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
-        <v>6384309</v>
+        <v>6384247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3642,19 +3652,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,12 +3669,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3684,7 +3684,7 @@
         <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128784530</v>
       </c>
       <c r="B36" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128790577</v>
       </c>
       <c r="B37" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128784518</v>
       </c>
       <c r="B38" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128791631</v>
       </c>
       <c r="B39" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>128790593</v>
       </c>
       <c r="B43" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>128790578</v>
       </c>
       <c r="B44" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>128791646</v>
       </c>
       <c r="B45" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>128791576</v>
       </c>
       <c r="B46" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>128791593</v>
       </c>
       <c r="B47" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,30 +5561,34 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128790629</v>
+        <v>128791648</v>
       </c>
       <c r="B51" t="n">
-        <v>87011</v>
+        <v>90960</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>433</v>
+        <v>3286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5592,10 +5596,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723637</v>
+        <v>723664</v>
       </c>
       <c r="R51" t="n">
-        <v>6384245</v>
+        <v>6384233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5625,19 +5629,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5652,12 +5646,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5667,7 +5661,7 @@
         <v>128784549</v>
       </c>
       <c r="B52" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,34 +5755,30 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128791648</v>
+        <v>128790629</v>
       </c>
       <c r="B53" t="n">
-        <v>90955</v>
+        <v>87015</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3286</v>
+        <v>433</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5796,10 +5786,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723664</v>
+        <v>723637</v>
       </c>
       <c r="R53" t="n">
-        <v>6384233</v>
+        <v>6384245</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5829,9 +5819,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5846,12 +5846,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5861,7 +5861,7 @@
         <v>128784539</v>
       </c>
       <c r="B54" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>128784554</v>
       </c>
       <c r="B55" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>128790589</v>
       </c>
       <c r="B56" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128785778</v>
+        <v>128784526</v>
       </c>
       <c r="B57" t="n">
-        <v>86802</v>
+        <v>86958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723760</v>
+        <v>723962</v>
       </c>
       <c r="R57" t="n">
-        <v>6384211</v>
+        <v>6384357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,63 +6239,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128790565</v>
+        <v>128784523</v>
       </c>
       <c r="B58" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723921</v>
+        <v>723878</v>
       </c>
       <c r="R58" t="n">
-        <v>6384444</v>
+        <v>6384241</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,84 +6326,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784545</v>
+        <v>128785778</v>
       </c>
       <c r="B59" t="n">
-        <v>107533</v>
+        <v>86806</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>424</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723768</v>
+        <v>723760</v>
       </c>
       <c r="R59" t="n">
-        <v>6384301</v>
+        <v>6384211</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6449,22 +6441,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784551</v>
+        <v>128790565</v>
       </c>
       <c r="B60" t="n">
-        <v>98621</v>
+        <v>86784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6472,34 +6464,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219811</v>
+        <v>3712</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723631</v>
+        <v>723921</v>
       </c>
       <c r="R60" t="n">
-        <v>6384236</v>
+        <v>6384444</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6529,9 +6521,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6546,22 +6548,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784526</v>
+        <v>128784545</v>
       </c>
       <c r="B61" t="n">
-        <v>86954</v>
+        <v>107539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6569,21 +6571,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6593,10 +6595,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723962</v>
+        <v>723768</v>
       </c>
       <c r="R61" t="n">
-        <v>6384357</v>
+        <v>6384301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6637,7 +6639,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6656,32 +6657,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784523</v>
+        <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>86954</v>
+        <v>98627</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6691,10 +6692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723878</v>
+        <v>723631</v>
       </c>
       <c r="R62" t="n">
-        <v>6384241</v>
+        <v>6384236</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6735,7 +6736,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128790556</v>
+        <v>128785779</v>
       </c>
       <c r="B63" t="n">
-        <v>86756</v>
+        <v>86806</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723703</v>
+        <v>723790</v>
       </c>
       <c r="R63" t="n">
-        <v>6384275</v>
+        <v>6384287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,19 +6822,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6849,22 +6839,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791601</v>
+        <v>128790556</v>
       </c>
       <c r="B64" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723723</v>
+        <v>723703</v>
       </c>
       <c r="R64" t="n">
-        <v>6384387</v>
+        <v>6384275</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6929,9 +6919,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6946,57 +6946,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128785779</v>
+        <v>128791601</v>
       </c>
       <c r="B65" t="n">
-        <v>86802</v>
+        <v>86760</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723790</v>
+        <v>723723</v>
       </c>
       <c r="R65" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,12 +7043,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
         <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>128784516</v>
       </c>
       <c r="B67" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>128784527</v>
       </c>
       <c r="B68" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128785782</v>
       </c>
       <c r="B69" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7544,45 +7544,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B71" t="n">
-        <v>86756</v>
+        <v>90960</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R71" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,85 +7612,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785795</v>
+        <v>128790555</v>
       </c>
       <c r="B72" t="n">
-        <v>90955</v>
+        <v>86760</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723789</v>
+        <v>723944</v>
       </c>
       <c r="R72" t="n">
-        <v>6384213</v>
+        <v>6384278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,61 +7709,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790611</v>
+        <v>128791626</v>
       </c>
       <c r="B73" t="n">
-        <v>105669</v>
+        <v>86874</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224098</v>
+        <v>248956</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723942</v>
+        <v>723741</v>
       </c>
       <c r="R73" t="n">
-        <v>6384482</v>
+        <v>6384216</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,19 +7817,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7844,44 +7834,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128784542</v>
+        <v>128784529</v>
       </c>
       <c r="B74" t="n">
-        <v>105669</v>
+        <v>86958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7891,10 +7881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723833</v>
+        <v>723953</v>
       </c>
       <c r="R74" t="n">
-        <v>6384211</v>
+        <v>6384442</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7935,6 +7925,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7953,10 +7944,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128784529</v>
+        <v>128790592</v>
       </c>
       <c r="B75" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7984,14 +7975,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723953</v>
+        <v>723955</v>
       </c>
       <c r="R75" t="n">
-        <v>6384442</v>
+        <v>6384283</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8021,9 +8012,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8039,22 +8040,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128790592</v>
+        <v>128790597</v>
       </c>
       <c r="B76" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8086,10 +8087,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723955</v>
+        <v>723990</v>
       </c>
       <c r="R76" t="n">
-        <v>6384283</v>
+        <v>6384408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8121,7 +8122,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8131,7 +8132,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8159,32 +8160,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790597</v>
+        <v>128790611</v>
       </c>
       <c r="B77" t="n">
-        <v>86954</v>
+        <v>105675</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8194,10 +8195,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723990</v>
+        <v>723942</v>
       </c>
       <c r="R77" t="n">
-        <v>6384408</v>
+        <v>6384482</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8229,7 +8230,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8239,7 +8240,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8248,7 +8249,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8267,45 +8267,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791626</v>
+        <v>128784542</v>
       </c>
       <c r="B78" t="n">
-        <v>86870</v>
+        <v>105675</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>248956</v>
+        <v>224098</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723741</v>
+        <v>723833</v>
       </c>
       <c r="R78" t="n">
-        <v>6384216</v>
+        <v>6384211</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,12 +8352,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128785788</v>
+        <v>128791643</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>86874</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>248956</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723850</v>
+        <v>723739</v>
       </c>
       <c r="R80" t="n">
-        <v>6384251</v>
+        <v>6384326</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,12 +8557,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8572,7 +8572,7 @@
         <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>128790576</v>
       </c>
       <c r="B82" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8775,45 +8775,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791643</v>
+        <v>128785788</v>
       </c>
       <c r="B83" t="n">
-        <v>86870</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>248956</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723739</v>
+        <v>723850</v>
       </c>
       <c r="R83" t="n">
-        <v>6384326</v>
+        <v>6384251</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8860,12 +8860,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
         <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>128784522</v>
       </c>
       <c r="B86" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>128791578</v>
       </c>
       <c r="B90" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10163,30 +10163,34 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128790622</v>
+        <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>87011</v>
+        <v>106950</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>433</v>
+        <v>221849</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10194,10 +10198,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723743</v>
+        <v>723604</v>
       </c>
       <c r="R97" t="n">
-        <v>6384262</v>
+        <v>6384282</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10229,7 +10233,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10239,12 +10243,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>3st, en liten i väska</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10253,7 +10252,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10272,10 +10270,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128790644</v>
+        <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>106944</v>
+        <v>107539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10283,21 +10281,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10307,10 +10305,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723604</v>
+        <v>723605</v>
       </c>
       <c r="R98" t="n">
-        <v>6384282</v>
+        <v>6384273</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10342,7 +10340,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10352,7 +10350,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10379,34 +10377,30 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128790612</v>
+        <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>107533</v>
+        <v>87015</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220079</v>
+        <v>433</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10414,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723605</v>
+        <v>723733</v>
       </c>
       <c r="R99" t="n">
-        <v>6384273</v>
+        <v>6384264</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10443,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10459,7 +10453,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10486,10 +10480,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128790619</v>
+        <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>87011</v>
+        <v>91034</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10497,30 +10491,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723956</v>
+        <v>723614</v>
       </c>
       <c r="R100" t="n">
-        <v>6384354</v>
+        <v>6384244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10552,7 +10553,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10562,12 +10563,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>I påse, en fruktkropp halvätna skivor</t>
+          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10595,10 +10596,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128790630</v>
+        <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>87011</v>
+        <v>86846</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10606,19 +10607,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10626,10 +10631,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723733</v>
+        <v>723637</v>
       </c>
       <c r="R101" t="n">
-        <v>6384264</v>
+        <v>6384245</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10661,7 +10666,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10671,7 +10676,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Dubbelrapport. Bilddokumentation av Liams fynd några meter bort.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10698,10 +10708,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128790631</v>
+        <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>87011</v>
+        <v>86806</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10709,19 +10719,23 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -10729,10 +10743,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723881</v>
+        <v>723615</v>
       </c>
       <c r="R102" t="n">
-        <v>6384222</v>
+        <v>6384242</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,7 +10778,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10774,12 +10788,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>I väska, 1 fk, hål i ena foten</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10788,7 +10797,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10807,10 +10815,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128790570</v>
+        <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>91029</v>
+        <v>87152</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10818,21 +10826,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5747</v>
+        <v>451</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10845,10 +10853,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723614</v>
+        <v>723726</v>
       </c>
       <c r="R103" t="n">
-        <v>6384244</v>
+        <v>6384251</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10880,7 +10888,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10890,12 +10898,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Långsmala fruktkroppar tillhör den andra rapporten.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10916,17 +10919,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Via Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128784561</v>
+        <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>86988</v>
+        <v>91034</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10934,34 +10937,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>248939</v>
+        <v>5747</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723677</v>
+        <v>723615</v>
       </c>
       <c r="R104" t="n">
-        <v>6384262</v>
+        <v>6384242</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10991,75 +10994,83 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814749</v>
+        <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>86842</v>
+        <v>92803</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>442</v>
+        <v>6047725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723637</v>
+        <v>723948</v>
       </c>
       <c r="R105" t="n">
-        <v>6384245</v>
+        <v>6384259</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11091,7 +11102,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11101,12 +11112,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Dubbelrapport. Bilddokumentation av Liams fynd några meter bort.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11115,6 +11121,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11133,10 +11140,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814809</v>
+        <v>128790618</v>
       </c>
       <c r="B106" t="n">
-        <v>86802</v>
+        <v>86874</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11144,34 +11151,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723615</v>
+        <v>723602</v>
       </c>
       <c r="R106" t="n">
-        <v>6384242</v>
+        <v>6384277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11203,7 +11213,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11213,7 +11223,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11222,6 +11237,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11240,48 +11256,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128790638</v>
+        <v>128790561</v>
       </c>
       <c r="B107" t="n">
-        <v>87148</v>
+        <v>90266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>451</v>
+        <v>245042</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723726</v>
+        <v>723960</v>
       </c>
       <c r="R107" t="n">
-        <v>6384251</v>
+        <v>6384272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11313,7 +11326,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11323,7 +11336,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11351,45 +11364,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128790568</v>
+        <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>91029</v>
+        <v>86924</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5747</v>
+        <v>6037417</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723615</v>
+        <v>723628</v>
       </c>
       <c r="R108" t="n">
-        <v>6384242</v>
+        <v>6384239</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11421,7 +11437,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11431,7 +11447,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11440,6 +11456,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11458,27 +11475,27 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128790569</v>
+        <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>92798</v>
+        <v>87015</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -11492,10 +11509,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723948</v>
+        <v>723743</v>
       </c>
       <c r="R109" t="n">
-        <v>6384259</v>
+        <v>6384262</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11527,7 +11544,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11537,7 +11554,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11565,45 +11582,44 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128790561</v>
+        <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>90261</v>
+        <v>87015</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245042</v>
+        <v>433</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723960</v>
+        <v>723956</v>
       </c>
       <c r="R110" t="n">
-        <v>6384272</v>
+        <v>6384354</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11635,7 +11651,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11645,7 +11661,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11673,10 +11689,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128790618</v>
+        <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>86870</v>
+        <v>87015</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11684,23 +11700,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -11711,10 +11723,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723602</v>
+        <v>723881</v>
       </c>
       <c r="R111" t="n">
-        <v>6384277</v>
+        <v>6384222</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11746,7 +11758,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11756,12 +11768,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11789,10 +11796,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814781</v>
+        <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86920</v>
+        <v>86924</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11823,14 +11830,14 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723628</v>
+        <v>723677</v>
       </c>
       <c r="R112" t="n">
-        <v>6384239</v>
+        <v>6384262</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11860,19 +11867,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11888,12 +11885,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>107546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R2" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>128790598</v>
       </c>
       <c r="B4" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +973,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B5" t="n">
-        <v>107539</v>
+        <v>90965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -984,34 +984,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R5" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,57 +1058,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128784517</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86958</v>
+        <v>86806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723612</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384274</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,40 +1138,49 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128790574</v>
+        <v>128785784</v>
       </c>
       <c r="B7" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,14 +1208,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723609</v>
+        <v>723969</v>
       </c>
       <c r="R7" t="n">
-        <v>6384278</v>
+        <v>6384430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,19 +1245,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,57 +1263,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128790645</v>
+        <v>128784517</v>
       </c>
       <c r="B8" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723788</v>
+        <v>723612</v>
       </c>
       <c r="R8" t="n">
-        <v>6384286</v>
+        <v>6384274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,71 +1343,62 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791638</v>
+        <v>128790574</v>
       </c>
       <c r="B9" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1418,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723771</v>
+        <v>723609</v>
       </c>
       <c r="R9" t="n">
-        <v>6384299</v>
+        <v>6384278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,74 +1441,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128785784</v>
+        <v>128791638</v>
       </c>
       <c r="B10" t="n">
-        <v>86958</v>
+        <v>86875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723969</v>
+        <v>723771</v>
       </c>
       <c r="R10" t="n">
-        <v>6384430</v>
+        <v>6384299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,64 +1560,63 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B11" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R11" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,19 +1664,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B12" t="n">
         <v>86760</v>
@@ -1721,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R12" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,74 +1744,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86958</v>
+        <v>86760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R13" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,49 +1863,52 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791663</v>
+        <v>128790595</v>
       </c>
       <c r="B14" t="n">
-        <v>87015</v>
+        <v>86959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723971</v>
+        <v>723931</v>
       </c>
       <c r="R14" t="n">
-        <v>6384460</v>
+        <v>6384427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,63 +1949,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784509</v>
+        <v>128784511</v>
       </c>
       <c r="B15" t="n">
-        <v>86806</v>
+        <v>92808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2009,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723618</v>
+        <v>723600</v>
       </c>
       <c r="R15" t="n">
-        <v>6384286</v>
+        <v>6384247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,45 +2082,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784506</v>
+        <v>128790583</v>
       </c>
       <c r="B16" t="n">
-        <v>88693</v>
+        <v>86959</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723922</v>
+        <v>723986</v>
       </c>
       <c r="R16" t="n">
-        <v>6384266</v>
+        <v>6384358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,63 +2150,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B17" t="n">
-        <v>86958</v>
+        <v>87016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2203,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R17" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,70 +2254,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784511</v>
+        <v>128784509</v>
       </c>
       <c r="B18" t="n">
-        <v>92803</v>
+        <v>86806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723600</v>
+        <v>723618</v>
       </c>
       <c r="R18" t="n">
-        <v>6384247</v>
+        <v>6384286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,45 +2380,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790583</v>
+        <v>128784506</v>
       </c>
       <c r="B19" t="n">
-        <v>86958</v>
+        <v>88694</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723986</v>
+        <v>723922</v>
       </c>
       <c r="R19" t="n">
-        <v>6384358</v>
+        <v>6384266</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,40 +2448,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,32 +2877,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791624</v>
+        <v>128790581</v>
       </c>
       <c r="B24" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723724</v>
+        <v>723930</v>
       </c>
       <c r="R24" t="n">
-        <v>6384209</v>
+        <v>6384314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,61 +2945,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791633</v>
+        <v>128790594</v>
       </c>
       <c r="B25" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3009,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723767</v>
+        <v>723948</v>
       </c>
       <c r="R25" t="n">
-        <v>6384282</v>
+        <v>6384417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,39 +3053,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791629</v>
+        <v>128791633</v>
       </c>
       <c r="B26" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723745</v>
+        <v>723767</v>
       </c>
       <c r="R26" t="n">
-        <v>6384273</v>
+        <v>6384282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3168,32 +3190,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790581</v>
+        <v>128791624</v>
       </c>
       <c r="B27" t="n">
-        <v>86958</v>
+        <v>86875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3203,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723930</v>
+        <v>723724</v>
       </c>
       <c r="R27" t="n">
-        <v>6384314</v>
+        <v>6384209</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,72 +3258,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790594</v>
+        <v>128791629</v>
       </c>
       <c r="B28" t="n">
-        <v>86958</v>
+        <v>86875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723948</v>
+        <v>723745</v>
       </c>
       <c r="R28" t="n">
-        <v>6384417</v>
+        <v>6384273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,81 +3355,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>87015</v>
+        <v>86760</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R29" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,19 +3452,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,19 +3469,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128791591</v>
       </c>
       <c r="B30" t="n">
         <v>86760</v>
@@ -3518,14 +3512,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723617</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,22 +3566,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128785780</v>
       </c>
       <c r="B31" t="n">
-        <v>86760</v>
+        <v>92808</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,31 +3589,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723935</v>
       </c>
       <c r="R31" t="n">
         <v>6384247</v>
@@ -3663,18 +3653,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3684,7 +3675,7 @@
         <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,41 +3769,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785780</v>
+        <v>128790627</v>
       </c>
       <c r="B33" t="n">
-        <v>92803</v>
+        <v>87016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723935</v>
+        <v>723660</v>
       </c>
       <c r="R33" t="n">
-        <v>6384247</v>
+        <v>6384309</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3842,30 +3833,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
         <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4062,45 +4062,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128784530</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86958</v>
+        <v>86875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>724024</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384488</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,29 +4141,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128790577</v>
+        <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,14 +4190,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723815</v>
+        <v>724024</v>
       </c>
       <c r="R37" t="n">
-        <v>6384231</v>
+        <v>6384488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,19 +4227,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4256,22 +4245,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128784518</v>
+        <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,14 +4288,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723642</v>
+        <v>723815</v>
       </c>
       <c r="R38" t="n">
-        <v>6384222</v>
+        <v>6384231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,9 +4325,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,57 +4353,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,28 +4444,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B40" t="n">
-        <v>86760</v>
+        <v>92808</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,34 +4474,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R40" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,28 +4538,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B41" t="n">
-        <v>92803</v>
+        <v>86760</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,30 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R41" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,19 +4636,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>128790593</v>
       </c>
       <c r="B43" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>128790578</v>
       </c>
       <c r="B44" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>128791646</v>
       </c>
       <c r="B45" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5075,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791576</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86806</v>
+        <v>86760</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723743</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384328</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5172,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B47" t="n">
-        <v>86760</v>
+        <v>86806</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R47" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,45 +5269,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B48" t="n">
-        <v>86806</v>
+        <v>106957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R48" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B49" t="n">
-        <v>106950</v>
+        <v>86806</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R49" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
         <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>128791648</v>
       </c>
       <c r="B51" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,32 +5658,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784549</v>
+        <v>128784539</v>
       </c>
       <c r="B52" t="n">
-        <v>92789</v>
+        <v>91039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723958</v>
+        <v>723615</v>
       </c>
       <c r="R52" t="n">
-        <v>6384364</v>
+        <v>6384240</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,41 +5755,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128790629</v>
+        <v>128784554</v>
       </c>
       <c r="B53" t="n">
-        <v>87015</v>
+        <v>98634</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723637</v>
+        <v>723982</v>
       </c>
       <c r="R53" t="n">
-        <v>6384245</v>
+        <v>6384442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5819,19 +5823,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5846,22 +5840,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784539</v>
+        <v>128790629</v>
       </c>
       <c r="B54" t="n">
-        <v>91034</v>
+        <v>87016</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,34 +5863,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>433</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723615</v>
+        <v>723637</v>
       </c>
       <c r="R54" t="n">
-        <v>6384240</v>
+        <v>6384245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,9 +5916,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,22 +5943,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128784554</v>
+        <v>128784549</v>
       </c>
       <c r="B55" t="n">
-        <v>98627</v>
+        <v>92794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219811</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723982</v>
+        <v>723958</v>
       </c>
       <c r="R55" t="n">
-        <v>6384442</v>
+        <v>6384364</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6055,7 +6055,7 @@
         <v>128790589</v>
       </c>
       <c r="B56" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128784526</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86958</v>
+        <v>86806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723962</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384357</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,29 +6239,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784523</v>
+        <v>128784545</v>
       </c>
       <c r="B58" t="n">
-        <v>86958</v>
+        <v>107546</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6269,21 +6268,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6293,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723878</v>
+        <v>723768</v>
       </c>
       <c r="R58" t="n">
-        <v>6384241</v>
+        <v>6384301</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,7 +6336,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6356,45 +6354,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128785778</v>
+        <v>128784551</v>
       </c>
       <c r="B59" t="n">
-        <v>86806</v>
+        <v>98634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>219811</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723760</v>
+        <v>723631</v>
       </c>
       <c r="R59" t="n">
-        <v>6384211</v>
+        <v>6384236</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6441,57 +6439,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128790565</v>
+        <v>128784526</v>
       </c>
       <c r="B60" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723921</v>
+        <v>723962</v>
       </c>
       <c r="R60" t="n">
-        <v>6384444</v>
+        <v>6384357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,49 +6519,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784545</v>
+        <v>128784523</v>
       </c>
       <c r="B61" t="n">
-        <v>107539</v>
+        <v>86959</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6571,21 +6560,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6595,10 +6584,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723768</v>
+        <v>723878</v>
       </c>
       <c r="R61" t="n">
-        <v>6384301</v>
+        <v>6384241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6639,6 +6628,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6657,10 +6647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784551</v>
+        <v>128790565</v>
       </c>
       <c r="B62" t="n">
-        <v>98627</v>
+        <v>86784</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6668,34 +6658,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219811</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723631</v>
+        <v>723921</v>
       </c>
       <c r="R62" t="n">
-        <v>6384236</v>
+        <v>6384444</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6725,9 +6715,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6742,12 +6742,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
         <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>128784516</v>
       </c>
       <c r="B67" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>128784527</v>
       </c>
       <c r="B68" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>128785782</v>
       </c>
       <c r="B69" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128784510</v>
+        <v>128790611</v>
       </c>
       <c r="B70" t="n">
-        <v>86806</v>
+        <v>105682</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>424</v>
+        <v>224098</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723610</v>
+        <v>723942</v>
       </c>
       <c r="R70" t="n">
-        <v>6384274</v>
+        <v>6384482</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,9 +7515,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7532,57 +7542,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128785795</v>
+        <v>128784542</v>
       </c>
       <c r="B71" t="n">
-        <v>90960</v>
+        <v>105682</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3286</v>
+        <v>224098</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723789</v>
+        <v>723833</v>
       </c>
       <c r="R71" t="n">
-        <v>6384213</v>
+        <v>6384211</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7629,44 +7639,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790555</v>
+        <v>128791626</v>
       </c>
       <c r="B72" t="n">
-        <v>86760</v>
+        <v>86875</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7676,10 +7686,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723944</v>
+        <v>723741</v>
       </c>
       <c r="R72" t="n">
-        <v>6384278</v>
+        <v>6384216</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,85 +7719,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791626</v>
+        <v>128785795</v>
       </c>
       <c r="B73" t="n">
-        <v>86874</v>
+        <v>90965</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>248956</v>
+        <v>3286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723741</v>
+        <v>723789</v>
       </c>
       <c r="R73" t="n">
-        <v>6384216</v>
+        <v>6384213</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7834,57 +7833,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128784529</v>
+        <v>128790555</v>
       </c>
       <c r="B74" t="n">
-        <v>86958</v>
+        <v>86760</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723953</v>
+        <v>723944</v>
       </c>
       <c r="R74" t="n">
-        <v>6384442</v>
+        <v>6384278</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7914,9 +7913,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,57 +7941,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128790592</v>
+        <v>128784510</v>
       </c>
       <c r="B75" t="n">
-        <v>86958</v>
+        <v>86806</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723955</v>
+        <v>723610</v>
       </c>
       <c r="R75" t="n">
-        <v>6384283</v>
+        <v>6384274</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8012,50 +8021,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128790597</v>
+        <v>128784529</v>
       </c>
       <c r="B76" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8083,14 +8081,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723990</v>
+        <v>723953</v>
       </c>
       <c r="R76" t="n">
-        <v>6384408</v>
+        <v>6384442</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8120,19 +8118,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8148,44 +8136,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790611</v>
+        <v>128790592</v>
       </c>
       <c r="B77" t="n">
-        <v>105675</v>
+        <v>86959</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8195,10 +8183,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723942</v>
+        <v>723955</v>
       </c>
       <c r="R77" t="n">
-        <v>6384482</v>
+        <v>6384283</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8230,7 +8218,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8240,7 +8228,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8249,6 +8237,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8267,45 +8256,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128784542</v>
+        <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>105675</v>
+        <v>86959</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723833</v>
+        <v>723990</v>
       </c>
       <c r="R78" t="n">
-        <v>6384211</v>
+        <v>6384408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,29 +8324,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>128791643</v>
       </c>
       <c r="B80" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8569,45 +8569,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128784519</v>
+        <v>128785788</v>
       </c>
       <c r="B81" t="n">
-        <v>86958</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723763</v>
+        <v>723850</v>
       </c>
       <c r="R81" t="n">
-        <v>6384295</v>
+        <v>6384251</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,29 +8648,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128790576</v>
+        <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8698,14 +8697,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723628</v>
+        <v>723763</v>
       </c>
       <c r="R82" t="n">
-        <v>6384239</v>
+        <v>6384295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,19 +8734,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8763,57 +8752,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128785788</v>
+        <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723850</v>
+        <v>723628</v>
       </c>
       <c r="R83" t="n">
-        <v>6384251</v>
+        <v>6384239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8843,29 +8832,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
         <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>128784522</v>
       </c>
       <c r="B86" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9262,45 +9262,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B88" t="n">
-        <v>86806</v>
+        <v>86760</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R88" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B89" t="n">
-        <v>86760</v>
+        <v>86806</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R89" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,19 +9444,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B90" t="n">
         <v>86806</v>
@@ -9487,14 +9487,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R90" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9529,11 +9529,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9546,19 +9541,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
         <v>86806</v>
@@ -9589,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9631,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,12 +9643,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
         <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107539</v>
+        <v>107546</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87152</v>
+        <v>87153</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11140,48 +11140,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128790618</v>
+        <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>86874</v>
+        <v>90271</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723602</v>
+        <v>723960</v>
       </c>
       <c r="R106" t="n">
-        <v>6384277</v>
+        <v>6384272</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11213,7 +11210,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11223,12 +11220,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11256,45 +11248,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128790561</v>
+        <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>90266</v>
+        <v>86875</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723960</v>
+        <v>723602</v>
       </c>
       <c r="R107" t="n">
-        <v>6384272</v>
+        <v>6384277</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11326,7 +11321,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11336,7 +11331,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86924</v>
+        <v>86925</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86924</v>
+        <v>86925</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>107546</v>
+        <v>90965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -973,10 +973,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B5" t="n">
-        <v>90965</v>
+        <v>107546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -984,34 +984,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R5" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,12 +1058,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1177,45 +1177,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128785784</v>
+        <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723969</v>
+        <v>723771</v>
       </c>
       <c r="R7" t="n">
-        <v>6384430</v>
+        <v>6384299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,26 +1256,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128784517</v>
+        <v>128785784</v>
       </c>
       <c r="B8" t="n">
         <v>86959</v>
@@ -1306,14 +1305,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723612</v>
+        <v>723969</v>
       </c>
       <c r="R8" t="n">
-        <v>6384274</v>
+        <v>6384430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,19 +1360,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128790574</v>
+        <v>128784517</v>
       </c>
       <c r="B9" t="n">
         <v>86959</v>
@@ -1404,14 +1403,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723609</v>
+        <v>723612</v>
       </c>
       <c r="R9" t="n">
-        <v>6384278</v>
+        <v>6384274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,19 +1440,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,44 +1458,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791638</v>
+        <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723771</v>
+        <v>723609</v>
       </c>
       <c r="R10" t="n">
-        <v>6384299</v>
+        <v>6384278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,74 +1538,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B11" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R11" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,64 +1657,63 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B12" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R12" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,19 +1743,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,19 +1761,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B13" t="n">
         <v>86760</v>
@@ -1819,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R13" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,63 +1841,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>86959</v>
+        <v>87016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R14" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,70 +1945,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784511</v>
+        <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>92808</v>
+        <v>86806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2020,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723600</v>
+        <v>723618</v>
       </c>
       <c r="R15" t="n">
-        <v>6384247</v>
+        <v>6384286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,45 +2071,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790583</v>
+        <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>86959</v>
+        <v>88694</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723986</v>
+        <v>723922</v>
       </c>
       <c r="R16" t="n">
-        <v>6384358</v>
+        <v>6384266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,70 +2139,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128791663</v>
+        <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>87016</v>
+        <v>86959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2221,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723971</v>
+        <v>723931</v>
       </c>
       <c r="R17" t="n">
-        <v>6384460</v>
+        <v>6384427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2254,63 +2236,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784509</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>86806</v>
+        <v>92808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2318,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723618</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384286</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,45 +2369,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128784506</v>
+        <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>88694</v>
+        <v>86959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723922</v>
+        <v>723986</v>
       </c>
       <c r="R19" t="n">
-        <v>6384266</v>
+        <v>6384358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,29 +2437,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2683,32 +2683,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128784553</v>
       </c>
       <c r="B22" t="n">
-        <v>86846</v>
+        <v>98634</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>219811</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723659</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384257</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128790581</v>
       </c>
       <c r="B23" t="n">
-        <v>98634</v>
+        <v>86959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723930</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,36 +2848,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790581</v>
+        <v>128790594</v>
       </c>
       <c r="B24" t="n">
         <v>86959</v>
@@ -2912,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723930</v>
+        <v>723948</v>
       </c>
       <c r="R24" t="n">
-        <v>6384314</v>
+        <v>6384417</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,7 +2958,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2957,7 +2968,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2985,32 +2996,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790594</v>
+        <v>128791633</v>
       </c>
       <c r="B25" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723948</v>
+        <v>723767</v>
       </c>
       <c r="R25" t="n">
-        <v>6384417</v>
+        <v>6384282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,47 +3064,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791633</v>
+        <v>128791624</v>
       </c>
       <c r="B26" t="n">
         <v>86875</v>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723767</v>
+        <v>723724</v>
       </c>
       <c r="R26" t="n">
-        <v>6384282</v>
+        <v>6384209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B27" t="n">
         <v>86875</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R27" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791629</v>
+        <v>128784550</v>
       </c>
       <c r="B28" t="n">
-        <v>86875</v>
+        <v>86846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,34 +3298,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723745</v>
+        <v>723644</v>
       </c>
       <c r="R28" t="n">
-        <v>6384273</v>
+        <v>6384278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,57 +3372,53 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785781</v>
+        <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>86760</v>
+        <v>87016</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723744</v>
+        <v>723660</v>
       </c>
       <c r="R29" t="n">
-        <v>6384205</v>
+        <v>6384309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3448,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,19 +3475,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
         <v>86760</v>
@@ -3512,14 +3518,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,22 +3572,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128785780</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>92808</v>
+        <v>86760</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,27 +3595,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723935</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
         <v>6384247</v>
@@ -3653,64 +3663,59 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128791642</v>
+        <v>128785780</v>
       </c>
       <c r="B32" t="n">
-        <v>86875</v>
+        <v>92808</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723745</v>
+        <v>723935</v>
       </c>
       <c r="R32" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,28 +3756,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790627</v>
+        <v>128791642</v>
       </c>
       <c r="B33" t="n">
-        <v>87016</v>
+        <v>86875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,19 +3786,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3800,10 +3810,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723660</v>
+        <v>723745</v>
       </c>
       <c r="R33" t="n">
-        <v>6384309</v>
+        <v>6384321</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,19 +3843,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3860,12 +3860,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4062,45 +4062,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128791631</v>
+        <v>128784530</v>
       </c>
       <c r="B36" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723764</v>
+        <v>724024</v>
       </c>
       <c r="R36" t="n">
-        <v>6384279</v>
+        <v>6384488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,25 +4141,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128784530</v>
+        <v>128790577</v>
       </c>
       <c r="B37" t="n">
         <v>86959</v>
@@ -4190,14 +4191,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>724024</v>
+        <v>723815</v>
       </c>
       <c r="R37" t="n">
-        <v>6384488</v>
+        <v>6384231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,9 +4228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4245,19 +4256,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128790577</v>
+        <v>128784518</v>
       </c>
       <c r="B38" t="n">
         <v>86959</v>
@@ -4288,14 +4299,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723815</v>
+        <v>723642</v>
       </c>
       <c r="R38" t="n">
-        <v>6384231</v>
+        <v>6384222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,19 +4336,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4353,57 +4354,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B39" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R39" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,29 +4445,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>92808</v>
+        <v>86760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,30 +4474,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R40" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,29 +4542,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>86760</v>
+        <v>92808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4571,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R41" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4636,50 +4635,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128790580</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86959</v>
+        <v>86806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723964</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384262</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,72 +4722,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790593</v>
+        <v>128791593</v>
       </c>
       <c r="B43" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723955</v>
+        <v>723736</v>
       </c>
       <c r="R43" t="n">
-        <v>6384354</v>
+        <v>6384250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4830,47 +4819,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790578</v>
+        <v>128790580</v>
       </c>
       <c r="B44" t="n">
         <v>86959</v>
@@ -4905,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723890</v>
+        <v>723964</v>
       </c>
       <c r="R44" t="n">
-        <v>6384224</v>
+        <v>6384262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4940,7 +4918,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4950,7 +4928,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4978,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128791646</v>
+        <v>128790593</v>
       </c>
       <c r="B45" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723732</v>
+        <v>723955</v>
       </c>
       <c r="R45" t="n">
-        <v>6384330</v>
+        <v>6384354</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5046,61 +5024,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791593</v>
+        <v>128790578</v>
       </c>
       <c r="B46" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723736</v>
+        <v>723890</v>
       </c>
       <c r="R46" t="n">
-        <v>6384250</v>
+        <v>6384224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,39 +5132,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791576</v>
+        <v>128791646</v>
       </c>
       <c r="B47" t="n">
-        <v>86806</v>
+        <v>86875</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723743</v>
+        <v>723732</v>
       </c>
       <c r="R47" t="n">
-        <v>6384328</v>
+        <v>6384330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,45 +5269,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>106957</v>
+        <v>86806</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86806</v>
+        <v>106957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5658,32 +5658,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784539</v>
+        <v>128784554</v>
       </c>
       <c r="B52" t="n">
-        <v>91039</v>
+        <v>98634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>219811</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723615</v>
+        <v>723982</v>
       </c>
       <c r="R52" t="n">
-        <v>6384240</v>
+        <v>6384442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5755,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784554</v>
+        <v>128790589</v>
       </c>
       <c r="B53" t="n">
-        <v>98634</v>
+        <v>86959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723982</v>
+        <v>723770</v>
       </c>
       <c r="R53" t="n">
-        <v>6384442</v>
+        <v>6384248</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5823,29 +5823,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6052,45 +6063,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128790589</v>
+        <v>128784539</v>
       </c>
       <c r="B56" t="n">
-        <v>86959</v>
+        <v>91039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723770</v>
+        <v>723615</v>
       </c>
       <c r="R56" t="n">
-        <v>6384248</v>
+        <v>6384240</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6120,40 +6131,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6257,45 +6257,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784545</v>
+        <v>128790565</v>
       </c>
       <c r="B58" t="n">
-        <v>107546</v>
+        <v>86784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>3712</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723768</v>
+        <v>723921</v>
       </c>
       <c r="R58" t="n">
-        <v>6384301</v>
+        <v>6384444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,9 +6325,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6342,44 +6352,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784551</v>
+        <v>128784545</v>
       </c>
       <c r="B59" t="n">
-        <v>98634</v>
+        <v>107546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6389,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723631</v>
+        <v>723768</v>
       </c>
       <c r="R59" t="n">
-        <v>6384236</v>
+        <v>6384301</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6451,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784526</v>
+        <v>128784551</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>98634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6486,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723962</v>
+        <v>723631</v>
       </c>
       <c r="R60" t="n">
-        <v>6384357</v>
+        <v>6384236</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,7 +6540,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6549,7 +6558,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784523</v>
+        <v>128784526</v>
       </c>
       <c r="B61" t="n">
         <v>86959</v>
@@ -6584,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723878</v>
+        <v>723962</v>
       </c>
       <c r="R61" t="n">
-        <v>6384241</v>
+        <v>6384357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6647,45 +6656,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128790565</v>
+        <v>128784523</v>
       </c>
       <c r="B62" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723921</v>
+        <v>723878</v>
       </c>
       <c r="R62" t="n">
-        <v>6384444</v>
+        <v>6384241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,39 +6724,30 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7447,32 +7447,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128790611</v>
+        <v>128791626</v>
       </c>
       <c r="B70" t="n">
-        <v>105682</v>
+        <v>86875</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224098</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723942</v>
+        <v>723741</v>
       </c>
       <c r="R70" t="n">
-        <v>6384482</v>
+        <v>6384216</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,19 +7515,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7542,44 +7532,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784542</v>
+        <v>128784529</v>
       </c>
       <c r="B71" t="n">
-        <v>105682</v>
+        <v>86959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7589,10 +7579,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723833</v>
+        <v>723953</v>
       </c>
       <c r="R71" t="n">
-        <v>6384211</v>
+        <v>6384442</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7633,6 +7623,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7651,32 +7642,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791626</v>
+        <v>128790592</v>
       </c>
       <c r="B72" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7686,10 +7677,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723741</v>
+        <v>723955</v>
       </c>
       <c r="R72" t="n">
-        <v>6384216</v>
+        <v>6384283</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7719,39 +7710,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128785795</v>
+        <v>128790597</v>
       </c>
       <c r="B73" t="n">
-        <v>90965</v>
+        <v>86959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7759,34 +7761,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723789</v>
+        <v>723990</v>
       </c>
       <c r="R73" t="n">
-        <v>6384213</v>
+        <v>6384408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7816,74 +7818,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B74" t="n">
-        <v>86760</v>
+        <v>90965</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R74" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7913,85 +7926,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128784510</v>
+        <v>128790555</v>
       </c>
       <c r="B75" t="n">
-        <v>86806</v>
+        <v>86760</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723610</v>
+        <v>723944</v>
       </c>
       <c r="R75" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8021,74 +8023,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128784529</v>
+        <v>128790611</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>105682</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723953</v>
+        <v>723942</v>
       </c>
       <c r="R76" t="n">
-        <v>6384442</v>
+        <v>6384482</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8118,75 +8131,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790592</v>
+        <v>128784542</v>
       </c>
       <c r="B77" t="n">
-        <v>86959</v>
+        <v>105682</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723955</v>
+        <v>723833</v>
       </c>
       <c r="R77" t="n">
-        <v>6384283</v>
+        <v>6384211</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8216,85 +8238,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128790597</v>
+        <v>128784510</v>
       </c>
       <c r="B78" t="n">
-        <v>86959</v>
+        <v>86806</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723990</v>
+        <v>723610</v>
       </c>
       <c r="R78" t="n">
-        <v>6384408</v>
+        <v>6384274</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8324,40 +8335,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791643</v>
+        <v>128784519</v>
       </c>
       <c r="B80" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723739</v>
+        <v>723763</v>
       </c>
       <c r="R80" t="n">
-        <v>6384326</v>
+        <v>6384295</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,63 +8551,64 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128785788</v>
+        <v>128790576</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>86959</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723850</v>
+        <v>723628</v>
       </c>
       <c r="R81" t="n">
-        <v>6384251</v>
+        <v>6384239</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8637,74 +8638,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128784519</v>
+        <v>128791643</v>
       </c>
       <c r="B82" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723763</v>
+        <v>723739</v>
       </c>
       <c r="R82" t="n">
-        <v>6384295</v>
+        <v>6384326</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8745,64 +8757,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128790576</v>
+        <v>128785788</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723628</v>
+        <v>723850</v>
       </c>
       <c r="R83" t="n">
-        <v>6384239</v>
+        <v>6384251</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,40 +8843,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8969,7 +8969,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B85" t="n">
         <v>86959</v>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R85" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9067,45 +9067,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B86" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R86" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,64 +9146,63 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B87" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R87" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9244,18 +9243,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
         <v>86806</v>
@@ -9487,14 +9487,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9529,6 +9529,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9541,19 +9546,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
         <v>86806</v>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,12 +9643,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -772,30 +772,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784512</v>
+        <v>128784544</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>107546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6047725</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723641</v>
+        <v>723794</v>
       </c>
       <c r="R3" t="n">
-        <v>6384196</v>
+        <v>6384290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,45 +869,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>86959</v>
+        <v>92808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R4" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -933,50 +933,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784544</v>
+        <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>107546</v>
+        <v>86959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -984,34 +973,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723794</v>
+        <v>723992</v>
       </c>
       <c r="R5" t="n">
-        <v>6384290</v>
+        <v>6384372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,39 +1030,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128790645</v>
+        <v>128791638</v>
       </c>
       <c r="B6" t="n">
-        <v>86806</v>
+        <v>86875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723788</v>
+        <v>723771</v>
       </c>
       <c r="R6" t="n">
-        <v>6384286</v>
+        <v>6384299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,19 +1138,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,22 +1155,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128791638</v>
+        <v>128790645</v>
       </c>
       <c r="B7" t="n">
-        <v>86875</v>
+        <v>86806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1178,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1202,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723771</v>
+        <v>723788</v>
       </c>
       <c r="R7" t="n">
-        <v>6384299</v>
+        <v>6384286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,9 +1235,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,12 +1262,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B11" t="n">
         <v>86760</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R11" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,74 +1646,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R12" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,64 +1765,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R13" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,19 +1851,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,12 +1869,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2168,45 +2168,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790595</v>
+        <v>128784511</v>
       </c>
       <c r="B17" t="n">
-        <v>86959</v>
+        <v>92808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723931</v>
+        <v>723600</v>
       </c>
       <c r="R17" t="n">
-        <v>6384427</v>
+        <v>6384247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,81 +2232,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784511</v>
+        <v>128790595</v>
       </c>
       <c r="B18" t="n">
-        <v>92808</v>
+        <v>86959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723600</v>
+        <v>723931</v>
       </c>
       <c r="R18" t="n">
-        <v>6384247</v>
+        <v>6384427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,29 +2329,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2683,32 +2683,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784553</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>98634</v>
+        <v>86846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219811</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723659</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384257</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790581</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86959</v>
+        <v>98634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723930</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384314</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,72 +2848,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790594</v>
+        <v>128791624</v>
       </c>
       <c r="B24" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723948</v>
+        <v>723724</v>
       </c>
       <c r="R24" t="n">
-        <v>6384417</v>
+        <v>6384209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,40 +2945,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3093,7 +3071,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B26" t="n">
         <v>86875</v>
@@ -3128,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,32 +3168,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B27" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R27" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,74 +3236,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128784550</v>
+        <v>128790594</v>
       </c>
       <c r="B28" t="n">
-        <v>86846</v>
+        <v>86959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723644</v>
+        <v>723948</v>
       </c>
       <c r="R28" t="n">
-        <v>6384278</v>
+        <v>6384417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,29 +3344,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4062,45 +4062,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128784530</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>724024</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384488</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,26 +4141,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128790577</v>
+        <v>128784530</v>
       </c>
       <c r="B37" t="n">
         <v>86959</v>
@@ -4191,14 +4190,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723815</v>
+        <v>724024</v>
       </c>
       <c r="R37" t="n">
-        <v>6384231</v>
+        <v>6384488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,19 +4227,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4256,19 +4245,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128784518</v>
+        <v>128790577</v>
       </c>
       <c r="B38" t="n">
         <v>86959</v>
@@ -4299,14 +4288,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723642</v>
+        <v>723815</v>
       </c>
       <c r="R38" t="n">
-        <v>6384222</v>
+        <v>6384231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,9 +4325,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,57 +4353,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,18 +4444,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791576</v>
+        <v>128791646</v>
       </c>
       <c r="B42" t="n">
-        <v>86806</v>
+        <v>86875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723743</v>
+        <v>723732</v>
       </c>
       <c r="R42" t="n">
-        <v>6384328</v>
+        <v>6384330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791593</v>
+        <v>128790580</v>
       </c>
       <c r="B43" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723736</v>
+        <v>723964</v>
       </c>
       <c r="R43" t="n">
-        <v>6384250</v>
+        <v>6384262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,36 +4819,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B44" t="n">
         <v>86959</v>
@@ -4883,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4918,7 +4929,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4928,7 +4939,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,7 +4967,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790593</v>
+        <v>128790578</v>
       </c>
       <c r="B45" t="n">
         <v>86959</v>
@@ -4991,10 +5002,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723955</v>
+        <v>723890</v>
       </c>
       <c r="R45" t="n">
-        <v>6384354</v>
+        <v>6384224</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,7 +5037,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5036,7 +5047,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790578</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5099,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723890</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384224</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5132,50 +5143,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791646</v>
+        <v>128791576</v>
       </c>
       <c r="B47" t="n">
-        <v>86875</v>
+        <v>86806</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723732</v>
+        <v>723743</v>
       </c>
       <c r="R47" t="n">
-        <v>6384330</v>
+        <v>6384328</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,34 +5561,30 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128791648</v>
+        <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>90965</v>
+        <v>87016</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3286</v>
+        <v>433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5596,10 +5592,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723664</v>
+        <v>723637</v>
       </c>
       <c r="R51" t="n">
-        <v>6384233</v>
+        <v>6384245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,9 +5625,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5646,57 +5652,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784554</v>
+        <v>128791648</v>
       </c>
       <c r="B52" t="n">
-        <v>98634</v>
+        <v>90965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219811</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723982</v>
+        <v>723664</v>
       </c>
       <c r="R52" t="n">
-        <v>6384442</v>
+        <v>6384233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5743,57 +5749,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128790589</v>
+        <v>128784549</v>
       </c>
       <c r="B53" t="n">
-        <v>86959</v>
+        <v>92794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723770</v>
+        <v>723958</v>
       </c>
       <c r="R53" t="n">
-        <v>6384248</v>
+        <v>6384364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5823,50 +5829,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128790629</v>
+        <v>128784539</v>
       </c>
       <c r="B54" t="n">
-        <v>87016</v>
+        <v>91039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,30 +5869,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R54" t="n">
-        <v>6384245</v>
+        <v>6384240</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5927,19 +5926,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5954,57 +5943,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128784549</v>
+        <v>128790589</v>
       </c>
       <c r="B55" t="n">
-        <v>92794</v>
+        <v>86959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723958</v>
+        <v>723770</v>
       </c>
       <c r="R55" t="n">
-        <v>6384364</v>
+        <v>6384248</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6034,61 +6023,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784539</v>
+        <v>128784554</v>
       </c>
       <c r="B56" t="n">
-        <v>91039</v>
+        <v>98634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>219811</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723615</v>
+        <v>723982</v>
       </c>
       <c r="R56" t="n">
-        <v>6384240</v>
+        <v>6384442</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6257,45 +6257,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128790565</v>
+        <v>128784545</v>
       </c>
       <c r="B58" t="n">
-        <v>86784</v>
+        <v>107546</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3712</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723921</v>
+        <v>723768</v>
       </c>
       <c r="R58" t="n">
-        <v>6384444</v>
+        <v>6384301</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,19 +6325,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6352,22 +6342,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784545</v>
+        <v>128784526</v>
       </c>
       <c r="B59" t="n">
-        <v>107546</v>
+        <v>86959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6365,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6389,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723768</v>
+        <v>723962</v>
       </c>
       <c r="R59" t="n">
-        <v>6384301</v>
+        <v>6384357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6443,6 +6433,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6461,32 +6452,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784551</v>
+        <v>128784523</v>
       </c>
       <c r="B60" t="n">
-        <v>98634</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6487,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723631</v>
+        <v>723878</v>
       </c>
       <c r="R60" t="n">
-        <v>6384236</v>
+        <v>6384241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6540,6 +6531,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6558,45 +6550,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784526</v>
+        <v>128790565</v>
       </c>
       <c r="B61" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723962</v>
+        <v>723921</v>
       </c>
       <c r="R61" t="n">
-        <v>6384357</v>
+        <v>6384444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6626,62 +6618,71 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784523</v>
+        <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>86959</v>
+        <v>98634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6691,10 +6692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723878</v>
+        <v>723631</v>
       </c>
       <c r="R62" t="n">
-        <v>6384241</v>
+        <v>6384236</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6735,7 +6736,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128791626</v>
+        <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>86875</v>
+        <v>86806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,34 +7458,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723741</v>
+        <v>723610</v>
       </c>
       <c r="R70" t="n">
-        <v>6384216</v>
+        <v>6384274</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7532,57 +7532,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784529</v>
+        <v>128790555</v>
       </c>
       <c r="B71" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723953</v>
+        <v>723944</v>
       </c>
       <c r="R71" t="n">
-        <v>6384442</v>
+        <v>6384278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,9 +7612,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7630,22 +7640,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790592</v>
+        <v>128785795</v>
       </c>
       <c r="B72" t="n">
-        <v>86959</v>
+        <v>90965</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7653,34 +7663,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723955</v>
+        <v>723789</v>
       </c>
       <c r="R72" t="n">
-        <v>6384283</v>
+        <v>6384213</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7710,72 +7720,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790597</v>
+        <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>86959</v>
+        <v>105682</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7785,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723990</v>
+        <v>723942</v>
       </c>
       <c r="R73" t="n">
-        <v>6384408</v>
+        <v>6384482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7820,7 +7819,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7830,7 +7829,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7839,7 +7838,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7858,45 +7856,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128785795</v>
+        <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>90965</v>
+        <v>105682</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3286</v>
+        <v>224098</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723789</v>
+        <v>723833</v>
       </c>
       <c r="R74" t="n">
-        <v>6384213</v>
+        <v>6384211</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7943,44 +7941,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128790555</v>
+        <v>128791626</v>
       </c>
       <c r="B75" t="n">
-        <v>86760</v>
+        <v>86875</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7990,10 +7988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723944</v>
+        <v>723741</v>
       </c>
       <c r="R75" t="n">
-        <v>6384278</v>
+        <v>6384216</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8023,85 +8021,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128790611</v>
+        <v>128784529</v>
       </c>
       <c r="B76" t="n">
-        <v>105682</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723942</v>
+        <v>723953</v>
       </c>
       <c r="R76" t="n">
-        <v>6384482</v>
+        <v>6384442</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8131,84 +8118,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128784542</v>
+        <v>128790592</v>
       </c>
       <c r="B77" t="n">
-        <v>105682</v>
+        <v>86959</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723833</v>
+        <v>723955</v>
       </c>
       <c r="R77" t="n">
-        <v>6384211</v>
+        <v>6384283</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,74 +8216,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128784510</v>
+        <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723610</v>
+        <v>723990</v>
       </c>
       <c r="R78" t="n">
-        <v>6384274</v>
+        <v>6384408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,29 +8324,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128784519</v>
+        <v>128785788</v>
       </c>
       <c r="B80" t="n">
-        <v>86959</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723763</v>
+        <v>723850</v>
       </c>
       <c r="R80" t="n">
-        <v>6384295</v>
+        <v>6384251</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,51 +8551,50 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128790576</v>
+        <v>128791643</v>
       </c>
       <c r="B81" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8605,10 +8604,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723628</v>
+        <v>723739</v>
       </c>
       <c r="R81" t="n">
-        <v>6384239</v>
+        <v>6384326</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,85 +8637,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791643</v>
+        <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723739</v>
+        <v>723763</v>
       </c>
       <c r="R82" t="n">
-        <v>6384326</v>
+        <v>6384295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8757,63 +8745,64 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128785788</v>
+        <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723850</v>
+        <v>723628</v>
       </c>
       <c r="R83" t="n">
-        <v>6384251</v>
+        <v>6384239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8843,74 +8832,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128784540</v>
+        <v>128791635</v>
       </c>
       <c r="B84" t="n">
-        <v>99385</v>
+        <v>86875</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222361</v>
+        <v>248956</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723956</v>
+        <v>723782</v>
       </c>
       <c r="R84" t="n">
-        <v>6384330</v>
+        <v>6384293</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8957,22 +8957,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784522</v>
+        <v>128784540</v>
       </c>
       <c r="B85" t="n">
-        <v>86959</v>
+        <v>99385</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8980,21 +8980,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>222361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723865</v>
+        <v>723956</v>
       </c>
       <c r="R85" t="n">
-        <v>6384223</v>
+        <v>6384330</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9048,7 +9048,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9067,45 +9066,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B86" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R86" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,25 +9145,26 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B87" t="n">
         <v>86959</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R87" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9262,45 +9262,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86760</v>
+        <v>86806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R88" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86806</v>
+        <v>86760</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R89" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,44 +9444,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791578</v>
+        <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>86806</v>
+        <v>90965</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723775</v>
+        <v>723728</v>
       </c>
       <c r="R90" t="n">
-        <v>6384432</v>
+        <v>6384262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,11 +9527,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9558,7 +9553,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
         <v>86806</v>
@@ -9589,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9631,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791655</v>
+        <v>128784508</v>
       </c>
       <c r="B92" t="n">
-        <v>90965</v>
+        <v>86806</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723728</v>
+        <v>723789</v>
       </c>
       <c r="R92" t="n">
-        <v>6384262</v>
+        <v>6384293</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128784544</v>
       </c>
       <c r="B3" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128791638</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86875</v>
+        <v>86810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723771</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384299</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,9 +1138,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1155,22 +1165,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128790645</v>
+        <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86806</v>
+        <v>86879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1178,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1202,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723788</v>
+        <v>723771</v>
       </c>
       <c r="R7" t="n">
-        <v>6384286</v>
+        <v>6384299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,19 +1245,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,12 +1262,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
         <v>128785784</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128784517</v>
       </c>
       <c r="B9" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128790554</v>
       </c>
       <c r="B11" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,41 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791663</v>
+        <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>87016</v>
+        <v>88698</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>433</v>
+        <v>4379</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723971</v>
+        <v>723922</v>
       </c>
       <c r="R14" t="n">
-        <v>6384460</v>
+        <v>6384266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,22 +1966,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784509</v>
+        <v>128791663</v>
       </c>
       <c r="B15" t="n">
-        <v>86806</v>
+        <v>87020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,34 +1989,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723618</v>
+        <v>723971</v>
       </c>
       <c r="R15" t="n">
-        <v>6384286</v>
+        <v>6384460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,44 +2059,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784506</v>
+        <v>128784509</v>
       </c>
       <c r="B16" t="n">
-        <v>88694</v>
+        <v>86810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4379</v>
+        <v>424</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723922</v>
+        <v>723618</v>
       </c>
       <c r="R16" t="n">
-        <v>6384266</v>
+        <v>6384286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,41 +2168,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128784511</v>
+        <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>92808</v>
+        <v>86963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723600</v>
+        <v>723931</v>
       </c>
       <c r="R17" t="n">
-        <v>6384247</v>
+        <v>6384427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,74 +2236,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790595</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>86959</v>
+        <v>92812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723931</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384427</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,40 +2340,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
         <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,32 +2683,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128784553</v>
       </c>
       <c r="B22" t="n">
-        <v>86846</v>
+        <v>98638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>219811</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723659</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384257</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128791624</v>
       </c>
       <c r="B23" t="n">
-        <v>98634</v>
+        <v>86879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723724</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,22 +2865,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791624</v>
+        <v>128791633</v>
       </c>
       <c r="B24" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723724</v>
+        <v>723767</v>
       </c>
       <c r="R24" t="n">
-        <v>6384209</v>
+        <v>6384282</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791633</v>
+        <v>128791629</v>
       </c>
       <c r="B25" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723767</v>
+        <v>723745</v>
       </c>
       <c r="R25" t="n">
-        <v>6384282</v>
+        <v>6384273</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,32 +3071,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B26" t="n">
-        <v>86875</v>
+        <v>86963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R26" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3139,39 +3139,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790581</v>
+        <v>128790594</v>
       </c>
       <c r="B27" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723930</v>
+        <v>723948</v>
       </c>
       <c r="R27" t="n">
-        <v>6384314</v>
+        <v>6384417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,7 +3249,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3248,7 +3259,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,45 +3287,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790594</v>
+        <v>128784550</v>
       </c>
       <c r="B28" t="n">
-        <v>86959</v>
+        <v>86850</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723948</v>
+        <v>723644</v>
       </c>
       <c r="R28" t="n">
-        <v>6384417</v>
+        <v>6384278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,40 +3355,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>128785781</v>
       </c>
       <c r="B30" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3681,41 +3681,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785780</v>
+        <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>92808</v>
+        <v>86879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723935</v>
+        <v>723745</v>
       </c>
       <c r="R32" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,64 +3760,59 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791642</v>
+        <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>86875</v>
+        <v>92812</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723745</v>
+        <v>723935</v>
       </c>
       <c r="R33" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,18 +3853,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
         <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B40" t="n">
-        <v>86760</v>
+        <v>92812</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,34 +4474,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R40" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,28 +4538,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B41" t="n">
-        <v>92808</v>
+        <v>86764</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,30 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R41" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,29 +4636,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791646</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86875</v>
+        <v>86810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723732</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384330</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790580</v>
+        <v>128791593</v>
       </c>
       <c r="B43" t="n">
-        <v>86959</v>
+        <v>86764</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723964</v>
+        <v>723736</v>
       </c>
       <c r="R43" t="n">
-        <v>6384262</v>
+        <v>6384250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,72 +4819,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790593</v>
+        <v>128791646</v>
       </c>
       <c r="B44" t="n">
-        <v>86959</v>
+        <v>86879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723955</v>
+        <v>723732</v>
       </c>
       <c r="R44" t="n">
-        <v>6384354</v>
+        <v>6384330</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4927,50 +4916,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790578</v>
+        <v>128790580</v>
       </c>
       <c r="B45" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723890</v>
+        <v>723964</v>
       </c>
       <c r="R45" t="n">
-        <v>6384224</v>
+        <v>6384262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5037,7 +5015,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5047,7 +5025,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791593</v>
+        <v>128790593</v>
       </c>
       <c r="B46" t="n">
-        <v>86760</v>
+        <v>86963</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723736</v>
+        <v>723955</v>
       </c>
       <c r="R46" t="n">
-        <v>6384250</v>
+        <v>6384354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,61 +5121,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791576</v>
+        <v>128790578</v>
       </c>
       <c r="B47" t="n">
-        <v>86806</v>
+        <v>86963</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5196,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723743</v>
+        <v>723890</v>
       </c>
       <c r="R47" t="n">
-        <v>6384328</v>
+        <v>6384224</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5240,74 +5229,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128791574</v>
+        <v>128784521</v>
       </c>
       <c r="B48" t="n">
-        <v>86806</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723611</v>
+        <v>723955</v>
       </c>
       <c r="R48" t="n">
-        <v>6384260</v>
+        <v>6384252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5348,18 +5348,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5369,7 +5370,7 @@
         <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5463,45 +5464,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128784521</v>
+        <v>128791574</v>
       </c>
       <c r="B50" t="n">
-        <v>86959</v>
+        <v>86810</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723955</v>
+        <v>723611</v>
       </c>
       <c r="R50" t="n">
-        <v>6384252</v>
+        <v>6384260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5542,19 +5543,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
         <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5664,45 +5664,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128791648</v>
+        <v>128784539</v>
       </c>
       <c r="B52" t="n">
-        <v>90965</v>
+        <v>91043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723664</v>
+        <v>723615</v>
       </c>
       <c r="R52" t="n">
-        <v>6384233</v>
+        <v>6384240</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5749,57 +5749,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784549</v>
+        <v>128791648</v>
       </c>
       <c r="B53" t="n">
-        <v>92794</v>
+        <v>90969</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>3286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723958</v>
+        <v>723664</v>
       </c>
       <c r="R53" t="n">
-        <v>6384364</v>
+        <v>6384233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,44 +5846,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784539</v>
+        <v>128784549</v>
       </c>
       <c r="B54" t="n">
-        <v>91039</v>
+        <v>92798</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723615</v>
+        <v>723958</v>
       </c>
       <c r="R54" t="n">
-        <v>6384240</v>
+        <v>6384364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,45 +5955,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128790589</v>
+        <v>128784554</v>
       </c>
       <c r="B55" t="n">
-        <v>86959</v>
+        <v>98638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723770</v>
+        <v>723982</v>
       </c>
       <c r="R55" t="n">
-        <v>6384248</v>
+        <v>6384442</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6023,85 +6023,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784554</v>
+        <v>128790589</v>
       </c>
       <c r="B56" t="n">
-        <v>98634</v>
+        <v>86963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723982</v>
+        <v>723770</v>
       </c>
       <c r="R56" t="n">
-        <v>6384442</v>
+        <v>6384248</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6131,74 +6120,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128785778</v>
+        <v>128790565</v>
       </c>
       <c r="B57" t="n">
-        <v>86806</v>
+        <v>86788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723760</v>
+        <v>723921</v>
       </c>
       <c r="R57" t="n">
-        <v>6384211</v>
+        <v>6384444</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,9 +6228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6245,57 +6255,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784545</v>
+        <v>128785778</v>
       </c>
       <c r="B58" t="n">
-        <v>107546</v>
+        <v>86810</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>424</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723768</v>
+        <v>723760</v>
       </c>
       <c r="R58" t="n">
-        <v>6384301</v>
+        <v>6384211</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6342,44 +6352,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784526</v>
+        <v>128784551</v>
       </c>
       <c r="B59" t="n">
-        <v>86959</v>
+        <v>98638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6389,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723962</v>
+        <v>723631</v>
       </c>
       <c r="R59" t="n">
-        <v>6384357</v>
+        <v>6384236</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,7 +6443,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6452,10 +6461,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784523</v>
+        <v>128784545</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>107550</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6463,21 +6472,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6487,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723878</v>
+        <v>723768</v>
       </c>
       <c r="R60" t="n">
-        <v>6384241</v>
+        <v>6384301</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6531,7 +6540,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6550,45 +6558,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128790565</v>
+        <v>128784526</v>
       </c>
       <c r="B61" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723921</v>
+        <v>723962</v>
       </c>
       <c r="R61" t="n">
-        <v>6384444</v>
+        <v>6384357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,71 +6626,62 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784551</v>
+        <v>128784523</v>
       </c>
       <c r="B62" t="n">
-        <v>98634</v>
+        <v>86963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6692,10 +6691,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723631</v>
+        <v>723878</v>
       </c>
       <c r="R62" t="n">
-        <v>6384236</v>
+        <v>6384241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6736,6 +6735,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128785779</v>
+        <v>128784516</v>
       </c>
       <c r="B63" t="n">
-        <v>86806</v>
+        <v>86963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723790</v>
+        <v>723922</v>
       </c>
       <c r="R63" t="n">
-        <v>6384287</v>
+        <v>6384267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6833,18 +6833,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6854,7 +6855,7 @@
         <v>128790556</v>
       </c>
       <c r="B64" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6961,7 +6962,7 @@
         <v>128791601</v>
       </c>
       <c r="B65" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7055,45 +7056,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128784525</v>
+        <v>128785779</v>
       </c>
       <c r="B66" t="n">
-        <v>86959</v>
+        <v>86810</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723945</v>
+        <v>723790</v>
       </c>
       <c r="R66" t="n">
-        <v>6384300</v>
+        <v>6384287</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7134,29 +7135,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128784516</v>
+        <v>128784527</v>
       </c>
       <c r="B67" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723922</v>
+        <v>723949</v>
       </c>
       <c r="R67" t="n">
-        <v>6384267</v>
+        <v>6384442</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7251,10 +7251,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128784527</v>
+        <v>128784525</v>
       </c>
       <c r="B68" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723949</v>
+        <v>723945</v>
       </c>
       <c r="R68" t="n">
-        <v>6384442</v>
+        <v>6384300</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7352,7 +7352,7 @@
         <v>128785782</v>
       </c>
       <c r="B69" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128784510</v>
+        <v>128785795</v>
       </c>
       <c r="B70" t="n">
-        <v>86806</v>
+        <v>90969</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723610</v>
+        <v>723789</v>
       </c>
       <c r="R70" t="n">
-        <v>6384274</v>
+        <v>6384213</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7532,57 +7532,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128790555</v>
+        <v>128784510</v>
       </c>
       <c r="B71" t="n">
-        <v>86760</v>
+        <v>86810</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723944</v>
+        <v>723610</v>
       </c>
       <c r="R71" t="n">
-        <v>6384278</v>
+        <v>6384274</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,85 +7612,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785795</v>
+        <v>128790555</v>
       </c>
       <c r="B72" t="n">
-        <v>90965</v>
+        <v>86764</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723789</v>
+        <v>723944</v>
       </c>
       <c r="R72" t="n">
-        <v>6384213</v>
+        <v>6384278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,39 +7709,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790611</v>
+        <v>128784542</v>
       </c>
       <c r="B73" t="n">
-        <v>105682</v>
+        <v>105686</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7780,14 +7780,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723942</v>
+        <v>723833</v>
       </c>
       <c r="R73" t="n">
-        <v>6384482</v>
+        <v>6384211</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,19 +7817,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7844,22 +7834,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128784542</v>
+        <v>128790611</v>
       </c>
       <c r="B74" t="n">
-        <v>105682</v>
+        <v>105686</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7887,14 +7877,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723833</v>
+        <v>723942</v>
       </c>
       <c r="R74" t="n">
-        <v>6384211</v>
+        <v>6384482</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7924,9 +7914,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7941,12 +7941,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
         <v>128791626</v>
       </c>
       <c r="B75" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>128784529</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>128790592</v>
       </c>
       <c r="B77" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>128791643</v>
       </c>
       <c r="B81" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8872,45 +8872,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791635</v>
+        <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>86875</v>
+        <v>99389</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>248956</v>
+        <v>222361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723782</v>
+        <v>723956</v>
       </c>
       <c r="R84" t="n">
-        <v>6384293</v>
+        <v>6384330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8957,57 +8957,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784540</v>
+        <v>128791635</v>
       </c>
       <c r="B85" t="n">
-        <v>99385</v>
+        <v>86879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222361</v>
+        <v>248956</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723956</v>
+        <v>723782</v>
       </c>
       <c r="R85" t="n">
-        <v>6384330</v>
+        <v>6384293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9054,12 +9054,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9069,7 +9069,7 @@
         <v>128784524</v>
       </c>
       <c r="B86" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>128784522</v>
       </c>
       <c r="B87" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9456,32 +9456,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791655</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
-        <v>90965</v>
+        <v>86810</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723728</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384262</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,6 +9527,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9553,10 +9558,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784508</v>
+        <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>86806</v>
+        <v>90969</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723789</v>
+        <v>723728</v>
       </c>
       <c r="R92" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
         <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87153</v>
+        <v>87157</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>90271</v>
+        <v>90275</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86925</v>
+        <v>86929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86925</v>
+        <v>86929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128790645</v>
+        <v>128791638</v>
       </c>
       <c r="B6" t="n">
-        <v>86810</v>
+        <v>86879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723788</v>
+        <v>723771</v>
       </c>
       <c r="R6" t="n">
-        <v>6384286</v>
+        <v>6384299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,19 +1138,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,22 +1155,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128791638</v>
+        <v>128790645</v>
       </c>
       <c r="B7" t="n">
-        <v>86879</v>
+        <v>86810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1178,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1202,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723771</v>
+        <v>723788</v>
       </c>
       <c r="R7" t="n">
-        <v>6384299</v>
+        <v>6384286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,9 +1235,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,12 +1262,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1881,45 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128784506</v>
+        <v>128790595</v>
       </c>
       <c r="B14" t="n">
-        <v>88698</v>
+        <v>86963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723922</v>
+        <v>723931</v>
       </c>
       <c r="R14" t="n">
-        <v>6384266</v>
+        <v>6384427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,70 +1949,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128791663</v>
+        <v>128784511</v>
       </c>
       <c r="B15" t="n">
-        <v>87020</v>
+        <v>92812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723971</v>
+        <v>723600</v>
       </c>
       <c r="R15" t="n">
-        <v>6384460</v>
+        <v>6384247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,57 +2070,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784509</v>
+        <v>128790583</v>
       </c>
       <c r="B16" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723618</v>
+        <v>723986</v>
       </c>
       <c r="R16" t="n">
-        <v>6384286</v>
+        <v>6384358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,74 +2150,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790595</v>
+        <v>128784506</v>
       </c>
       <c r="B17" t="n">
-        <v>86963</v>
+        <v>88698</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723931</v>
+        <v>723922</v>
       </c>
       <c r="R17" t="n">
-        <v>6384427</v>
+        <v>6384266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,81 +2258,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784511</v>
+        <v>128791663</v>
       </c>
       <c r="B18" t="n">
-        <v>92812</v>
+        <v>87020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723600</v>
+        <v>723971</v>
       </c>
       <c r="R18" t="n">
-        <v>6384247</v>
+        <v>6384460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,57 +2368,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790583</v>
+        <v>128784509</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723986</v>
+        <v>723618</v>
       </c>
       <c r="R19" t="n">
-        <v>6384358</v>
+        <v>6384286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,40 +2448,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2683,32 +2683,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784553</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>98638</v>
+        <v>86850</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219811</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723659</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384257</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791624</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86879</v>
+        <v>98638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723724</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384209</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,12 +2865,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2974,32 +2974,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B25" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R25" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,61 +3042,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790581</v>
+        <v>128791629</v>
       </c>
       <c r="B26" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3106,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723930</v>
+        <v>723745</v>
       </c>
       <c r="R26" t="n">
-        <v>6384314</v>
+        <v>6384273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3139,40 +3150,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128784550</v>
+        <v>128791624</v>
       </c>
       <c r="B28" t="n">
-        <v>86850</v>
+        <v>86879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,34 +3298,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723644</v>
+        <v>723724</v>
       </c>
       <c r="R28" t="n">
-        <v>6384278</v>
+        <v>6384209</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,53 +3372,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>87020</v>
+        <v>86764</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R29" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,19 +3452,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,19 +3469,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128791591</v>
       </c>
       <c r="B30" t="n">
         <v>86764</v>
@@ -3518,14 +3512,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723617</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,44 +3566,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128791642</v>
       </c>
       <c r="B31" t="n">
-        <v>86764</v>
+        <v>86879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3619,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723745</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3681,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128791642</v>
+        <v>128790627</v>
       </c>
       <c r="B32" t="n">
-        <v>86879</v>
+        <v>87020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,23 +3686,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3716,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723745</v>
+        <v>723660</v>
       </c>
       <c r="R32" t="n">
-        <v>6384321</v>
+        <v>6384309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3749,9 +3739,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3766,12 +3766,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3872,41 +3872,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128791566</v>
+        <v>128784530</v>
       </c>
       <c r="B34" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723725</v>
+        <v>724024</v>
       </c>
       <c r="R34" t="n">
-        <v>6384258</v>
+        <v>6384488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3947,63 +3951,64 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128785776</v>
+        <v>128790577</v>
       </c>
       <c r="B35" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723727</v>
+        <v>723815</v>
       </c>
       <c r="R35" t="n">
-        <v>6384228</v>
+        <v>6384231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4033,74 +4038,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B36" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R36" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,63 +4157,60 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128784530</v>
+        <v>128791566</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>87020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>724024</v>
+        <v>723725</v>
       </c>
       <c r="R37" t="n">
-        <v>6384488</v>
+        <v>6384258</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4238,64 +4251,63 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128790577</v>
+        <v>128785776</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723815</v>
+        <v>723727</v>
       </c>
       <c r="R38" t="n">
-        <v>6384231</v>
+        <v>6384228</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,85 +4337,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R39" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,29 +4445,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>92812</v>
+        <v>86764</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,30 +4474,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R40" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,29 +4542,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>86764</v>
+        <v>92812</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4571,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R41" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4636,18 +4635,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4848,32 +4848,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128791646</v>
+        <v>128790580</v>
       </c>
       <c r="B44" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723732</v>
+        <v>723964</v>
       </c>
       <c r="R44" t="n">
-        <v>6384330</v>
+        <v>6384262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,36 +4916,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B45" t="n">
         <v>86963</v>
@@ -4980,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R45" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5015,7 +5026,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5025,7 +5036,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,7 +5064,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790593</v>
+        <v>128790578</v>
       </c>
       <c r="B46" t="n">
         <v>86963</v>
@@ -5088,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723955</v>
+        <v>723890</v>
       </c>
       <c r="R46" t="n">
-        <v>6384354</v>
+        <v>6384224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5123,7 +5134,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5133,7 +5144,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128790578</v>
+        <v>128791646</v>
       </c>
       <c r="B47" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723890</v>
+        <v>723732</v>
       </c>
       <c r="R47" t="n">
-        <v>6384224</v>
+        <v>6384330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5229,85 +5240,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784521</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723955</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384252</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5348,19 +5348,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5457,52 +5456,52 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128791574</v>
+        <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723611</v>
+        <v>723955</v>
       </c>
       <c r="R50" t="n">
-        <v>6384260</v>
+        <v>6384252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,28 +5542,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128790629</v>
+        <v>128784539</v>
       </c>
       <c r="B51" t="n">
-        <v>87020</v>
+        <v>91043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5572,30 +5572,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R51" t="n">
-        <v>6384245</v>
+        <v>6384240</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5625,19 +5629,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5652,22 +5646,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784539</v>
+        <v>128790629</v>
       </c>
       <c r="B52" t="n">
-        <v>91043</v>
+        <v>87020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5675,34 +5669,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>433</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723615</v>
+        <v>723637</v>
       </c>
       <c r="R52" t="n">
-        <v>6384240</v>
+        <v>6384245</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5732,9 +5722,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5749,57 +5749,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128791648</v>
+        <v>128784549</v>
       </c>
       <c r="B53" t="n">
-        <v>90969</v>
+        <v>92798</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3286</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723664</v>
+        <v>723958</v>
       </c>
       <c r="R53" t="n">
-        <v>6384233</v>
+        <v>6384364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,57 +5846,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784549</v>
+        <v>128791648</v>
       </c>
       <c r="B54" t="n">
-        <v>92798</v>
+        <v>90969</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>3286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723958</v>
+        <v>723664</v>
       </c>
       <c r="R54" t="n">
-        <v>6384364</v>
+        <v>6384233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5943,12 +5943,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128790565</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86788</v>
+        <v>86810</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723921</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384444</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,19 +6228,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6255,57 +6245,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128785778</v>
+        <v>128784545</v>
       </c>
       <c r="B58" t="n">
-        <v>86810</v>
+        <v>107550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>424</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723760</v>
+        <v>723768</v>
       </c>
       <c r="R58" t="n">
-        <v>6384211</v>
+        <v>6384301</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,12 +6342,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6461,10 +6451,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784545</v>
+        <v>128784523</v>
       </c>
       <c r="B60" t="n">
-        <v>107550</v>
+        <v>86963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6472,21 +6462,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723768</v>
+        <v>723878</v>
       </c>
       <c r="R60" t="n">
-        <v>6384301</v>
+        <v>6384241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6540,6 +6530,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6558,45 +6549,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784526</v>
+        <v>128790565</v>
       </c>
       <c r="B61" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723962</v>
+        <v>723921</v>
       </c>
       <c r="R61" t="n">
-        <v>6384357</v>
+        <v>6384444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6626,37 +6617,46 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784523</v>
+        <v>128784526</v>
       </c>
       <c r="B62" t="n">
         <v>86963</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723878</v>
+        <v>723962</v>
       </c>
       <c r="R62" t="n">
-        <v>6384241</v>
+        <v>6384357</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128784516</v>
+        <v>128785779</v>
       </c>
       <c r="B63" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723922</v>
+        <v>723790</v>
       </c>
       <c r="R63" t="n">
-        <v>6384267</v>
+        <v>6384287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6833,19 +6833,18 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7056,45 +7055,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128785779</v>
+        <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723790</v>
+        <v>723945</v>
       </c>
       <c r="R66" t="n">
-        <v>6384287</v>
+        <v>6384300</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7135,25 +7134,26 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128784527</v>
+        <v>128784516</v>
       </c>
       <c r="B67" t="n">
         <v>86963</v>
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723949</v>
+        <v>723922</v>
       </c>
       <c r="R67" t="n">
-        <v>6384442</v>
+        <v>6384267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7251,7 +7251,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128784525</v>
+        <v>128784527</v>
       </c>
       <c r="B68" t="n">
         <v>86963</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723945</v>
+        <v>723949</v>
       </c>
       <c r="R68" t="n">
-        <v>6384300</v>
+        <v>6384442</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128785795</v>
+        <v>128790555</v>
       </c>
       <c r="B70" t="n">
-        <v>90969</v>
+        <v>86764</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723789</v>
+        <v>723944</v>
       </c>
       <c r="R70" t="n">
-        <v>6384213</v>
+        <v>6384278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,74 +7515,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784510</v>
+        <v>128785795</v>
       </c>
       <c r="B71" t="n">
-        <v>86810</v>
+        <v>90969</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723610</v>
+        <v>723789</v>
       </c>
       <c r="R71" t="n">
-        <v>6384274</v>
+        <v>6384213</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7629,57 +7640,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790555</v>
+        <v>128784529</v>
       </c>
       <c r="B72" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723944</v>
+        <v>723953</v>
       </c>
       <c r="R72" t="n">
-        <v>6384278</v>
+        <v>6384442</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,19 +7720,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7737,57 +7738,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128784542</v>
+        <v>128790592</v>
       </c>
       <c r="B73" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723833</v>
+        <v>723955</v>
       </c>
       <c r="R73" t="n">
-        <v>6384211</v>
+        <v>6384283</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,61 +7818,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128790611</v>
+        <v>128790597</v>
       </c>
       <c r="B74" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7881,10 +7893,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723942</v>
+        <v>723990</v>
       </c>
       <c r="R74" t="n">
-        <v>6384482</v>
+        <v>6384408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7916,7 +7928,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7926,7 +7938,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7935,6 +7947,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7953,10 +7966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791626</v>
+        <v>128784510</v>
       </c>
       <c r="B75" t="n">
-        <v>86879</v>
+        <v>86810</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7964,34 +7977,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723741</v>
+        <v>723610</v>
       </c>
       <c r="R75" t="n">
-        <v>6384216</v>
+        <v>6384274</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8038,57 +8051,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128784529</v>
+        <v>128790611</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723953</v>
+        <v>723942</v>
       </c>
       <c r="R76" t="n">
-        <v>6384442</v>
+        <v>6384482</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8118,75 +8131,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790592</v>
+        <v>128784542</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723955</v>
+        <v>723833</v>
       </c>
       <c r="R77" t="n">
-        <v>6384283</v>
+        <v>6384211</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8216,72 +8238,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B78" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8291,10 +8302,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R78" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8324,40 +8335,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8569,45 +8569,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791643</v>
+        <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723739</v>
+        <v>723763</v>
       </c>
       <c r="R81" t="n">
-        <v>6384326</v>
+        <v>6384295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,25 +8648,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128784519</v>
+        <v>128790576</v>
       </c>
       <c r="B82" t="n">
         <v>86963</v>
@@ -8697,14 +8698,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723763</v>
+        <v>723628</v>
       </c>
       <c r="R82" t="n">
-        <v>6384295</v>
+        <v>6384239</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8734,9 +8735,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8752,44 +8763,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128790576</v>
+        <v>128791643</v>
       </c>
       <c r="B83" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8799,10 +8810,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723628</v>
+        <v>723739</v>
       </c>
       <c r="R83" t="n">
-        <v>6384239</v>
+        <v>6384326</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,40 +8843,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8969,45 +8969,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R85" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9048,25 +9048,26 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B86" t="n">
         <v>86963</v>
@@ -9101,10 +9102,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R86" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9164,45 +9165,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R87" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9243,19 +9244,18 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B90" t="n">
         <v>86810</v>
@@ -9487,14 +9487,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R90" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9529,11 +9529,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9546,19 +9541,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
         <v>86810</v>
@@ -9589,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9631,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,12 +9643,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -772,34 +772,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784544</v>
+        <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>107550</v>
+        <v>92812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>6047725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723794</v>
+        <v>723641</v>
       </c>
       <c r="R3" t="n">
-        <v>6384290</v>
+        <v>6384196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,41 +865,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B4" t="n">
-        <v>92812</v>
+        <v>86963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R4" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -933,39 +933,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128790598</v>
+        <v>128784544</v>
       </c>
       <c r="B5" t="n">
-        <v>86963</v>
+        <v>107550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,34 +984,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723992</v>
+        <v>723794</v>
       </c>
       <c r="R5" t="n">
-        <v>6384372</v>
+        <v>6384290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1030,50 +1041,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128791638</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86879</v>
+        <v>86810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723771</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384299</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,9 +1138,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1155,57 +1165,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128790645</v>
+        <v>128785784</v>
       </c>
       <c r="B7" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723788</v>
+        <v>723969</v>
       </c>
       <c r="R7" t="n">
-        <v>6384286</v>
+        <v>6384430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,46 +1245,37 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128785784</v>
+        <v>128784517</v>
       </c>
       <c r="B8" t="n">
         <v>86963</v>
@@ -1305,14 +1306,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723969</v>
+        <v>723612</v>
       </c>
       <c r="R8" t="n">
-        <v>6384430</v>
+        <v>6384274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,19 +1361,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128784517</v>
+        <v>128790574</v>
       </c>
       <c r="B9" t="n">
         <v>86963</v>
@@ -1403,14 +1404,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723612</v>
+        <v>723609</v>
       </c>
       <c r="R9" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,9 +1441,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1458,44 +1469,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790574</v>
+        <v>128791638</v>
       </c>
       <c r="B10" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723609</v>
+        <v>723771</v>
       </c>
       <c r="R10" t="n">
-        <v>6384278</v>
+        <v>6384299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,40 +1549,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1881,45 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790595</v>
+        <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>86963</v>
+        <v>88698</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723931</v>
+        <v>723922</v>
       </c>
       <c r="R14" t="n">
-        <v>6384427</v>
+        <v>6384266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,81 +1949,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784511</v>
+        <v>128790595</v>
       </c>
       <c r="B15" t="n">
-        <v>92812</v>
+        <v>86963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723600</v>
+        <v>723931</v>
       </c>
       <c r="R15" t="n">
-        <v>6384247</v>
+        <v>6384427</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,74 +2046,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790583</v>
+        <v>128784511</v>
       </c>
       <c r="B16" t="n">
-        <v>86963</v>
+        <v>92812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723986</v>
+        <v>723600</v>
       </c>
       <c r="R16" t="n">
-        <v>6384358</v>
+        <v>6384247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,85 +2150,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128784506</v>
+        <v>128790583</v>
       </c>
       <c r="B17" t="n">
-        <v>88698</v>
+        <v>86963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723922</v>
+        <v>723986</v>
       </c>
       <c r="R17" t="n">
-        <v>6384266</v>
+        <v>6384358</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,29 +2247,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2683,45 +2683,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128790581</v>
       </c>
       <c r="B22" t="n">
-        <v>86850</v>
+        <v>86963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723930</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,74 +2751,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128790594</v>
       </c>
       <c r="B23" t="n">
-        <v>98638</v>
+        <v>86963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723948</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,74 +2859,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791633</v>
+        <v>128784553</v>
       </c>
       <c r="B24" t="n">
-        <v>86879</v>
+        <v>98638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723767</v>
+        <v>723659</v>
       </c>
       <c r="R24" t="n">
-        <v>6384282</v>
+        <v>6384257</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,57 +2984,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790581</v>
+        <v>128784550</v>
       </c>
       <c r="B25" t="n">
-        <v>86963</v>
+        <v>86850</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723930</v>
+        <v>723644</v>
       </c>
       <c r="R25" t="n">
-        <v>6384314</v>
+        <v>6384278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,47 +3064,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791629</v>
+        <v>128791624</v>
       </c>
       <c r="B26" t="n">
         <v>86879</v>
@@ -3117,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723745</v>
+        <v>723724</v>
       </c>
       <c r="R26" t="n">
-        <v>6384273</v>
+        <v>6384209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,32 +3190,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790594</v>
+        <v>128791633</v>
       </c>
       <c r="B27" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723948</v>
+        <v>723767</v>
       </c>
       <c r="R27" t="n">
-        <v>6384417</v>
+        <v>6384282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,47 +3258,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B28" t="n">
         <v>86879</v>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R28" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785781</v>
+        <v>128785780</v>
       </c>
       <c r="B29" t="n">
-        <v>86764</v>
+        <v>92812</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,23 +3395,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3419,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723744</v>
+        <v>723935</v>
       </c>
       <c r="R29" t="n">
-        <v>6384205</v>
+        <v>6384247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,6 +3459,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3481,7 +3478,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
         <v>86764</v>
@@ -3512,14 +3509,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,44 +3563,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791642</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>86879</v>
+        <v>86764</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3610,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723745</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3778,41 +3775,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785780</v>
+        <v>128791642</v>
       </c>
       <c r="B33" t="n">
-        <v>92812</v>
+        <v>86879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723935</v>
+        <v>723745</v>
       </c>
       <c r="R33" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3853,64 +3854,59 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128784530</v>
+        <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>86963</v>
+        <v>87020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>724024</v>
+        <v>723725</v>
       </c>
       <c r="R34" t="n">
-        <v>6384488</v>
+        <v>6384258</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,64 +3947,63 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790577</v>
+        <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723815</v>
+        <v>723727</v>
       </c>
       <c r="R35" t="n">
-        <v>6384231</v>
+        <v>6384228</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,85 +4033,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4157,60 +4141,63 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128791566</v>
+        <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723725</v>
+        <v>724024</v>
       </c>
       <c r="R37" t="n">
-        <v>6384258</v>
+        <v>6384488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4251,63 +4238,64 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128785776</v>
+        <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723727</v>
+        <v>723815</v>
       </c>
       <c r="R38" t="n">
-        <v>6384228</v>
+        <v>6384231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4337,74 +4325,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,18 +4444,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791576</v>
+        <v>128791593</v>
       </c>
       <c r="B42" t="n">
-        <v>86810</v>
+        <v>86764</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723743</v>
+        <v>723736</v>
       </c>
       <c r="R42" t="n">
-        <v>6384328</v>
+        <v>6384250</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B43" t="n">
-        <v>86764</v>
+        <v>86810</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R43" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5269,45 +5269,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128791574</v>
+        <v>128784521</v>
       </c>
       <c r="B48" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723611</v>
+        <v>723955</v>
       </c>
       <c r="R48" t="n">
-        <v>6384260</v>
+        <v>6384252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5348,18 +5348,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5456,52 +5457,52 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128784521</v>
+        <v>128791574</v>
       </c>
       <c r="B50" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723955</v>
+        <v>723611</v>
       </c>
       <c r="R50" t="n">
-        <v>6384252</v>
+        <v>6384260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5542,64 +5543,63 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784539</v>
+        <v>128790589</v>
       </c>
       <c r="B51" t="n">
-        <v>91043</v>
+        <v>86963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723615</v>
+        <v>723770</v>
       </c>
       <c r="R51" t="n">
-        <v>6384240</v>
+        <v>6384248</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,70 +5629,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128790629</v>
+        <v>128784554</v>
       </c>
       <c r="B52" t="n">
-        <v>87020</v>
+        <v>98638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723637</v>
+        <v>723982</v>
       </c>
       <c r="R52" t="n">
-        <v>6384245</v>
+        <v>6384442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,19 +5737,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5749,44 +5754,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784549</v>
+        <v>128784539</v>
       </c>
       <c r="B53" t="n">
-        <v>92798</v>
+        <v>91043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5796,10 +5801,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723958</v>
+        <v>723615</v>
       </c>
       <c r="R53" t="n">
-        <v>6384364</v>
+        <v>6384240</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5955,45 +5960,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128784554</v>
+        <v>128790629</v>
       </c>
       <c r="B55" t="n">
-        <v>98638</v>
+        <v>87020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723982</v>
+        <v>723637</v>
       </c>
       <c r="R55" t="n">
-        <v>6384442</v>
+        <v>6384245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6023,9 +6024,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6040,57 +6051,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128790589</v>
+        <v>128784549</v>
       </c>
       <c r="B56" t="n">
-        <v>86963</v>
+        <v>92798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723770</v>
+        <v>723958</v>
       </c>
       <c r="R56" t="n">
-        <v>6384248</v>
+        <v>6384364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6120,85 +6131,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128785778</v>
+        <v>128790565</v>
       </c>
       <c r="B57" t="n">
-        <v>86810</v>
+        <v>86788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723760</v>
+        <v>723921</v>
       </c>
       <c r="R57" t="n">
-        <v>6384211</v>
+        <v>6384444</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,9 +6228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6245,22 +6255,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784545</v>
+        <v>128784526</v>
       </c>
       <c r="B58" t="n">
-        <v>107550</v>
+        <v>86963</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6268,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6292,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723768</v>
+        <v>723962</v>
       </c>
       <c r="R58" t="n">
-        <v>6384301</v>
+        <v>6384357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6336,6 +6346,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6354,32 +6365,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784551</v>
+        <v>128784523</v>
       </c>
       <c r="B59" t="n">
-        <v>98638</v>
+        <v>86963</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6389,10 +6400,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723631</v>
+        <v>723878</v>
       </c>
       <c r="R59" t="n">
-        <v>6384236</v>
+        <v>6384241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,6 +6444,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6451,10 +6463,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784523</v>
+        <v>128784545</v>
       </c>
       <c r="B60" t="n">
-        <v>86963</v>
+        <v>107550</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6462,21 +6474,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6486,10 +6498,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723878</v>
+        <v>723768</v>
       </c>
       <c r="R60" t="n">
-        <v>6384241</v>
+        <v>6384301</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,7 +6542,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6549,10 +6560,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128790565</v>
+        <v>128784551</v>
       </c>
       <c r="B61" t="n">
-        <v>86788</v>
+        <v>98638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6560,34 +6571,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3712</v>
+        <v>219811</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723921</v>
+        <v>723631</v>
       </c>
       <c r="R61" t="n">
-        <v>6384444</v>
+        <v>6384236</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6617,19 +6628,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6644,57 +6645,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784526</v>
+        <v>128785778</v>
       </c>
       <c r="B62" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723962</v>
+        <v>723760</v>
       </c>
       <c r="R62" t="n">
-        <v>6384357</v>
+        <v>6384211</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6735,64 +6736,63 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128785779</v>
+        <v>128791601</v>
       </c>
       <c r="B63" t="n">
-        <v>86810</v>
+        <v>86764</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723790</v>
+        <v>723723</v>
       </c>
       <c r="R63" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6839,12 +6839,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6958,45 +6958,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791601</v>
+        <v>128785779</v>
       </c>
       <c r="B65" t="n">
-        <v>86764</v>
+        <v>86810</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723723</v>
+        <v>723790</v>
       </c>
       <c r="R65" t="n">
-        <v>6384387</v>
+        <v>6384287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,12 +7043,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7652,32 +7652,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128784529</v>
+        <v>128784510</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723953</v>
+        <v>723610</v>
       </c>
       <c r="R72" t="n">
-        <v>6384442</v>
+        <v>6384274</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7731,7 +7731,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7750,32 +7749,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790592</v>
+        <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7785,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723955</v>
+        <v>723942</v>
       </c>
       <c r="R73" t="n">
-        <v>6384283</v>
+        <v>6384482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7820,7 +7819,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7830,7 +7829,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7839,7 +7838,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7858,45 +7856,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128790597</v>
+        <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>86963</v>
+        <v>105686</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723990</v>
+        <v>723833</v>
       </c>
       <c r="R74" t="n">
-        <v>6384408</v>
+        <v>6384211</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7926,72 +7924,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128784510</v>
+        <v>128784529</v>
       </c>
       <c r="B75" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8001,10 +7988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723610</v>
+        <v>723953</v>
       </c>
       <c r="R75" t="n">
-        <v>6384274</v>
+        <v>6384442</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8045,6 +8032,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8063,32 +8051,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128790611</v>
+        <v>128790592</v>
       </c>
       <c r="B76" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8098,10 +8086,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723942</v>
+        <v>723955</v>
       </c>
       <c r="R76" t="n">
-        <v>6384482</v>
+        <v>6384283</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,7 +8121,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8143,7 +8131,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8152,6 +8140,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8170,45 +8159,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128784542</v>
+        <v>128790597</v>
       </c>
       <c r="B77" t="n">
-        <v>105686</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723833</v>
+        <v>723990</v>
       </c>
       <c r="R77" t="n">
-        <v>6384211</v>
+        <v>6384408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,29 +8227,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128785788</v>
+        <v>128784519</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>86963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723850</v>
+        <v>723763</v>
       </c>
       <c r="R80" t="n">
-        <v>6384251</v>
+        <v>6384295</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,63 +8551,64 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128784519</v>
+        <v>128785788</v>
       </c>
       <c r="B81" t="n">
-        <v>86963</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723763</v>
+        <v>723850</v>
       </c>
       <c r="R81" t="n">
-        <v>6384295</v>
+        <v>6384251</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,19 +8649,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8872,10 +8872,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128784540</v>
+        <v>128784524</v>
       </c>
       <c r="B84" t="n">
-        <v>99389</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8883,21 +8883,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222361</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723956</v>
+        <v>723940</v>
       </c>
       <c r="R84" t="n">
-        <v>6384330</v>
+        <v>6384281</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,6 +8951,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8969,7 +8970,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B85" t="n">
         <v>86963</v>
@@ -9004,10 +9005,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R85" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9067,10 +9068,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784522</v>
+        <v>128784540</v>
       </c>
       <c r="B86" t="n">
-        <v>86963</v>
+        <v>99389</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9078,21 +9079,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>222361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9102,10 +9103,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723865</v>
+        <v>723956</v>
       </c>
       <c r="R86" t="n">
-        <v>6384223</v>
+        <v>6384330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,7 +9147,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9456,45 +9456,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784508</v>
+        <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>86810</v>
+        <v>90969</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723789</v>
+        <v>723728</v>
       </c>
       <c r="R90" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,12 +9541,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9655,45 +9655,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791655</v>
+        <v>128784508</v>
       </c>
       <c r="B92" t="n">
-        <v>90969</v>
+        <v>86810</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723728</v>
+        <v>723789</v>
       </c>
       <c r="R92" t="n">
-        <v>6384262</v>
+        <v>6384293</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,30 +772,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784512</v>
+        <v>128784544</v>
       </c>
       <c r="B3" t="n">
-        <v>92812</v>
+        <v>107558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6047725</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723641</v>
+        <v>723794</v>
       </c>
       <c r="R3" t="n">
-        <v>6384196</v>
+        <v>6384290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,45 +869,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>86963</v>
+        <v>92817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R4" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -933,50 +933,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784544</v>
+        <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>107550</v>
+        <v>86968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -984,34 +973,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723794</v>
+        <v>723992</v>
       </c>
       <c r="R5" t="n">
-        <v>6384290</v>
+        <v>6384372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,29 +1030,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128785784</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128784517</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128790574</v>
       </c>
       <c r="B9" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128791638</v>
       </c>
       <c r="B10" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128790554</v>
       </c>
       <c r="B11" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>88698</v>
+        <v>88703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,34 +1978,30 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B15" t="n">
-        <v>86963</v>
+        <v>87025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R15" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,70 +2042,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784511</v>
+        <v>128784509</v>
       </c>
       <c r="B16" t="n">
-        <v>92812</v>
+        <v>86815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2117,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723600</v>
+        <v>723618</v>
       </c>
       <c r="R16" t="n">
-        <v>6384247</v>
+        <v>6384286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,10 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790583</v>
+        <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723986</v>
+        <v>723931</v>
       </c>
       <c r="R17" t="n">
-        <v>6384358</v>
+        <v>6384427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,7 +2238,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2259,7 +2248,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,41 +2276,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128791663</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>87020</v>
+        <v>92817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723971</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384460</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,57 +2357,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128784509</v>
+        <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>86810</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723618</v>
+        <v>723986</v>
       </c>
       <c r="R19" t="n">
-        <v>6384286</v>
+        <v>6384358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,29 +2437,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,45 +2683,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128790581</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86963</v>
+        <v>86855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723930</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384314</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,50 +2751,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790594</v>
+        <v>128790581</v>
       </c>
       <c r="B23" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723948</v>
+        <v>723930</v>
       </c>
       <c r="R23" t="n">
-        <v>6384417</v>
+        <v>6384314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,7 +2850,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2871,7 +2860,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2899,45 +2888,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128784553</v>
+        <v>128790594</v>
       </c>
       <c r="B24" t="n">
-        <v>98638</v>
+        <v>86968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723659</v>
+        <v>723948</v>
       </c>
       <c r="R24" t="n">
-        <v>6384257</v>
+        <v>6384417</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,39 +2956,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128784550</v>
+        <v>128791624</v>
       </c>
       <c r="B25" t="n">
-        <v>86850</v>
+        <v>86884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,34 +3007,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723644</v>
+        <v>723724</v>
       </c>
       <c r="R25" t="n">
-        <v>6384278</v>
+        <v>6384209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,22 +3081,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128791633</v>
       </c>
       <c r="B26" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723767</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791633</v>
+        <v>128791629</v>
       </c>
       <c r="B27" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723767</v>
+        <v>723745</v>
       </c>
       <c r="R27" t="n">
-        <v>6384282</v>
+        <v>6384273</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,45 +3287,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791629</v>
+        <v>128784553</v>
       </c>
       <c r="B28" t="n">
-        <v>86879</v>
+        <v>98645</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723745</v>
+        <v>723659</v>
       </c>
       <c r="R28" t="n">
-        <v>6384273</v>
+        <v>6384257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,12 +3372,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>128785780</v>
       </c>
       <c r="B29" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,45 +3478,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128791642</v>
       </c>
       <c r="B30" t="n">
-        <v>86764</v>
+        <v>86884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723745</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,46 +3563,42 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128790627</v>
       </c>
       <c r="B31" t="n">
-        <v>86764</v>
+        <v>87025</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3610,10 +3606,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723660</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,9 +3639,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3660,53 +3666,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B32" t="n">
-        <v>87020</v>
+        <v>86769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R32" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,19 +3746,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3763,44 +3763,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791642</v>
+        <v>128791591</v>
       </c>
       <c r="B33" t="n">
-        <v>86879</v>
+        <v>86769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723745</v>
+        <v>723617</v>
       </c>
       <c r="R33" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3875,7 +3875,7 @@
         <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86764</v>
+        <v>86815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791576</v>
+        <v>128791593</v>
       </c>
       <c r="B43" t="n">
-        <v>86810</v>
+        <v>86769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723743</v>
+        <v>723736</v>
       </c>
       <c r="R43" t="n">
-        <v>6384328</v>
+        <v>6384250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,32 +4848,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128791646</v>
       </c>
       <c r="B44" t="n">
-        <v>86963</v>
+        <v>86884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723732</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384330</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,50 +4916,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790593</v>
+        <v>128790580</v>
       </c>
       <c r="B45" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723955</v>
+        <v>723964</v>
       </c>
       <c r="R45" t="n">
-        <v>6384354</v>
+        <v>6384262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,7 +5015,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5036,7 +5025,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790578</v>
+        <v>128790593</v>
       </c>
       <c r="B46" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5099,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723890</v>
+        <v>723955</v>
       </c>
       <c r="R46" t="n">
-        <v>6384224</v>
+        <v>6384354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5134,7 +5123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5144,7 +5133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,32 +5161,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791646</v>
+        <v>128790578</v>
       </c>
       <c r="B47" t="n">
-        <v>86879</v>
+        <v>86968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5196,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723732</v>
+        <v>723890</v>
       </c>
       <c r="R47" t="n">
-        <v>6384330</v>
+        <v>6384224</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5240,74 +5229,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784521</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723955</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384252</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5348,19 +5348,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5370,7 +5369,7 @@
         <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5464,45 +5463,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128791574</v>
+        <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86810</v>
+        <v>86968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723611</v>
+        <v>723955</v>
       </c>
       <c r="R50" t="n">
-        <v>6384260</v>
+        <v>6384252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,52 +5542,49 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128790589</v>
+        <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>86963</v>
+        <v>87025</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5596,10 +5592,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723770</v>
+        <v>723637</v>
       </c>
       <c r="R51" t="n">
-        <v>6384248</v>
+        <v>6384245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,7 +5627,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5641,7 +5637,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5650,7 +5646,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5669,45 +5664,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784554</v>
+        <v>128790589</v>
       </c>
       <c r="B52" t="n">
-        <v>98638</v>
+        <v>86968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723982</v>
+        <v>723770</v>
       </c>
       <c r="R52" t="n">
-        <v>6384442</v>
+        <v>6384248</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,74 +5732,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784539</v>
+        <v>128791648</v>
       </c>
       <c r="B53" t="n">
-        <v>91043</v>
+        <v>90974</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723615</v>
+        <v>723664</v>
       </c>
       <c r="R53" t="n">
-        <v>6384240</v>
+        <v>6384233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5851,57 +5857,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128791648</v>
+        <v>128784549</v>
       </c>
       <c r="B54" t="n">
-        <v>90969</v>
+        <v>92803</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3286</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723664</v>
+        <v>723958</v>
       </c>
       <c r="R54" t="n">
-        <v>6384233</v>
+        <v>6384364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5948,22 +5954,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128790629</v>
+        <v>128784539</v>
       </c>
       <c r="B55" t="n">
-        <v>87020</v>
+        <v>91048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,30 +5977,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R55" t="n">
-        <v>6384245</v>
+        <v>6384240</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,19 +6034,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6051,22 +6051,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784549</v>
+        <v>128784554</v>
       </c>
       <c r="B56" t="n">
-        <v>92798</v>
+        <v>98645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6074,21 +6074,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>219811</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723958</v>
+        <v>723982</v>
       </c>
       <c r="R56" t="n">
-        <v>6384364</v>
+        <v>6384442</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128790565</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86788</v>
+        <v>86815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723921</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384444</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,19 +6228,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6255,57 +6245,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784526</v>
+        <v>128790565</v>
       </c>
       <c r="B58" t="n">
-        <v>86963</v>
+        <v>86793</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723962</v>
+        <v>723921</v>
       </c>
       <c r="R58" t="n">
-        <v>6384357</v>
+        <v>6384444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6335,40 +6325,49 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784523</v>
+        <v>128784526</v>
       </c>
       <c r="B59" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6400,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723878</v>
+        <v>723962</v>
       </c>
       <c r="R59" t="n">
-        <v>6384241</v>
+        <v>6384357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6463,10 +6462,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784545</v>
+        <v>128784523</v>
       </c>
       <c r="B60" t="n">
-        <v>107550</v>
+        <v>86968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6474,21 +6473,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6498,10 +6497,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723768</v>
+        <v>723878</v>
       </c>
       <c r="R60" t="n">
-        <v>6384301</v>
+        <v>6384241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6542,6 +6541,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6560,32 +6560,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784551</v>
+        <v>128784545</v>
       </c>
       <c r="B61" t="n">
-        <v>98638</v>
+        <v>107558</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723631</v>
+        <v>723768</v>
       </c>
       <c r="R61" t="n">
-        <v>6384236</v>
+        <v>6384301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6657,45 +6657,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128785778</v>
+        <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>86810</v>
+        <v>98645</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>219811</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723760</v>
+        <v>723631</v>
       </c>
       <c r="R62" t="n">
-        <v>6384211</v>
+        <v>6384236</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6742,22 +6742,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128791601</v>
+        <v>128790556</v>
       </c>
       <c r="B63" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6789,10 +6789,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723723</v>
+        <v>723703</v>
       </c>
       <c r="R63" t="n">
-        <v>6384387</v>
+        <v>6384275</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,9 +6822,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6839,22 +6849,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128790556</v>
+        <v>128791601</v>
       </c>
       <c r="B64" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6886,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723703</v>
+        <v>723723</v>
       </c>
       <c r="R64" t="n">
-        <v>6384275</v>
+        <v>6384387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6919,19 +6929,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6946,57 +6946,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128785779</v>
+        <v>128784525</v>
       </c>
       <c r="B65" t="n">
-        <v>86810</v>
+        <v>86968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723790</v>
+        <v>723945</v>
       </c>
       <c r="R65" t="n">
-        <v>6384287</v>
+        <v>6384300</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7037,28 +7037,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128784525</v>
+        <v>128784516</v>
       </c>
       <c r="B66" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7090,10 +7091,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723945</v>
+        <v>723922</v>
       </c>
       <c r="R66" t="n">
-        <v>6384300</v>
+        <v>6384267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,10 +7154,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128784516</v>
+        <v>128784527</v>
       </c>
       <c r="B67" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7188,10 +7189,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723922</v>
+        <v>723949</v>
       </c>
       <c r="R67" t="n">
-        <v>6384267</v>
+        <v>6384442</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7251,10 +7252,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128784527</v>
+        <v>128785782</v>
       </c>
       <c r="B68" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7282,14 +7283,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723949</v>
+        <v>723777</v>
       </c>
       <c r="R68" t="n">
-        <v>6384442</v>
+        <v>6384287</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,44 +7338,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128785782</v>
+        <v>128785779</v>
       </c>
       <c r="B69" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7384,7 +7385,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723777</v>
+        <v>723790</v>
       </c>
       <c r="R69" t="n">
         <v>6384287</v>
@@ -7428,7 +7429,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B70" t="n">
-        <v>86764</v>
+        <v>90974</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R70" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,85 +7515,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128785795</v>
+        <v>128790555</v>
       </c>
       <c r="B71" t="n">
-        <v>90969</v>
+        <v>86769</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723789</v>
+        <v>723944</v>
       </c>
       <c r="R71" t="n">
-        <v>6384213</v>
+        <v>6384278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,29 +7612,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7655,7 +7655,7 @@
         <v>128784510</v>
       </c>
       <c r="B72" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>128784529</v>
       </c>
       <c r="B75" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>128790592</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>128790597</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>128791626</v>
       </c>
       <c r="B78" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128784519</v>
+        <v>128785788</v>
       </c>
       <c r="B80" t="n">
-        <v>86963</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723763</v>
+        <v>723850</v>
       </c>
       <c r="R80" t="n">
-        <v>6384295</v>
+        <v>6384251</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,64 +8551,63 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128785788</v>
+        <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>86968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723850</v>
+        <v>723763</v>
       </c>
       <c r="R81" t="n">
-        <v>6384251</v>
+        <v>6384295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8649,18 +8648,19 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
         <v>128790576</v>
       </c>
       <c r="B82" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>128791643</v>
       </c>
       <c r="B83" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8872,10 +8872,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128784524</v>
+        <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>99396</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8883,21 +8883,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>222361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723940</v>
+        <v>723956</v>
       </c>
       <c r="R84" t="n">
-        <v>6384281</v>
+        <v>6384330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8951,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8970,45 +8969,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B85" t="n">
-        <v>86963</v>
+        <v>86884</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R85" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9049,29 +9048,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784540</v>
+        <v>128784524</v>
       </c>
       <c r="B86" t="n">
-        <v>99389</v>
+        <v>86968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9079,21 +9077,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222361</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9103,10 +9101,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723956</v>
+        <v>723940</v>
       </c>
       <c r="R86" t="n">
-        <v>6384330</v>
+        <v>6384281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9147,6 +9145,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9165,45 +9164,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791635</v>
+        <v>128784522</v>
       </c>
       <c r="B87" t="n">
-        <v>86879</v>
+        <v>86968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723782</v>
+        <v>723865</v>
       </c>
       <c r="R87" t="n">
-        <v>6384293</v>
+        <v>6384223</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9244,63 +9243,64 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B88" t="n">
-        <v>86810</v>
+        <v>86769</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R88" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B89" t="n">
-        <v>86764</v>
+        <v>86815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R89" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,44 +9444,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791655</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
-        <v>90969</v>
+        <v>86815</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723728</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384262</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,6 +9527,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9553,10 +9558,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784508</v>
+        <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>86810</v>
+        <v>90974</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723789</v>
+        <v>723728</v>
       </c>
       <c r="R92" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,12 +9740,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
         <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>86850</v>
+        <v>86855</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87157</v>
+        <v>87162</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>90275</v>
+        <v>90280</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86929</v>
+        <v>86934</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86929</v>
+        <v>86934</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784512</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>90981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723641</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384196</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,57 +760,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>86975</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R3" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -836,50 +836,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128791651</v>
+        <v>128790598</v>
       </c>
       <c r="B4" t="n">
-        <v>90981</v>
+        <v>86975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -887,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -911,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723674</v>
+        <v>723992</v>
       </c>
       <c r="R4" t="n">
-        <v>6384225</v>
+        <v>6384372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,29 +933,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1881,41 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791663</v>
+        <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>87032</v>
+        <v>88710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>433</v>
+        <v>4379</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723971</v>
+        <v>723922</v>
       </c>
       <c r="R14" t="n">
-        <v>6384460</v>
+        <v>6384266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,22 +1966,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784509</v>
+        <v>128791663</v>
       </c>
       <c r="B15" t="n">
-        <v>86822</v>
+        <v>87032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,34 +1989,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723618</v>
+        <v>723971</v>
       </c>
       <c r="R15" t="n">
-        <v>6384286</v>
+        <v>6384460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,44 +2059,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784506</v>
+        <v>128784509</v>
       </c>
       <c r="B16" t="n">
-        <v>88710</v>
+        <v>86822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4379</v>
+        <v>424</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723922</v>
+        <v>723618</v>
       </c>
       <c r="R16" t="n">
-        <v>6384266</v>
+        <v>6384286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3384,41 +3384,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790627</v>
+        <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>87032</v>
+        <v>86776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723660</v>
+        <v>723744</v>
       </c>
       <c r="R29" t="n">
-        <v>6384309</v>
+        <v>6384205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,19 +3452,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,57 +3469,53 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128790627</v>
       </c>
       <c r="B30" t="n">
-        <v>86776</v>
+        <v>87032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723660</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,9 +3545,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3572,12 +3572,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86776</v>
+        <v>86822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791576</v>
+        <v>128790580</v>
       </c>
       <c r="B43" t="n">
-        <v>86822</v>
+        <v>86975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723743</v>
+        <v>723964</v>
       </c>
       <c r="R43" t="n">
-        <v>6384328</v>
+        <v>6384262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,36 +4819,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B44" t="n">
         <v>86975</v>
@@ -4883,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4918,7 +4929,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4928,7 +4939,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,7 +4967,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790593</v>
+        <v>128790578</v>
       </c>
       <c r="B45" t="n">
         <v>86975</v>
@@ -4991,10 +5002,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723955</v>
+        <v>723890</v>
       </c>
       <c r="R45" t="n">
-        <v>6384354</v>
+        <v>6384224</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,7 +5037,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5036,7 +5047,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790578</v>
+        <v>128791646</v>
       </c>
       <c r="B46" t="n">
-        <v>86975</v>
+        <v>86891</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5099,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723890</v>
+        <v>723732</v>
       </c>
       <c r="R46" t="n">
-        <v>6384224</v>
+        <v>6384330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5132,72 +5143,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791646</v>
+        <v>128791593</v>
       </c>
       <c r="B47" t="n">
-        <v>86891</v>
+        <v>86776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723732</v>
+        <v>723736</v>
       </c>
       <c r="R47" t="n">
-        <v>6384330</v>
+        <v>6384250</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7544,32 +7544,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128791626</v>
+        <v>128790555</v>
       </c>
       <c r="B71" t="n">
-        <v>86891</v>
+        <v>86776</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723741</v>
+        <v>723944</v>
       </c>
       <c r="R71" t="n">
-        <v>6384216</v>
+        <v>6384278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,74 +7612,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B72" t="n">
-        <v>86776</v>
+        <v>90981</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R72" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,50 +7720,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128785795</v>
+        <v>128784529</v>
       </c>
       <c r="B73" t="n">
-        <v>90981</v>
+        <v>86975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7760,34 +7760,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723789</v>
+        <v>723953</v>
       </c>
       <c r="R73" t="n">
-        <v>6384213</v>
+        <v>6384442</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7828,25 +7828,26 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128784529</v>
+        <v>128790592</v>
       </c>
       <c r="B74" t="n">
         <v>86975</v>
@@ -7877,14 +7878,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723953</v>
+        <v>723955</v>
       </c>
       <c r="R74" t="n">
-        <v>6384442</v>
+        <v>6384283</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7914,9 +7915,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,19 +7943,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128790592</v>
+        <v>128790597</v>
       </c>
       <c r="B75" t="n">
         <v>86975</v>
@@ -7979,10 +7990,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723955</v>
+        <v>723990</v>
       </c>
       <c r="R75" t="n">
-        <v>6384283</v>
+        <v>6384408</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8014,7 +8025,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8024,7 +8035,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8052,32 +8063,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B76" t="n">
-        <v>86975</v>
+        <v>86891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8087,10 +8098,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R76" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8120,40 +8131,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8872,45 +8872,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128784524</v>
+        <v>128791635</v>
       </c>
       <c r="B84" t="n">
-        <v>86975</v>
+        <v>86891</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723940</v>
+        <v>723782</v>
       </c>
       <c r="R84" t="n">
-        <v>6384281</v>
+        <v>6384293</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,26 +8951,25 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784522</v>
+        <v>128784524</v>
       </c>
       <c r="B85" t="n">
         <v>86975</v>
@@ -9005,10 +9004,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723865</v>
+        <v>723940</v>
       </c>
       <c r="R85" t="n">
-        <v>6384223</v>
+        <v>6384281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9068,45 +9067,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791635</v>
+        <v>128784522</v>
       </c>
       <c r="B86" t="n">
-        <v>86891</v>
+        <v>86975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723782</v>
+        <v>723865</v>
       </c>
       <c r="R86" t="n">
-        <v>6384293</v>
+        <v>6384223</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9147,18 +9146,19 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9262,45 +9262,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86776</v>
+        <v>86822</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R88" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86822</v>
+        <v>86776</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R89" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,12 +9444,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,30 +772,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784512</v>
+        <v>128784544</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>107571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6047725</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723641</v>
+        <v>723794</v>
       </c>
       <c r="R3" t="n">
-        <v>6384196</v>
+        <v>6384290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,45 +869,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>86975</v>
+        <v>92830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R4" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -933,50 +933,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784544</v>
+        <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>107566</v>
+        <v>86978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -984,34 +973,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723794</v>
+        <v>723992</v>
       </c>
       <c r="R5" t="n">
-        <v>6384290</v>
+        <v>6384372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,74 +1030,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128785784</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86975</v>
+        <v>86825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723969</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384430</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,75 +1138,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128784517</v>
+        <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723612</v>
+        <v>723771</v>
       </c>
       <c r="R7" t="n">
-        <v>6384274</v>
+        <v>6384299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,64 +1256,63 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128791638</v>
+        <v>128785784</v>
       </c>
       <c r="B8" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723771</v>
+        <v>723969</v>
       </c>
       <c r="R8" t="n">
-        <v>6384299</v>
+        <v>6384430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,28 +1353,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128790574</v>
+        <v>128784517</v>
       </c>
       <c r="B9" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,14 +1403,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723609</v>
+        <v>723612</v>
       </c>
       <c r="R9" t="n">
-        <v>6384278</v>
+        <v>6384274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,19 +1440,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,44 +1458,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790645</v>
+        <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723788</v>
+        <v>723609</v>
       </c>
       <c r="R10" t="n">
-        <v>6384286</v>
+        <v>6384278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,7 +1540,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1551,7 +1550,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1560,6 +1559,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B11" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R11" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,22 +1664,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B12" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R12" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,74 +1744,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86975</v>
+        <v>86779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R13" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,19 +1863,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>88710</v>
+        <v>88713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128791663</v>
       </c>
       <c r="B15" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128784509</v>
       </c>
       <c r="B16" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86862</v>
+        <v>86865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790581</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86975</v>
+        <v>98658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723930</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384314</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,72 +2848,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790594</v>
+        <v>128791633</v>
       </c>
       <c r="B24" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2923,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723948</v>
+        <v>723767</v>
       </c>
       <c r="R24" t="n">
-        <v>6384417</v>
+        <v>6384282</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,50 +2945,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791633</v>
+        <v>128791624</v>
       </c>
       <c r="B25" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723767</v>
+        <v>723724</v>
       </c>
       <c r="R25" t="n">
-        <v>6384282</v>
+        <v>6384209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,10 +3071,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B26" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,32 +3168,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B27" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R27" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,74 +3236,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128784553</v>
+        <v>128790594</v>
       </c>
       <c r="B28" t="n">
-        <v>98653</v>
+        <v>86978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723659</v>
+        <v>723948</v>
       </c>
       <c r="R28" t="n">
-        <v>6384257</v>
+        <v>6384417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,29 +3344,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,30 +3481,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128790627</v>
+        <v>128791591</v>
       </c>
       <c r="B30" t="n">
-        <v>87032</v>
+        <v>86779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3512,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723660</v>
+        <v>723617</v>
       </c>
       <c r="R30" t="n">
-        <v>6384309</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3545,19 +3549,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3572,46 +3566,42 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128790627</v>
       </c>
       <c r="B31" t="n">
-        <v>86776</v>
+        <v>87035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3619,10 +3609,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723660</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3652,9 +3642,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,53 +3669,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785780</v>
+        <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>92825</v>
+        <v>86894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723935</v>
+        <v>723745</v>
       </c>
       <c r="R32" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,64 +3760,59 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791642</v>
+        <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>86891</v>
+        <v>92830</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723745</v>
+        <v>723935</v>
       </c>
       <c r="R33" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,18 +3853,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
         <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4062,45 +4062,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128784530</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>724024</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384488</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,29 +4141,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128790577</v>
+        <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,14 +4190,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723815</v>
+        <v>724024</v>
       </c>
       <c r="R37" t="n">
-        <v>6384231</v>
+        <v>6384488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,19 +4227,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4256,22 +4245,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128784518</v>
+        <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,14 +4288,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723642</v>
+        <v>723815</v>
       </c>
       <c r="R38" t="n">
-        <v>6384222</v>
+        <v>6384231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,9 +4325,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,57 +4353,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,18 +4444,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4466,7 +4466,7 @@
         <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790580</v>
+        <v>128791646</v>
       </c>
       <c r="B43" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723964</v>
+        <v>723732</v>
       </c>
       <c r="R43" t="n">
-        <v>6384262</v>
+        <v>6384330</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,50 +4819,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790593</v>
+        <v>128790580</v>
       </c>
       <c r="B44" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723955</v>
+        <v>723964</v>
       </c>
       <c r="R44" t="n">
-        <v>6384354</v>
+        <v>6384262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4929,7 +4918,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4939,7 +4928,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4967,10 +4956,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790578</v>
+        <v>128790593</v>
       </c>
       <c r="B45" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723890</v>
+        <v>723955</v>
       </c>
       <c r="R45" t="n">
-        <v>6384224</v>
+        <v>6384354</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5037,7 +5026,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5047,7 +5036,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,32 +5064,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791646</v>
+        <v>128790578</v>
       </c>
       <c r="B46" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723732</v>
+        <v>723890</v>
       </c>
       <c r="R46" t="n">
-        <v>6384330</v>
+        <v>6384224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,29 +5132,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5175,7 +5175,7 @@
         <v>128791593</v>
       </c>
       <c r="B47" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784521</v>
+        <v>128784562</v>
       </c>
       <c r="B48" t="n">
-        <v>86975</v>
+        <v>106982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5280,21 +5280,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723955</v>
+        <v>723639</v>
       </c>
       <c r="R48" t="n">
-        <v>6384252</v>
+        <v>6384269</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5348,7 +5348,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5367,10 +5366,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784562</v>
+        <v>128784521</v>
       </c>
       <c r="B49" t="n">
-        <v>106977</v>
+        <v>86978</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5378,21 +5377,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5402,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723639</v>
+        <v>723955</v>
       </c>
       <c r="R49" t="n">
-        <v>6384269</v>
+        <v>6384252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,6 +5445,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>128791574</v>
       </c>
       <c r="B50" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784549</v>
+        <v>128784554</v>
       </c>
       <c r="B51" t="n">
-        <v>92811</v>
+        <v>98658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5572,21 +5572,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>219811</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723958</v>
+        <v>723982</v>
       </c>
       <c r="R51" t="n">
-        <v>6384364</v>
+        <v>6384442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,30 +5658,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128790629</v>
+        <v>128791648</v>
       </c>
       <c r="B52" t="n">
-        <v>87032</v>
+        <v>90984</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>433</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5689,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723637</v>
+        <v>723664</v>
       </c>
       <c r="R52" t="n">
-        <v>6384245</v>
+        <v>6384233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,19 +5726,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5749,57 +5743,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128791648</v>
+        <v>128784549</v>
       </c>
       <c r="B53" t="n">
-        <v>90981</v>
+        <v>92816</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3286</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723664</v>
+        <v>723958</v>
       </c>
       <c r="R53" t="n">
-        <v>6384233</v>
+        <v>6384364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,22 +5840,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784539</v>
+        <v>128790629</v>
       </c>
       <c r="B54" t="n">
-        <v>91055</v>
+        <v>87035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,34 +5863,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>433</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723615</v>
+        <v>723637</v>
       </c>
       <c r="R54" t="n">
-        <v>6384240</v>
+        <v>6384245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,9 +5916,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,12 +5943,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5958,7 +5958,7 @@
         <v>128790589</v>
       </c>
       <c r="B55" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784554</v>
+        <v>128784539</v>
       </c>
       <c r="B56" t="n">
-        <v>98653</v>
+        <v>91058</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219811</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723982</v>
+        <v>723615</v>
       </c>
       <c r="R56" t="n">
-        <v>6384442</v>
+        <v>6384240</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128785778</v>
+        <v>128784526</v>
       </c>
       <c r="B57" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723760</v>
+        <v>723962</v>
       </c>
       <c r="R57" t="n">
-        <v>6384211</v>
+        <v>6384357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,63 +6239,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128790565</v>
+        <v>128784523</v>
       </c>
       <c r="B58" t="n">
-        <v>86800</v>
+        <v>86978</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723921</v>
+        <v>723878</v>
       </c>
       <c r="R58" t="n">
-        <v>6384444</v>
+        <v>6384241</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,84 +6326,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784526</v>
+        <v>128790565</v>
       </c>
       <c r="B59" t="n">
-        <v>86975</v>
+        <v>86803</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723962</v>
+        <v>723921</v>
       </c>
       <c r="R59" t="n">
-        <v>6384357</v>
+        <v>6384444</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,75 +6424,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784523</v>
+        <v>128785778</v>
       </c>
       <c r="B60" t="n">
-        <v>86975</v>
+        <v>86825</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723878</v>
+        <v>723760</v>
       </c>
       <c r="R60" t="n">
-        <v>6384241</v>
+        <v>6384211</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6541,19 +6542,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
         <v>128784545</v>
       </c>
       <c r="B61" t="n">
-        <v>107566</v>
+        <v>107571</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128790556</v>
+        <v>128784525</v>
       </c>
       <c r="B63" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723703</v>
+        <v>723945</v>
       </c>
       <c r="R63" t="n">
-        <v>6384275</v>
+        <v>6384300</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,84 +6822,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791601</v>
+        <v>128784516</v>
       </c>
       <c r="B64" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723723</v>
+        <v>723922</v>
       </c>
       <c r="R64" t="n">
-        <v>6384387</v>
+        <v>6384267</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6940,28 +6931,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128784525</v>
+        <v>128784527</v>
       </c>
       <c r="B65" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6993,10 +6985,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723945</v>
+        <v>723949</v>
       </c>
       <c r="R65" t="n">
-        <v>6384300</v>
+        <v>6384442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7056,10 +7048,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128784516</v>
+        <v>128785782</v>
       </c>
       <c r="B66" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7087,14 +7079,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723922</v>
+        <v>723777</v>
       </c>
       <c r="R66" t="n">
-        <v>6384267</v>
+        <v>6384287</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,57 +7134,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128784527</v>
+        <v>128790556</v>
       </c>
       <c r="B67" t="n">
-        <v>86975</v>
+        <v>86779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723949</v>
+        <v>723703</v>
       </c>
       <c r="R67" t="n">
-        <v>6384442</v>
+        <v>6384275</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7222,75 +7214,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128785782</v>
+        <v>128791601</v>
       </c>
       <c r="B68" t="n">
-        <v>86975</v>
+        <v>86779</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723777</v>
+        <v>723723</v>
       </c>
       <c r="R68" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7331,19 +7332,18 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
         <v>128785779</v>
       </c>
       <c r="B69" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128784510</v>
+        <v>128790555</v>
       </c>
       <c r="B70" t="n">
-        <v>86822</v>
+        <v>86779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723610</v>
+        <v>723944</v>
       </c>
       <c r="R70" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,74 +7515,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128790555</v>
+        <v>128785795</v>
       </c>
       <c r="B71" t="n">
-        <v>86776</v>
+        <v>90984</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723944</v>
+        <v>723789</v>
       </c>
       <c r="R71" t="n">
-        <v>6384278</v>
+        <v>6384213</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,85 +7623,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785795</v>
+        <v>128784510</v>
       </c>
       <c r="B72" t="n">
-        <v>90981</v>
+        <v>86825</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723789</v>
+        <v>723610</v>
       </c>
       <c r="R72" t="n">
-        <v>6384213</v>
+        <v>6384274</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7737,57 +7737,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128784529</v>
+        <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>86975</v>
+        <v>105706</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723953</v>
+        <v>723942</v>
       </c>
       <c r="R73" t="n">
-        <v>6384442</v>
+        <v>6384482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,75 +7817,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128790592</v>
+        <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>86975</v>
+        <v>105706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>224098</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723955</v>
+        <v>723833</v>
       </c>
       <c r="R74" t="n">
-        <v>6384283</v>
+        <v>6384211</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7915,72 +7924,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B75" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7990,10 +7988,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R75" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8023,85 +8021,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791626</v>
+        <v>128784529</v>
       </c>
       <c r="B76" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723741</v>
+        <v>723953</v>
       </c>
       <c r="R76" t="n">
-        <v>6384216</v>
+        <v>6384442</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8142,50 +8129,51 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790611</v>
+        <v>128790592</v>
       </c>
       <c r="B77" t="n">
-        <v>105701</v>
+        <v>86978</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8195,10 +8183,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723942</v>
+        <v>723955</v>
       </c>
       <c r="R77" t="n">
-        <v>6384482</v>
+        <v>6384283</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8230,7 +8218,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8240,7 +8228,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8249,6 +8237,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8267,45 +8256,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128784542</v>
+        <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>105701</v>
+        <v>86978</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723833</v>
+        <v>723990</v>
       </c>
       <c r="R78" t="n">
-        <v>6384211</v>
+        <v>6384408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,29 +8324,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8569,45 +8569,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791643</v>
+        <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723739</v>
+        <v>723763</v>
       </c>
       <c r="R81" t="n">
-        <v>6384326</v>
+        <v>6384295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,18 +8648,19 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8669,7 +8670,7 @@
         <v>128790576</v>
       </c>
       <c r="B82" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8774,45 +8775,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128784519</v>
+        <v>128791643</v>
       </c>
       <c r="B83" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723763</v>
+        <v>723739</v>
       </c>
       <c r="R83" t="n">
-        <v>6384295</v>
+        <v>6384326</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8853,64 +8854,63 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B84" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R84" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,28 +8951,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B85" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9004,10 +9005,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R85" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9067,10 +9068,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784522</v>
+        <v>128784540</v>
       </c>
       <c r="B86" t="n">
-        <v>86975</v>
+        <v>99409</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9078,21 +9079,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>222361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9102,10 +9103,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723865</v>
+        <v>723956</v>
       </c>
       <c r="R86" t="n">
-        <v>6384223</v>
+        <v>6384330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,7 +9147,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9165,45 +9165,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784540</v>
+        <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>99404</v>
+        <v>86894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222361</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723956</v>
+        <v>723782</v>
       </c>
       <c r="R87" t="n">
-        <v>6384330</v>
+        <v>6384293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9250,57 +9250,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B88" t="n">
-        <v>86822</v>
+        <v>86779</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R88" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B89" t="n">
-        <v>86776</v>
+        <v>86825</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R89" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,44 +9444,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791578</v>
+        <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>86822</v>
+        <v>90984</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723775</v>
+        <v>723728</v>
       </c>
       <c r="R90" t="n">
-        <v>6384432</v>
+        <v>6384262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,11 +9527,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9561,7 +9556,7 @@
         <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9655,32 +9650,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791655</v>
+        <v>128791578</v>
       </c>
       <c r="B92" t="n">
-        <v>90981</v>
+        <v>86825</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9690,10 +9685,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723728</v>
+        <v>723775</v>
       </c>
       <c r="R92" t="n">
-        <v>6384262</v>
+        <v>6384432</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9726,6 +9721,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9752,41 +9752,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B93" t="n">
-        <v>87032</v>
+        <v>98658</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R93" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9816,78 +9824,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B94" t="n">
-        <v>98653</v>
+        <v>87035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R94" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9917,40 +9928,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106977</v>
+        <v>106982</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107566</v>
+        <v>107571</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>86862</v>
+        <v>86865</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87169</v>
+        <v>87172</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>90287</v>
+        <v>90290</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B2" t="n">
-        <v>90984</v>
+        <v>107574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R2" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B3" t="n">
-        <v>107571</v>
+        <v>90987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R3" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128785784</v>
+        <v>128784517</v>
       </c>
       <c r="B8" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,14 +1305,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723969</v>
+        <v>723612</v>
       </c>
       <c r="R8" t="n">
-        <v>6384430</v>
+        <v>6384274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,22 +1360,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128784517</v>
+        <v>128790574</v>
       </c>
       <c r="B9" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,14 +1403,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723612</v>
+        <v>723609</v>
       </c>
       <c r="R9" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,9 +1440,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1458,22 +1468,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790574</v>
+        <v>128785784</v>
       </c>
       <c r="B10" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,14 +1511,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723609</v>
+        <v>723969</v>
       </c>
       <c r="R10" t="n">
-        <v>6384278</v>
+        <v>6384430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,19 +1548,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128785783</v>
       </c>
       <c r="B11" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>128790554</v>
       </c>
       <c r="B12" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,45 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128784506</v>
+        <v>128790595</v>
       </c>
       <c r="B14" t="n">
-        <v>88713</v>
+        <v>86981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723922</v>
+        <v>723931</v>
       </c>
       <c r="R14" t="n">
-        <v>6384266</v>
+        <v>6384427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,59 +1949,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128791663</v>
+        <v>128790583</v>
       </c>
       <c r="B15" t="n">
-        <v>87035</v>
+        <v>86981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2009,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723971</v>
+        <v>723986</v>
       </c>
       <c r="R15" t="n">
-        <v>6384460</v>
+        <v>6384358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,63 +2057,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784509</v>
+        <v>128784511</v>
       </c>
       <c r="B16" t="n">
-        <v>86825</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2106,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723618</v>
+        <v>723600</v>
       </c>
       <c r="R16" t="n">
-        <v>6384286</v>
+        <v>6384247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,34 +2190,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B17" t="n">
-        <v>86978</v>
+        <v>87038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2203,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R17" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,70 +2254,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784511</v>
+        <v>128784509</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>86828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723600</v>
+        <v>723618</v>
       </c>
       <c r="R18" t="n">
-        <v>6384247</v>
+        <v>6384286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,45 +2380,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790583</v>
+        <v>128784506</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>88716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723986</v>
+        <v>723922</v>
       </c>
       <c r="R19" t="n">
-        <v>6384358</v>
+        <v>6384266</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,40 +2448,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128791624</v>
       </c>
       <c r="B22" t="n">
-        <v>86865</v>
+        <v>86897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723724</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,57 +2768,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128791633</v>
       </c>
       <c r="B23" t="n">
-        <v>98658</v>
+        <v>86897</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723767</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,22 +2865,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791633</v>
+        <v>128791629</v>
       </c>
       <c r="B24" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723767</v>
+        <v>723745</v>
       </c>
       <c r="R24" t="n">
-        <v>6384282</v>
+        <v>6384273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,45 +2974,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791624</v>
+        <v>128784553</v>
       </c>
       <c r="B25" t="n">
-        <v>86894</v>
+        <v>98661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723724</v>
+        <v>723659</v>
       </c>
       <c r="R25" t="n">
-        <v>6384209</v>
+        <v>6384257</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,44 +3059,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791629</v>
+        <v>128790581</v>
       </c>
       <c r="B26" t="n">
-        <v>86894</v>
+        <v>86981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723745</v>
+        <v>723930</v>
       </c>
       <c r="R26" t="n">
-        <v>6384273</v>
+        <v>6384314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3139,39 +3139,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790581</v>
+        <v>128790594</v>
       </c>
       <c r="B27" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723930</v>
+        <v>723948</v>
       </c>
       <c r="R27" t="n">
-        <v>6384314</v>
+        <v>6384417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,7 +3249,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3248,7 +3259,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,45 +3287,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790594</v>
+        <v>128784550</v>
       </c>
       <c r="B28" t="n">
-        <v>86978</v>
+        <v>86868</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723948</v>
+        <v>723644</v>
       </c>
       <c r="R28" t="n">
-        <v>6384417</v>
+        <v>6384278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,40 +3355,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>128791591</v>
       </c>
       <c r="B30" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>128790627</v>
       </c>
       <c r="B31" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128791566</v>
+        <v>128791631</v>
       </c>
       <c r="B34" t="n">
-        <v>87035</v>
+        <v>86897</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3883,19 +3883,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3903,10 +3907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723725</v>
+        <v>723764</v>
       </c>
       <c r="R34" t="n">
-        <v>6384258</v>
+        <v>6384279</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3965,10 +3969,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128785776</v>
+        <v>128791566</v>
       </c>
       <c r="B35" t="n">
-        <v>86825</v>
+        <v>87038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3976,34 +3980,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723727</v>
+        <v>723725</v>
       </c>
       <c r="R35" t="n">
-        <v>6384228</v>
+        <v>6384258</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,22 +4050,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128791631</v>
+        <v>128785776</v>
       </c>
       <c r="B36" t="n">
-        <v>86894</v>
+        <v>86828</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,34 +4073,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723764</v>
+        <v>723727</v>
       </c>
       <c r="R36" t="n">
-        <v>6384279</v>
+        <v>6384228</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4147,12 +4147,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>128784530</v>
       </c>
       <c r="B37" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>128790577</v>
       </c>
       <c r="B38" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B40" t="n">
-        <v>86779</v>
+        <v>92833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,34 +4474,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R40" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,28 +4538,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B41" t="n">
-        <v>92830</v>
+        <v>86782</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,30 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R41" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,51 +4636,50 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791576</v>
+        <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723743</v>
+        <v>723964</v>
       </c>
       <c r="R42" t="n">
-        <v>6384328</v>
+        <v>6384262</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,61 +4722,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791646</v>
+        <v>128790593</v>
       </c>
       <c r="B43" t="n">
-        <v>86894</v>
+        <v>86981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723732</v>
+        <v>723955</v>
       </c>
       <c r="R43" t="n">
-        <v>6384330</v>
+        <v>6384354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,39 +4830,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128790578</v>
       </c>
       <c r="B44" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723890</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384224</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4918,7 +4940,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4928,7 +4950,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4978,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790593</v>
+        <v>128791576</v>
       </c>
       <c r="B45" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723955</v>
+        <v>723743</v>
       </c>
       <c r="R45" t="n">
-        <v>6384354</v>
+        <v>6384328</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5024,72 +5046,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790578</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86978</v>
+        <v>86782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5099,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723890</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384224</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5132,72 +5143,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791593</v>
+        <v>128791646</v>
       </c>
       <c r="B47" t="n">
-        <v>86779</v>
+        <v>86897</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723736</v>
+        <v>723732</v>
       </c>
       <c r="R47" t="n">
-        <v>6384250</v>
+        <v>6384330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,45 +5269,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>106982</v>
+        <v>86828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,22 +5354,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784521</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86978</v>
+        <v>106985</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5377,21 +5377,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723955</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384252</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5445,7 +5445,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5464,45 +5463,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128791574</v>
+        <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723611</v>
+        <v>723955</v>
       </c>
       <c r="R50" t="n">
-        <v>6384260</v>
+        <v>6384252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,63 +5542,60 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784554</v>
+        <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>98658</v>
+        <v>87038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723982</v>
+        <v>723637</v>
       </c>
       <c r="R51" t="n">
-        <v>6384442</v>
+        <v>6384245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,9 +5625,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5646,57 +5652,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128791648</v>
+        <v>128784549</v>
       </c>
       <c r="B52" t="n">
-        <v>90984</v>
+        <v>92819</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3286</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723664</v>
+        <v>723958</v>
       </c>
       <c r="R52" t="n">
-        <v>6384233</v>
+        <v>6384364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5743,57 +5749,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128784549</v>
+        <v>128791648</v>
       </c>
       <c r="B53" t="n">
-        <v>92816</v>
+        <v>90987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>3286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723958</v>
+        <v>723664</v>
       </c>
       <c r="R53" t="n">
-        <v>6384364</v>
+        <v>6384233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5840,22 +5846,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128790629</v>
+        <v>128784539</v>
       </c>
       <c r="B54" t="n">
-        <v>87035</v>
+        <v>91061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,30 +5869,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R54" t="n">
-        <v>6384245</v>
+        <v>6384240</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5916,19 +5926,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,57 +5943,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128790589</v>
+        <v>128784554</v>
       </c>
       <c r="B55" t="n">
-        <v>86978</v>
+        <v>98661</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723770</v>
+        <v>723982</v>
       </c>
       <c r="R55" t="n">
-        <v>6384248</v>
+        <v>6384442</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6023,85 +6023,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128784539</v>
+        <v>128790589</v>
       </c>
       <c r="B56" t="n">
-        <v>91058</v>
+        <v>86981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723615</v>
+        <v>723770</v>
       </c>
       <c r="R56" t="n">
-        <v>6384240</v>
+        <v>6384248</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6131,74 +6120,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128784526</v>
+        <v>128790565</v>
       </c>
       <c r="B57" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723962</v>
+        <v>723921</v>
       </c>
       <c r="R57" t="n">
-        <v>6384357</v>
+        <v>6384444</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,40 +6228,49 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784523</v>
+        <v>128784545</v>
       </c>
       <c r="B58" t="n">
-        <v>86978</v>
+        <v>107574</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6269,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6293,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723878</v>
+        <v>723768</v>
       </c>
       <c r="R58" t="n">
-        <v>6384241</v>
+        <v>6384301</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,7 +6346,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6356,45 +6364,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128790565</v>
+        <v>128784526</v>
       </c>
       <c r="B59" t="n">
-        <v>86803</v>
+        <v>86981</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723921</v>
+        <v>723962</v>
       </c>
       <c r="R59" t="n">
-        <v>6384444</v>
+        <v>6384357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,84 +6432,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128785778</v>
+        <v>128784523</v>
       </c>
       <c r="B60" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723760</v>
+        <v>723878</v>
       </c>
       <c r="R60" t="n">
-        <v>6384211</v>
+        <v>6384241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6542,63 +6541,64 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784545</v>
+        <v>128785778</v>
       </c>
       <c r="B61" t="n">
-        <v>107571</v>
+        <v>86828</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>424</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723768</v>
+        <v>723760</v>
       </c>
       <c r="R61" t="n">
-        <v>6384301</v>
+        <v>6384211</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6645,12 +6645,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
         <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128784525</v>
+        <v>128790556</v>
       </c>
       <c r="B63" t="n">
-        <v>86978</v>
+        <v>86782</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723945</v>
+        <v>723703</v>
       </c>
       <c r="R63" t="n">
-        <v>6384300</v>
+        <v>6384275</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,75 +6822,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128784516</v>
+        <v>128791601</v>
       </c>
       <c r="B64" t="n">
-        <v>86978</v>
+        <v>86782</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723922</v>
+        <v>723723</v>
       </c>
       <c r="R64" t="n">
-        <v>6384267</v>
+        <v>6384387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6931,64 +6940,63 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128784527</v>
+        <v>128785779</v>
       </c>
       <c r="B65" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723949</v>
+        <v>723790</v>
       </c>
       <c r="R65" t="n">
-        <v>6384442</v>
+        <v>6384287</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,29 +7037,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128785782</v>
+        <v>128784525</v>
       </c>
       <c r="B66" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,14 +7086,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723777</v>
+        <v>723945</v>
       </c>
       <c r="R66" t="n">
-        <v>6384287</v>
+        <v>6384300</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7134,57 +7141,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128790556</v>
+        <v>128784516</v>
       </c>
       <c r="B67" t="n">
-        <v>86779</v>
+        <v>86981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723703</v>
+        <v>723922</v>
       </c>
       <c r="R67" t="n">
-        <v>6384275</v>
+        <v>6384267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7214,84 +7221,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791601</v>
+        <v>128784527</v>
       </c>
       <c r="B68" t="n">
-        <v>86779</v>
+        <v>86981</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723723</v>
+        <v>723949</v>
       </c>
       <c r="R68" t="n">
-        <v>6384387</v>
+        <v>6384442</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7332,50 +7330,51 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128785779</v>
+        <v>128785782</v>
       </c>
       <c r="B69" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7385,7 +7384,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723790</v>
+        <v>723777</v>
       </c>
       <c r="R69" t="n">
         <v>6384287</v>
@@ -7429,6 +7428,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7447,45 +7447,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128790555</v>
+        <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>86779</v>
+        <v>86828</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723944</v>
+        <v>723610</v>
       </c>
       <c r="R70" t="n">
-        <v>6384278</v>
+        <v>6384274</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7515,85 +7515,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128785795</v>
+        <v>128791626</v>
       </c>
       <c r="B71" t="n">
-        <v>90984</v>
+        <v>86897</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3286</v>
+        <v>248956</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723789</v>
+        <v>723741</v>
       </c>
       <c r="R71" t="n">
-        <v>6384213</v>
+        <v>6384216</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7640,57 +7629,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128784510</v>
+        <v>128785795</v>
       </c>
       <c r="B72" t="n">
-        <v>86825</v>
+        <v>90987</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723610</v>
+        <v>723789</v>
       </c>
       <c r="R72" t="n">
-        <v>6384274</v>
+        <v>6384213</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7737,22 +7726,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790611</v>
+        <v>128790555</v>
       </c>
       <c r="B73" t="n">
-        <v>105706</v>
+        <v>86782</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7760,21 +7749,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224098</v>
+        <v>3762</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7784,10 +7773,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723942</v>
+        <v>723944</v>
       </c>
       <c r="R73" t="n">
-        <v>6384482</v>
+        <v>6384278</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7819,7 +7808,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7829,7 +7818,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7838,6 +7827,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7859,7 +7849,7 @@
         <v>128784542</v>
       </c>
       <c r="B74" t="n">
-        <v>105706</v>
+        <v>105709</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7953,32 +7943,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791626</v>
+        <v>128790611</v>
       </c>
       <c r="B75" t="n">
-        <v>86894</v>
+        <v>105709</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248956</v>
+        <v>224098</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7988,10 +7978,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723741</v>
+        <v>723942</v>
       </c>
       <c r="R75" t="n">
-        <v>6384216</v>
+        <v>6384482</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8021,9 +8011,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8038,12 +8038,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
         <v>128784529</v>
       </c>
       <c r="B76" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>128790592</v>
       </c>
       <c r="B77" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8569,45 +8569,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128784519</v>
+        <v>128791643</v>
       </c>
       <c r="B81" t="n">
-        <v>86978</v>
+        <v>86897</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723763</v>
+        <v>723739</v>
       </c>
       <c r="R81" t="n">
-        <v>6384295</v>
+        <v>6384326</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8648,29 +8648,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128790576</v>
+        <v>128784519</v>
       </c>
       <c r="B82" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8698,14 +8697,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723628</v>
+        <v>723763</v>
       </c>
       <c r="R82" t="n">
-        <v>6384239</v>
+        <v>6384295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,19 +8734,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8763,44 +8752,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791643</v>
+        <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>86894</v>
+        <v>86981</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8810,10 +8799,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723739</v>
+        <v>723628</v>
       </c>
       <c r="R83" t="n">
-        <v>6384326</v>
+        <v>6384239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8843,74 +8832,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128784524</v>
+        <v>128791635</v>
       </c>
       <c r="B84" t="n">
-        <v>86978</v>
+        <v>86897</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723940</v>
+        <v>723782</v>
       </c>
       <c r="R84" t="n">
-        <v>6384281</v>
+        <v>6384293</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,19 +8951,18 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8973,7 +8972,7 @@
         <v>128784522</v>
       </c>
       <c r="B85" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9071,7 +9070,7 @@
         <v>128784540</v>
       </c>
       <c r="B86" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9165,45 +9164,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B87" t="n">
-        <v>86894</v>
+        <v>86981</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R87" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9244,63 +9243,64 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128791597</v>
+        <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86779</v>
+        <v>86828</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723767</v>
+        <v>723658</v>
       </c>
       <c r="R88" t="n">
-        <v>6384288</v>
+        <v>6384251</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,57 +9347,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128785775</v>
+        <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86825</v>
+        <v>86782</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723658</v>
+        <v>723767</v>
       </c>
       <c r="R89" t="n">
-        <v>6384251</v>
+        <v>6384288</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,57 +9444,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791655</v>
+        <v>128784508</v>
       </c>
       <c r="B90" t="n">
-        <v>90984</v>
+        <v>86828</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723728</v>
+        <v>723789</v>
       </c>
       <c r="R90" t="n">
-        <v>6384262</v>
+        <v>6384293</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,22 +9541,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9638,44 +9643,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791578</v>
+        <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>86825</v>
+        <v>90987</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9685,10 +9690,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723775</v>
+        <v>723728</v>
       </c>
       <c r="R92" t="n">
-        <v>6384432</v>
+        <v>6384262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9721,11 +9726,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>2 st</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9752,49 +9752,41 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>98658</v>
+        <v>87038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R93" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9824,81 +9816,78 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>87035</v>
+        <v>98661</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R94" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9928,29 +9917,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106982</v>
+        <v>106985</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107571</v>
+        <v>107574</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>86865</v>
+        <v>86868</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87172</v>
+        <v>87175</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>90290</v>
+        <v>90293</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86944</v>
+        <v>86947</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86944</v>
+        <v>86947</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>107574</v>
+        <v>90987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,57 +760,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128791651</v>
+        <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>90987</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723674</v>
+        <v>723641</v>
       </c>
       <c r="R3" t="n">
-        <v>6384225</v>
+        <v>6384196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,42 +853,46 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128784512</v>
+        <v>128784544</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>107574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6047725</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723641</v>
+        <v>723794</v>
       </c>
       <c r="R4" t="n">
-        <v>6384196</v>
+        <v>6384290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128790645</v>
+        <v>128791638</v>
       </c>
       <c r="B6" t="n">
-        <v>86828</v>
+        <v>86897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723788</v>
+        <v>723771</v>
       </c>
       <c r="R6" t="n">
-        <v>6384286</v>
+        <v>6384299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,19 +1138,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,22 +1155,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128791638</v>
+        <v>128790645</v>
       </c>
       <c r="B7" t="n">
-        <v>86897</v>
+        <v>86828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1178,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1202,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723771</v>
+        <v>723788</v>
       </c>
       <c r="R7" t="n">
-        <v>6384299</v>
+        <v>6384286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,9 +1235,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,19 +1262,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128784517</v>
+        <v>128785784</v>
       </c>
       <c r="B8" t="n">
         <v>86981</v>
@@ -1305,14 +1305,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723612</v>
+        <v>723969</v>
       </c>
       <c r="R8" t="n">
-        <v>6384274</v>
+        <v>6384430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,19 +1360,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128790574</v>
+        <v>128784517</v>
       </c>
       <c r="B9" t="n">
         <v>86981</v>
@@ -1403,14 +1403,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723609</v>
+        <v>723612</v>
       </c>
       <c r="R9" t="n">
-        <v>6384278</v>
+        <v>6384274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,19 +1440,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1468,19 +1458,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128785784</v>
+        <v>128790574</v>
       </c>
       <c r="B10" t="n">
         <v>86981</v>
@@ -1511,14 +1501,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723969</v>
+        <v>723609</v>
       </c>
       <c r="R10" t="n">
-        <v>6384430</v>
+        <v>6384278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,9 +1538,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,57 +1566,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B11" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R11" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,19 +1657,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1784,45 +1783,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791599</v>
+        <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723734</v>
+        <v>723974</v>
       </c>
       <c r="R13" t="n">
-        <v>6384367</v>
+        <v>6384345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,52 +1862,49 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>86981</v>
+        <v>87038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R14" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,85 +1945,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790583</v>
+        <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723986</v>
+        <v>723618</v>
       </c>
       <c r="R15" t="n">
-        <v>6384358</v>
+        <v>6384286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,50 +2042,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784511</v>
+        <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>88716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,19 +2082,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6047725</v>
+        <v>4379</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2128,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723600</v>
+        <v>723922</v>
       </c>
       <c r="R16" t="n">
-        <v>6384247</v>
+        <v>6384266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,30 +2168,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128791663</v>
+        <v>128790595</v>
       </c>
       <c r="B17" t="n">
-        <v>87038</v>
+        <v>86981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2221,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723971</v>
+        <v>723931</v>
       </c>
       <c r="R17" t="n">
-        <v>6384460</v>
+        <v>6384427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2254,63 +2236,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784509</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>86828</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2318,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723618</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384286</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,45 +2369,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128784506</v>
+        <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>88716</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723922</v>
+        <v>723986</v>
       </c>
       <c r="R19" t="n">
-        <v>6384266</v>
+        <v>6384358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,29 +2437,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128791624</v>
+        <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86897</v>
+        <v>86868</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248956</v>
+        <v>442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723724</v>
+        <v>723644</v>
       </c>
       <c r="R22" t="n">
-        <v>6384209</v>
+        <v>6384278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,19 +2768,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791633</v>
+        <v>128791624</v>
       </c>
       <c r="B23" t="n">
         <v>86897</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723767</v>
+        <v>723724</v>
       </c>
       <c r="R23" t="n">
-        <v>6384282</v>
+        <v>6384209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791629</v>
+        <v>128791633</v>
       </c>
       <c r="B24" t="n">
         <v>86897</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723745</v>
+        <v>723767</v>
       </c>
       <c r="R24" t="n">
-        <v>6384273</v>
+        <v>6384282</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,45 +2974,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128784553</v>
+        <v>128791629</v>
       </c>
       <c r="B25" t="n">
-        <v>98661</v>
+        <v>86897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723659</v>
+        <v>723745</v>
       </c>
       <c r="R25" t="n">
-        <v>6384257</v>
+        <v>6384273</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,57 +3059,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790581</v>
+        <v>128784553</v>
       </c>
       <c r="B26" t="n">
-        <v>86981</v>
+        <v>98661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723930</v>
+        <v>723659</v>
       </c>
       <c r="R26" t="n">
-        <v>6384314</v>
+        <v>6384257</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3139,47 +3139,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790594</v>
+        <v>128790581</v>
       </c>
       <c r="B27" t="n">
         <v>86981</v>
@@ -3214,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723948</v>
+        <v>723930</v>
       </c>
       <c r="R27" t="n">
-        <v>6384417</v>
+        <v>6384314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,7 +3238,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3259,7 +3248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3287,45 +3276,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128784550</v>
+        <v>128790594</v>
       </c>
       <c r="B28" t="n">
-        <v>86868</v>
+        <v>86981</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723644</v>
+        <v>723948</v>
       </c>
       <c r="R28" t="n">
-        <v>6384278</v>
+        <v>6384417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,74 +3344,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785781</v>
+        <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>86782</v>
+        <v>87038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723744</v>
+        <v>723660</v>
       </c>
       <c r="R29" t="n">
-        <v>6384205</v>
+        <v>6384309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3448,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,19 +3475,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
         <v>86782</v>
@@ -3512,14 +3518,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,42 +3572,46 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128790627</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>87038</v>
+        <v>86782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3609,10 +3619,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723660</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
-        <v>6384309</v>
+        <v>6384247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3642,19 +3652,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,57 +3669,53 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128791642</v>
+        <v>128785780</v>
       </c>
       <c r="B32" t="n">
-        <v>86897</v>
+        <v>92833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723745</v>
+        <v>723935</v>
       </c>
       <c r="R32" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,59 +3756,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785780</v>
+        <v>128791642</v>
       </c>
       <c r="B33" t="n">
-        <v>92833</v>
+        <v>86897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723935</v>
+        <v>723745</v>
       </c>
       <c r="R33" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3853,29 +3854,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128791631</v>
+        <v>128791566</v>
       </c>
       <c r="B34" t="n">
-        <v>86897</v>
+        <v>87038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3883,23 +3883,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3907,10 +3903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723764</v>
+        <v>723725</v>
       </c>
       <c r="R34" t="n">
-        <v>6384279</v>
+        <v>6384258</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,10 +3965,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128791566</v>
+        <v>128785776</v>
       </c>
       <c r="B35" t="n">
-        <v>87038</v>
+        <v>86828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3980,30 +3976,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723725</v>
+        <v>723727</v>
       </c>
       <c r="R35" t="n">
-        <v>6384258</v>
+        <v>6384228</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,57 +4050,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128785776</v>
+        <v>128784530</v>
       </c>
       <c r="B36" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723727</v>
+        <v>724024</v>
       </c>
       <c r="R36" t="n">
-        <v>6384228</v>
+        <v>6384488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,25 +4141,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128784530</v>
+        <v>128790577</v>
       </c>
       <c r="B37" t="n">
         <v>86981</v>
@@ -4190,14 +4191,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>724024</v>
+        <v>723815</v>
       </c>
       <c r="R37" t="n">
-        <v>6384488</v>
+        <v>6384231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,9 +4228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4245,19 +4256,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128790577</v>
+        <v>128784518</v>
       </c>
       <c r="B38" t="n">
         <v>86981</v>
@@ -4288,14 +4299,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723815</v>
+        <v>723642</v>
       </c>
       <c r="R38" t="n">
-        <v>6384231</v>
+        <v>6384222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,19 +4336,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4353,57 +4354,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B39" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R39" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,19 +4445,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128790580</v>
+        <v>128791646</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723964</v>
+        <v>723732</v>
       </c>
       <c r="R42" t="n">
-        <v>6384262</v>
+        <v>6384330</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,72 +4722,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790593</v>
+        <v>128791593</v>
       </c>
       <c r="B43" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723955</v>
+        <v>723736</v>
       </c>
       <c r="R43" t="n">
-        <v>6384354</v>
+        <v>6384250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4830,72 +4819,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790578</v>
+        <v>128791576</v>
       </c>
       <c r="B44" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723890</v>
+        <v>723743</v>
       </c>
       <c r="R44" t="n">
-        <v>6384224</v>
+        <v>6384328</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4938,72 +4916,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128791576</v>
+        <v>128790580</v>
       </c>
       <c r="B45" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723743</v>
+        <v>723964</v>
       </c>
       <c r="R45" t="n">
-        <v>6384328</v>
+        <v>6384262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5046,61 +5013,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791593</v>
+        <v>128790593</v>
       </c>
       <c r="B46" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723736</v>
+        <v>723955</v>
       </c>
       <c r="R46" t="n">
-        <v>6384250</v>
+        <v>6384354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,61 +5121,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791646</v>
+        <v>128790578</v>
       </c>
       <c r="B47" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5196,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723732</v>
+        <v>723890</v>
       </c>
       <c r="R47" t="n">
-        <v>6384330</v>
+        <v>6384224</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5240,29 +5229,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128790629</v>
+        <v>128784539</v>
       </c>
       <c r="B51" t="n">
-        <v>87038</v>
+        <v>91061</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5572,30 +5572,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723637</v>
+        <v>723615</v>
       </c>
       <c r="R51" t="n">
-        <v>6384245</v>
+        <v>6384240</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5625,19 +5629,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5652,57 +5646,53 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128784549</v>
+        <v>128790629</v>
       </c>
       <c r="B52" t="n">
-        <v>92819</v>
+        <v>87038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>433</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723958</v>
+        <v>723637</v>
       </c>
       <c r="R52" t="n">
-        <v>6384364</v>
+        <v>6384245</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5732,9 +5722,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5749,12 +5749,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5858,32 +5858,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784539</v>
+        <v>128784549</v>
       </c>
       <c r="B54" t="n">
-        <v>91061</v>
+        <v>92819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723615</v>
+        <v>723958</v>
       </c>
       <c r="R54" t="n">
-        <v>6384240</v>
+        <v>6384364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128790565</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>86806</v>
+        <v>86828</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723921</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384444</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,19 +6228,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6255,44 +6245,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784545</v>
+        <v>128784551</v>
       </c>
       <c r="B58" t="n">
-        <v>107574</v>
+        <v>98661</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>219811</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723768</v>
+        <v>723631</v>
       </c>
       <c r="R58" t="n">
-        <v>6384301</v>
+        <v>6384236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6560,45 +6550,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128785778</v>
+        <v>128784545</v>
       </c>
       <c r="B61" t="n">
-        <v>86828</v>
+        <v>107574</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>424</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723760</v>
+        <v>723768</v>
       </c>
       <c r="R61" t="n">
-        <v>6384211</v>
+        <v>6384301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6645,22 +6635,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784551</v>
+        <v>128790565</v>
       </c>
       <c r="B62" t="n">
-        <v>98661</v>
+        <v>86806</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6668,34 +6658,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219811</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723631</v>
+        <v>723921</v>
       </c>
       <c r="R62" t="n">
-        <v>6384236</v>
+        <v>6384444</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6725,9 +6715,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6742,12 +6742,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7544,45 +7544,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128791626</v>
+        <v>128785795</v>
       </c>
       <c r="B71" t="n">
-        <v>86897</v>
+        <v>90987</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>248956</v>
+        <v>3286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723741</v>
+        <v>723789</v>
       </c>
       <c r="R71" t="n">
-        <v>6384216</v>
+        <v>6384213</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7629,57 +7629,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785795</v>
+        <v>128790555</v>
       </c>
       <c r="B72" t="n">
-        <v>90987</v>
+        <v>86782</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723789</v>
+        <v>723944</v>
       </c>
       <c r="R72" t="n">
-        <v>6384213</v>
+        <v>6384278</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,39 +7709,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128790555</v>
+        <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>86782</v>
+        <v>105709</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,21 +7760,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3762</v>
+        <v>224098</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7773,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723944</v>
+        <v>723942</v>
       </c>
       <c r="R73" t="n">
-        <v>6384278</v>
+        <v>6384482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7808,7 +7819,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7818,7 +7829,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7827,7 +7838,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7943,45 +7953,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128790611</v>
+        <v>128784529</v>
       </c>
       <c r="B75" t="n">
-        <v>105709</v>
+        <v>86981</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224098</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723942</v>
+        <v>723953</v>
       </c>
       <c r="R75" t="n">
-        <v>6384482</v>
+        <v>6384442</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8011,46 +8021,37 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128784529</v>
+        <v>128790592</v>
       </c>
       <c r="B76" t="n">
         <v>86981</v>
@@ -8081,14 +8082,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723953</v>
+        <v>723955</v>
       </c>
       <c r="R76" t="n">
-        <v>6384442</v>
+        <v>6384283</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8118,9 +8119,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8136,19 +8147,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790592</v>
+        <v>128790597</v>
       </c>
       <c r="B77" t="n">
         <v>86981</v>
@@ -8183,10 +8194,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723955</v>
+        <v>723990</v>
       </c>
       <c r="R77" t="n">
-        <v>6384283</v>
+        <v>6384408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8218,7 +8229,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8228,7 +8239,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8256,32 +8267,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B78" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8291,10 +8302,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R78" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8324,40 +8335,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128785788</v>
+        <v>128791643</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>86897</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>248956</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723850</v>
+        <v>723739</v>
       </c>
       <c r="R80" t="n">
-        <v>6384251</v>
+        <v>6384326</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,57 +8557,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791643</v>
+        <v>128785788</v>
       </c>
       <c r="B81" t="n">
-        <v>86897</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>248956</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723739</v>
+        <v>723850</v>
       </c>
       <c r="R81" t="n">
-        <v>6384326</v>
+        <v>6384251</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8654,12 +8654,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8872,45 +8872,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791635</v>
+        <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>86897</v>
+        <v>99412</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>248956</v>
+        <v>222361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723782</v>
+        <v>723956</v>
       </c>
       <c r="R84" t="n">
-        <v>6384293</v>
+        <v>6384330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8957,57 +8957,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B85" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R85" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9048,29 +9048,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784540</v>
+        <v>128784524</v>
       </c>
       <c r="B86" t="n">
-        <v>99412</v>
+        <v>86981</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9078,21 +9077,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222361</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9102,10 +9101,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723956</v>
+        <v>723940</v>
       </c>
       <c r="R86" t="n">
-        <v>6384330</v>
+        <v>6384281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,6 +9145,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9164,7 +9164,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B87" t="n">
         <v>86981</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R87" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9456,7 +9456,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
         <v>86828</v>
@@ -9487,14 +9487,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9529,6 +9529,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9541,19 +9546,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
         <v>86828</v>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,12 +9643,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B2" t="n">
-        <v>90987</v>
+        <v>107574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R2" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,53 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>86981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R3" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -836,39 +840,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B4" t="n">
-        <v>107574</v>
+        <v>90987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,34 +891,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R4" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,57 +965,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B5" t="n">
-        <v>86981</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R5" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1030,40 +1041,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B11" t="n">
         <v>86782</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R11" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,74 +1646,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B12" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R12" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1754,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1771,57 +1772,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R13" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,19 +1863,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2780,45 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791624</v>
+        <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>86897</v>
+        <v>98661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723724</v>
+        <v>723659</v>
       </c>
       <c r="R23" t="n">
-        <v>6384209</v>
+        <v>6384257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,44 +2865,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791633</v>
+        <v>128790581</v>
       </c>
       <c r="B24" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723767</v>
+        <v>723930</v>
       </c>
       <c r="R24" t="n">
-        <v>6384282</v>
+        <v>6384314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,61 +2945,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791629</v>
+        <v>128790594</v>
       </c>
       <c r="B25" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3009,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723745</v>
+        <v>723948</v>
       </c>
       <c r="R25" t="n">
-        <v>6384273</v>
+        <v>6384417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,74 +3053,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128784553</v>
+        <v>128791624</v>
       </c>
       <c r="B26" t="n">
-        <v>98661</v>
+        <v>86897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723659</v>
+        <v>723724</v>
       </c>
       <c r="R26" t="n">
-        <v>6384257</v>
+        <v>6384209</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,44 +3178,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790581</v>
+        <v>128791633</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3203,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723930</v>
+        <v>723767</v>
       </c>
       <c r="R27" t="n">
-        <v>6384314</v>
+        <v>6384282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,72 +3258,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790594</v>
+        <v>128791629</v>
       </c>
       <c r="B28" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723948</v>
+        <v>723745</v>
       </c>
       <c r="R28" t="n">
-        <v>6384417</v>
+        <v>6384273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,81 +3355,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790627</v>
+        <v>128785780</v>
       </c>
       <c r="B29" t="n">
-        <v>87038</v>
+        <v>92833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723660</v>
+        <v>723935</v>
       </c>
       <c r="R29" t="n">
-        <v>6384309</v>
+        <v>6384247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,84 +3448,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128791642</v>
       </c>
       <c r="B30" t="n">
-        <v>86782</v>
+        <v>86897</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723745</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,46 +3563,42 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128790627</v>
       </c>
       <c r="B31" t="n">
-        <v>86782</v>
+        <v>87038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3619,10 +3606,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723660</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3652,9 +3639,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,22 +3666,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785780</v>
+        <v>128785781</v>
       </c>
       <c r="B32" t="n">
-        <v>92833</v>
+        <v>86782</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,19 +3689,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3712,10 +3713,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723935</v>
+        <v>723744</v>
       </c>
       <c r="R32" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,7 +3757,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3775,32 +3775,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791642</v>
+        <v>128791591</v>
       </c>
       <c r="B33" t="n">
-        <v>86897</v>
+        <v>86782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723745</v>
+        <v>723617</v>
       </c>
       <c r="R33" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>92833</v>
+        <v>86782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,30 +4474,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R40" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,29 +4542,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>86782</v>
+        <v>92833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4571,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R41" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4636,50 +4635,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791646</v>
+        <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723732</v>
+        <v>723964</v>
       </c>
       <c r="R42" t="n">
-        <v>6384330</v>
+        <v>6384262</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,61 +4722,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791593</v>
+        <v>128790593</v>
       </c>
       <c r="B43" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723736</v>
+        <v>723955</v>
       </c>
       <c r="R43" t="n">
-        <v>6384250</v>
+        <v>6384354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,61 +4830,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128791576</v>
+        <v>128790578</v>
       </c>
       <c r="B44" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4883,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723743</v>
+        <v>723890</v>
       </c>
       <c r="R44" t="n">
-        <v>6384328</v>
+        <v>6384224</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,61 +4938,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128790580</v>
+        <v>128791646</v>
       </c>
       <c r="B45" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4980,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723964</v>
+        <v>723732</v>
       </c>
       <c r="R45" t="n">
-        <v>6384262</v>
+        <v>6384330</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5013,72 +5046,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790593</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723955</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384354</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,72 +5143,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128790578</v>
+        <v>128791576</v>
       </c>
       <c r="B47" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723890</v>
+        <v>723743</v>
       </c>
       <c r="R47" t="n">
-        <v>6384224</v>
+        <v>6384328</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5229,85 +5240,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B48" t="n">
-        <v>86828</v>
+        <v>106985</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R48" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B49" t="n">
-        <v>106985</v>
+        <v>86828</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R49" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128785778</v>
+        <v>128790565</v>
       </c>
       <c r="B57" t="n">
-        <v>86828</v>
+        <v>86806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723760</v>
+        <v>723921</v>
       </c>
       <c r="R57" t="n">
-        <v>6384211</v>
+        <v>6384444</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,9 +6228,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6245,57 +6255,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784551</v>
+        <v>128785778</v>
       </c>
       <c r="B58" t="n">
-        <v>98661</v>
+        <v>86828</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219811</v>
+        <v>424</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723631</v>
+        <v>723760</v>
       </c>
       <c r="R58" t="n">
-        <v>6384236</v>
+        <v>6384211</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6342,44 +6352,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784526</v>
+        <v>128784551</v>
       </c>
       <c r="B59" t="n">
-        <v>86981</v>
+        <v>98661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6389,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723962</v>
+        <v>723631</v>
       </c>
       <c r="R59" t="n">
-        <v>6384357</v>
+        <v>6384236</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,7 +6443,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6452,7 +6461,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784523</v>
+        <v>128784526</v>
       </c>
       <c r="B60" t="n">
         <v>86981</v>
@@ -6487,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723878</v>
+        <v>723962</v>
       </c>
       <c r="R60" t="n">
-        <v>6384241</v>
+        <v>6384357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6550,10 +6559,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784545</v>
+        <v>128784523</v>
       </c>
       <c r="B61" t="n">
-        <v>107574</v>
+        <v>86981</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6561,21 +6570,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6585,10 +6594,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723768</v>
+        <v>723878</v>
       </c>
       <c r="R61" t="n">
-        <v>6384301</v>
+        <v>6384241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6629,6 +6638,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6647,45 +6657,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128790565</v>
+        <v>128784545</v>
       </c>
       <c r="B62" t="n">
-        <v>86806</v>
+        <v>107574</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723921</v>
+        <v>723768</v>
       </c>
       <c r="R62" t="n">
-        <v>6384444</v>
+        <v>6384301</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,19 +6725,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6742,12 +6742,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791643</v>
+        <v>128784519</v>
       </c>
       <c r="B80" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723739</v>
+        <v>723763</v>
       </c>
       <c r="R80" t="n">
-        <v>6384326</v>
+        <v>6384295</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,63 +8551,64 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128785788</v>
+        <v>128790576</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>86981</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723850</v>
+        <v>723628</v>
       </c>
       <c r="R81" t="n">
-        <v>6384251</v>
+        <v>6384239</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8637,74 +8638,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128784519</v>
+        <v>128791643</v>
       </c>
       <c r="B82" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723763</v>
+        <v>723739</v>
       </c>
       <c r="R82" t="n">
-        <v>6384295</v>
+        <v>6384326</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8745,64 +8757,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128790576</v>
+        <v>128785788</v>
       </c>
       <c r="B83" t="n">
-        <v>86981</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723628</v>
+        <v>723850</v>
       </c>
       <c r="R83" t="n">
-        <v>6384239</v>
+        <v>6384251</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,40 +8843,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9752,41 +9752,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B93" t="n">
-        <v>87038</v>
+        <v>98661</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R93" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9816,78 +9824,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B94" t="n">
-        <v>98661</v>
+        <v>87038</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R94" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9917,40 +9928,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11140,45 +11140,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128790561</v>
+        <v>128790618</v>
       </c>
       <c r="B106" t="n">
-        <v>90293</v>
+        <v>86897</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723960</v>
+        <v>723602</v>
       </c>
       <c r="R106" t="n">
-        <v>6384272</v>
+        <v>6384277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11210,7 +11213,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11220,7 +11223,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11248,48 +11256,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128790618</v>
+        <v>128790561</v>
       </c>
       <c r="B107" t="n">
-        <v>86897</v>
+        <v>90293</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723602</v>
+        <v>723960</v>
       </c>
       <c r="R107" t="n">
-        <v>6384277</v>
+        <v>6384272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11321,7 +11326,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11331,12 +11336,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>107574</v>
+        <v>90987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,57 +760,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128790598</v>
+        <v>128784512</v>
       </c>
       <c r="B3" t="n">
-        <v>86981</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723992</v>
+        <v>723641</v>
       </c>
       <c r="R3" t="n">
-        <v>6384372</v>
+        <v>6384196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,50 +836,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128791651</v>
+        <v>128784544</v>
       </c>
       <c r="B4" t="n">
-        <v>90987</v>
+        <v>107574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,34 +876,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723674</v>
+        <v>723794</v>
       </c>
       <c r="R4" t="n">
-        <v>6384225</v>
+        <v>6384290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,53 +950,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>86981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R5" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,74 +1030,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128791638</v>
+        <v>128785784</v>
       </c>
       <c r="B6" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723771</v>
+        <v>723969</v>
       </c>
       <c r="R6" t="n">
-        <v>6384299</v>
+        <v>6384430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,28 +1149,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128790645</v>
+        <v>128791638</v>
       </c>
       <c r="B7" t="n">
-        <v>86828</v>
+        <v>86897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1178,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1202,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723788</v>
+        <v>723771</v>
       </c>
       <c r="R7" t="n">
-        <v>6384286</v>
+        <v>6384299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,19 +1236,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,19 +1253,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128785784</v>
+        <v>128784517</v>
       </c>
       <c r="B8" t="n">
         <v>86981</v>
@@ -1305,14 +1296,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723969</v>
+        <v>723612</v>
       </c>
       <c r="R8" t="n">
-        <v>6384430</v>
+        <v>6384274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,19 +1351,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128784517</v>
+        <v>128790574</v>
       </c>
       <c r="B9" t="n">
         <v>86981</v>
@@ -1403,14 +1394,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723612</v>
+        <v>723609</v>
       </c>
       <c r="R9" t="n">
-        <v>6384274</v>
+        <v>6384278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,9 +1431,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1458,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790574</v>
+        <v>128790645</v>
       </c>
       <c r="B10" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723609</v>
+        <v>723788</v>
       </c>
       <c r="R10" t="n">
-        <v>6384278</v>
+        <v>6384286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,7 +1541,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1550,7 +1551,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,45 +1686,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R12" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,64 +1765,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791599</v>
+        <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723734</v>
+        <v>723974</v>
       </c>
       <c r="R13" t="n">
-        <v>6384367</v>
+        <v>6384345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,48 +1862,53 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791663</v>
+        <v>128790595</v>
       </c>
       <c r="B14" t="n">
-        <v>87038</v>
+        <v>86981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723971</v>
+        <v>723931</v>
       </c>
       <c r="R14" t="n">
-        <v>6384460</v>
+        <v>6384427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,74 +1949,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784509</v>
+        <v>128790583</v>
       </c>
       <c r="B15" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723618</v>
+        <v>723986</v>
       </c>
       <c r="R15" t="n">
-        <v>6384286</v>
+        <v>6384358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,39 +2057,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784506</v>
+        <v>128784511</v>
       </c>
       <c r="B16" t="n">
-        <v>88716</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,23 +2108,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4379</v>
+        <v>6047725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2106,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723922</v>
+        <v>723600</v>
       </c>
       <c r="R16" t="n">
-        <v>6384266</v>
+        <v>6384247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,34 +2190,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790595</v>
+        <v>128791663</v>
       </c>
       <c r="B17" t="n">
-        <v>86981</v>
+        <v>87038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2203,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723931</v>
+        <v>723971</v>
       </c>
       <c r="R17" t="n">
-        <v>6384427</v>
+        <v>6384460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,70 +2254,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784511</v>
+        <v>128784509</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>86828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723600</v>
+        <v>723618</v>
       </c>
       <c r="R18" t="n">
-        <v>6384247</v>
+        <v>6384286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,45 +2380,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790583</v>
+        <v>128784506</v>
       </c>
       <c r="B19" t="n">
-        <v>86981</v>
+        <v>88716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723986</v>
+        <v>723922</v>
       </c>
       <c r="R19" t="n">
-        <v>6384358</v>
+        <v>6384266</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,40 +2448,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2877,32 +2877,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790581</v>
+        <v>128791624</v>
       </c>
       <c r="B24" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723930</v>
+        <v>723724</v>
       </c>
       <c r="R24" t="n">
-        <v>6384314</v>
+        <v>6384209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,47 +2945,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790594</v>
+        <v>128790581</v>
       </c>
       <c r="B25" t="n">
         <v>86981</v>
@@ -3020,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723948</v>
+        <v>723930</v>
       </c>
       <c r="R25" t="n">
-        <v>6384417</v>
+        <v>6384314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3055,7 +3044,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3065,7 +3054,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,7 +3082,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791624</v>
+        <v>128791633</v>
       </c>
       <c r="B26" t="n">
         <v>86897</v>
@@ -3128,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723724</v>
+        <v>723767</v>
       </c>
       <c r="R26" t="n">
-        <v>6384209</v>
+        <v>6384282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,32 +3179,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128791633</v>
+        <v>128790594</v>
       </c>
       <c r="B27" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723767</v>
+        <v>723948</v>
       </c>
       <c r="R27" t="n">
-        <v>6384282</v>
+        <v>6384417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,29 +3247,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785780</v>
+        <v>128785781</v>
       </c>
       <c r="B29" t="n">
-        <v>92833</v>
+        <v>86782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,19 +3395,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3415,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723935</v>
+        <v>723744</v>
       </c>
       <c r="R29" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,7 +3463,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3478,32 +3481,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791642</v>
+        <v>128791591</v>
       </c>
       <c r="B30" t="n">
-        <v>86897</v>
+        <v>86782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3513,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723745</v>
+        <v>723617</v>
       </c>
       <c r="R30" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,45 +3681,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785781</v>
+        <v>128791642</v>
       </c>
       <c r="B32" t="n">
-        <v>86782</v>
+        <v>86897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723744</v>
+        <v>723745</v>
       </c>
       <c r="R32" t="n">
-        <v>6384205</v>
+        <v>6384321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,22 +3766,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128791591</v>
+        <v>128785780</v>
       </c>
       <c r="B33" t="n">
-        <v>86782</v>
+        <v>92833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3786,31 +3789,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723617</v>
+        <v>723935</v>
       </c>
       <c r="R33" t="n">
         <v>6384247</v>
@@ -3854,18 +3853,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4268,45 +4268,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128784518</v>
+        <v>128791631</v>
       </c>
       <c r="B38" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723642</v>
+        <v>723764</v>
       </c>
       <c r="R38" t="n">
-        <v>6384222</v>
+        <v>6384279</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,64 +4347,63 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128791631</v>
+        <v>128784518</v>
       </c>
       <c r="B39" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723764</v>
+        <v>723642</v>
       </c>
       <c r="R39" t="n">
-        <v>6384279</v>
+        <v>6384222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,28 +4444,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B40" t="n">
-        <v>86782</v>
+        <v>92833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,34 +4474,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R40" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,28 +4538,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B41" t="n">
-        <v>92833</v>
+        <v>86782</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,30 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R41" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,51 +4636,50 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128790580</v>
+        <v>128791576</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723964</v>
+        <v>723743</v>
       </c>
       <c r="R42" t="n">
-        <v>6384262</v>
+        <v>6384328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,72 +4722,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128790593</v>
+        <v>128791593</v>
       </c>
       <c r="B43" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723955</v>
+        <v>723736</v>
       </c>
       <c r="R43" t="n">
-        <v>6384354</v>
+        <v>6384250</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4830,47 +4819,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790578</v>
+        <v>128790580</v>
       </c>
       <c r="B44" t="n">
         <v>86981</v>
@@ -4905,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723890</v>
+        <v>723964</v>
       </c>
       <c r="R44" t="n">
-        <v>6384224</v>
+        <v>6384262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4940,7 +4918,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4950,7 +4928,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791593</v>
+        <v>128790593</v>
       </c>
       <c r="B46" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723736</v>
+        <v>723955</v>
       </c>
       <c r="R46" t="n">
-        <v>6384250</v>
+        <v>6384354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,61 +5121,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791576</v>
+        <v>128790578</v>
       </c>
       <c r="B47" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5196,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723743</v>
+        <v>723890</v>
       </c>
       <c r="R47" t="n">
-        <v>6384328</v>
+        <v>6384224</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5240,74 +5229,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>106985</v>
+        <v>86828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86828</v>
+        <v>106985</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5561,32 +5561,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784539</v>
+        <v>128784554</v>
       </c>
       <c r="B51" t="n">
-        <v>91061</v>
+        <v>98661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>219811</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723615</v>
+        <v>723982</v>
       </c>
       <c r="R51" t="n">
-        <v>6384240</v>
+        <v>6384442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5858,32 +5858,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784549</v>
+        <v>128784539</v>
       </c>
       <c r="B54" t="n">
-        <v>92819</v>
+        <v>91061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723958</v>
+        <v>723615</v>
       </c>
       <c r="R54" t="n">
-        <v>6384364</v>
+        <v>6384240</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128784554</v>
+        <v>128784549</v>
       </c>
       <c r="B55" t="n">
-        <v>98661</v>
+        <v>92819</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219811</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723982</v>
+        <v>723958</v>
       </c>
       <c r="R55" t="n">
-        <v>6384442</v>
+        <v>6384364</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128790565</v>
+        <v>128784526</v>
       </c>
       <c r="B57" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723921</v>
+        <v>723962</v>
       </c>
       <c r="R57" t="n">
-        <v>6384444</v>
+        <v>6384357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6228,84 +6228,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128785778</v>
+        <v>128784523</v>
       </c>
       <c r="B58" t="n">
-        <v>86828</v>
+        <v>86981</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723760</v>
+        <v>723878</v>
       </c>
       <c r="R58" t="n">
-        <v>6384211</v>
+        <v>6384241</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6346,50 +6337,51 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784551</v>
+        <v>128784545</v>
       </c>
       <c r="B59" t="n">
-        <v>98661</v>
+        <v>107574</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723631</v>
+        <v>723768</v>
       </c>
       <c r="R59" t="n">
-        <v>6384236</v>
+        <v>6384301</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6453,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784526</v>
+        <v>128784551</v>
       </c>
       <c r="B60" t="n">
-        <v>86981</v>
+        <v>98661</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6488,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723962</v>
+        <v>723631</v>
       </c>
       <c r="R60" t="n">
-        <v>6384357</v>
+        <v>6384236</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6540,7 +6532,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6559,45 +6550,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784523</v>
+        <v>128785778</v>
       </c>
       <c r="B61" t="n">
-        <v>86981</v>
+        <v>86828</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723878</v>
+        <v>723760</v>
       </c>
       <c r="R61" t="n">
-        <v>6384241</v>
+        <v>6384211</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6638,64 +6629,63 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784545</v>
+        <v>128790565</v>
       </c>
       <c r="B62" t="n">
-        <v>107574</v>
+        <v>86806</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723768</v>
+        <v>723921</v>
       </c>
       <c r="R62" t="n">
-        <v>6384301</v>
+        <v>6384444</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6725,9 +6715,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6742,57 +6742,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128790556</v>
+        <v>128785779</v>
       </c>
       <c r="B63" t="n">
-        <v>86782</v>
+        <v>86828</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723703</v>
+        <v>723790</v>
       </c>
       <c r="R63" t="n">
-        <v>6384275</v>
+        <v>6384287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6822,19 +6822,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6849,19 +6839,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791601</v>
+        <v>128790556</v>
       </c>
       <c r="B64" t="n">
         <v>86782</v>
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723723</v>
+        <v>723703</v>
       </c>
       <c r="R64" t="n">
-        <v>6384387</v>
+        <v>6384275</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6929,9 +6919,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6946,57 +6946,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128785779</v>
+        <v>128791601</v>
       </c>
       <c r="B65" t="n">
-        <v>86828</v>
+        <v>86782</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723790</v>
+        <v>723723</v>
       </c>
       <c r="R65" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,12 +7043,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8159,32 +8159,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128790597</v>
+        <v>128791626</v>
       </c>
       <c r="B77" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723990</v>
+        <v>723741</v>
       </c>
       <c r="R77" t="n">
-        <v>6384408</v>
+        <v>6384216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8227,72 +8227,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791626</v>
+        <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8302,10 +8291,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723741</v>
+        <v>723990</v>
       </c>
       <c r="R78" t="n">
-        <v>6384216</v>
+        <v>6384408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,29 +8324,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8472,45 +8472,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128784519</v>
+        <v>128785788</v>
       </c>
       <c r="B80" t="n">
-        <v>86981</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723763</v>
+        <v>723850</v>
       </c>
       <c r="R80" t="n">
-        <v>6384295</v>
+        <v>6384251</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,26 +8551,25 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128790576</v>
+        <v>128784519</v>
       </c>
       <c r="B81" t="n">
         <v>86981</v>
@@ -8601,14 +8600,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723628</v>
+        <v>723763</v>
       </c>
       <c r="R81" t="n">
-        <v>6384239</v>
+        <v>6384295</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,19 +8637,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8666,12 +8655,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8775,45 +8764,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128785788</v>
+        <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>86981</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723850</v>
+        <v>723628</v>
       </c>
       <c r="R83" t="n">
-        <v>6384251</v>
+        <v>6384239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8843,29 +8832,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8969,45 +8969,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791635</v>
+        <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86897</v>
+        <v>86981</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723782</v>
+        <v>723940</v>
       </c>
       <c r="R85" t="n">
-        <v>6384293</v>
+        <v>6384281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9048,25 +9048,26 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128784524</v>
+        <v>128784522</v>
       </c>
       <c r="B86" t="n">
         <v>86981</v>
@@ -9101,10 +9102,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723940</v>
+        <v>723865</v>
       </c>
       <c r="R86" t="n">
-        <v>6384281</v>
+        <v>6384223</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9164,45 +9165,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128784522</v>
+        <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86981</v>
+        <v>86897</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723865</v>
+        <v>723782</v>
       </c>
       <c r="R87" t="n">
-        <v>6384223</v>
+        <v>6384293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9243,19 +9244,18 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9456,32 +9456,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791578</v>
+        <v>128791655</v>
       </c>
       <c r="B90" t="n">
-        <v>86828</v>
+        <v>90987</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723775</v>
+        <v>723728</v>
       </c>
       <c r="R90" t="n">
-        <v>6384432</v>
+        <v>6384262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,11 +9527,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9558,7 +9553,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784508</v>
+        <v>128791578</v>
       </c>
       <c r="B91" t="n">
         <v>86828</v>
@@ -9589,14 +9584,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723789</v>
+        <v>723775</v>
       </c>
       <c r="R91" t="n">
-        <v>6384293</v>
+        <v>6384432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9631,6 +9626,11 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791655</v>
+        <v>128784508</v>
       </c>
       <c r="B92" t="n">
-        <v>90987</v>
+        <v>86828</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723728</v>
+        <v>723789</v>
       </c>
       <c r="R92" t="n">
-        <v>6384262</v>
+        <v>6384293</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,61 +9740,53 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>98661</v>
+        <v>87038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R93" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9824,81 +9816,78 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>87038</v>
+        <v>98661</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R94" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9928,29 +9917,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128791651</v>
+        <v>128784512</v>
       </c>
       <c r="B2" t="n">
-        <v>90987</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723674</v>
+        <v>723641</v>
       </c>
       <c r="R2" t="n">
-        <v>6384225</v>
+        <v>6384196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,53 +756,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128784512</v>
+        <v>128790598</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>86985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723641</v>
+        <v>723992</v>
       </c>
       <c r="R3" t="n">
-        <v>6384196</v>
+        <v>6384372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -836,39 +836,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128784544</v>
+        <v>128791651</v>
       </c>
       <c r="B4" t="n">
-        <v>107574</v>
+        <v>90991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,34 +887,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723794</v>
+        <v>723674</v>
       </c>
       <c r="R4" t="n">
-        <v>6384290</v>
+        <v>6384225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,22 +961,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128790598</v>
+        <v>128784544</v>
       </c>
       <c r="B5" t="n">
-        <v>86981</v>
+        <v>107584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,34 +984,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723992</v>
+        <v>723794</v>
       </c>
       <c r="R5" t="n">
-        <v>6384372</v>
+        <v>6384290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1030,85 +1041,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128785784</v>
+        <v>128790645</v>
       </c>
       <c r="B6" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723969</v>
+        <v>723788</v>
       </c>
       <c r="R6" t="n">
-        <v>6384430</v>
+        <v>6384286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,75 +1138,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128791638</v>
+        <v>128784517</v>
       </c>
       <c r="B7" t="n">
-        <v>86897</v>
+        <v>86985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723771</v>
+        <v>723612</v>
       </c>
       <c r="R7" t="n">
-        <v>6384299</v>
+        <v>6384274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,28 +1256,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128784517</v>
+        <v>128785784</v>
       </c>
       <c r="B8" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,14 +1306,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723612</v>
+        <v>723969</v>
       </c>
       <c r="R8" t="n">
-        <v>6384274</v>
+        <v>6384430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,44 +1361,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128790574</v>
+        <v>128791638</v>
       </c>
       <c r="B9" t="n">
-        <v>86981</v>
+        <v>86901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723609</v>
+        <v>723771</v>
       </c>
       <c r="R9" t="n">
-        <v>6384278</v>
+        <v>6384299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,72 +1441,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790645</v>
+        <v>128790574</v>
       </c>
       <c r="B10" t="n">
-        <v>86828</v>
+        <v>86985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723788</v>
+        <v>723609</v>
       </c>
       <c r="R10" t="n">
-        <v>6384286</v>
+        <v>6384278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,7 +1540,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1551,7 +1550,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1560,6 +1559,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>128790554</v>
       </c>
       <c r="B11" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128791599</v>
       </c>
       <c r="B12" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128785783</v>
       </c>
       <c r="B13" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,45 +1881,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790595</v>
+        <v>128784506</v>
       </c>
       <c r="B14" t="n">
-        <v>86981</v>
+        <v>88720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>4379</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723931</v>
+        <v>723922</v>
       </c>
       <c r="R14" t="n">
-        <v>6384427</v>
+        <v>6384266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,85 +1949,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790583</v>
+        <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723986</v>
+        <v>723618</v>
       </c>
       <c r="R15" t="n">
-        <v>6384358</v>
+        <v>6384286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,81 +2046,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784511</v>
+        <v>128791663</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>87042</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723600</v>
+        <v>723971</v>
       </c>
       <c r="R16" t="n">
-        <v>6384247</v>
+        <v>6384460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,53 +2156,53 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128791663</v>
+        <v>128784511</v>
       </c>
       <c r="B17" t="n">
-        <v>87038</v>
+        <v>92840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723971</v>
+        <v>723600</v>
       </c>
       <c r="R17" t="n">
-        <v>6384460</v>
+        <v>6384247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,57 +2249,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128784509</v>
+        <v>128790595</v>
       </c>
       <c r="B18" t="n">
-        <v>86828</v>
+        <v>86985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723618</v>
+        <v>723931</v>
       </c>
       <c r="R18" t="n">
-        <v>6384286</v>
+        <v>6384427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,74 +2329,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128784506</v>
+        <v>128790583</v>
       </c>
       <c r="B19" t="n">
-        <v>88716</v>
+        <v>86985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4379</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723922</v>
+        <v>723986</v>
       </c>
       <c r="R19" t="n">
-        <v>6384266</v>
+        <v>6384358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,29 +2437,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>128784520</v>
       </c>
       <c r="B20" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128790590</v>
       </c>
       <c r="B21" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>128784550</v>
       </c>
       <c r="B22" t="n">
-        <v>86868</v>
+        <v>86872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>128784553</v>
       </c>
       <c r="B23" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>128791624</v>
       </c>
       <c r="B24" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>128790581</v>
       </c>
       <c r="B25" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>128791633</v>
       </c>
       <c r="B26" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>128790594</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128791629</v>
       </c>
       <c r="B28" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,45 +3384,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785781</v>
+        <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>86782</v>
+        <v>87042</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723744</v>
+        <v>723660</v>
       </c>
       <c r="R29" t="n">
-        <v>6384205</v>
+        <v>6384309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,9 +3448,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,22 +3475,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B30" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,14 +3518,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R30" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,42 +3572,46 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128790627</v>
+        <v>128791591</v>
       </c>
       <c r="B31" t="n">
-        <v>87038</v>
+        <v>86786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>433</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3609,10 +3619,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723660</v>
+        <v>723617</v>
       </c>
       <c r="R31" t="n">
-        <v>6384309</v>
+        <v>6384247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3642,19 +3652,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3669,57 +3669,53 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128791642</v>
+        <v>128785780</v>
       </c>
       <c r="B32" t="n">
-        <v>86897</v>
+        <v>92840</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>6047725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723745</v>
+        <v>723935</v>
       </c>
       <c r="R32" t="n">
-        <v>6384321</v>
+        <v>6384247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,59 +3756,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785780</v>
+        <v>128791642</v>
       </c>
       <c r="B33" t="n">
-        <v>92833</v>
+        <v>86901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723935</v>
+        <v>723745</v>
       </c>
       <c r="R33" t="n">
-        <v>6384247</v>
+        <v>6384321</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3853,60 +3854,63 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128791566</v>
+        <v>128784530</v>
       </c>
       <c r="B34" t="n">
-        <v>87038</v>
+        <v>86985</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723725</v>
+        <v>724024</v>
       </c>
       <c r="R34" t="n">
-        <v>6384258</v>
+        <v>6384488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3947,63 +3951,64 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128785776</v>
+        <v>128790577</v>
       </c>
       <c r="B35" t="n">
-        <v>86828</v>
+        <v>86985</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723727</v>
+        <v>723815</v>
       </c>
       <c r="R35" t="n">
-        <v>6384228</v>
+        <v>6384231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4033,74 +4038,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128784530</v>
+        <v>128791631</v>
       </c>
       <c r="B36" t="n">
-        <v>86981</v>
+        <v>86901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>724024</v>
+        <v>723764</v>
       </c>
       <c r="R36" t="n">
-        <v>6384488</v>
+        <v>6384279</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,29 +4157,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128790577</v>
+        <v>128784518</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,14 +4206,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723815</v>
+        <v>723642</v>
       </c>
       <c r="R37" t="n">
-        <v>6384231</v>
+        <v>6384222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,19 +4243,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4256,22 +4261,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128791631</v>
+        <v>128791566</v>
       </c>
       <c r="B38" t="n">
-        <v>86897</v>
+        <v>87042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4279,23 +4284,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4303,10 +4304,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723764</v>
+        <v>723725</v>
       </c>
       <c r="R38" t="n">
-        <v>6384279</v>
+        <v>6384258</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4365,45 +4366,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128784518</v>
+        <v>128785776</v>
       </c>
       <c r="B39" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723642</v>
+        <v>723727</v>
       </c>
       <c r="R39" t="n">
-        <v>6384222</v>
+        <v>6384228</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,29 +4445,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B40" t="n">
-        <v>92833</v>
+        <v>86786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,30 +4474,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R40" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,29 +4542,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B41" t="n">
-        <v>86782</v>
+        <v>92840</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4571,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R41" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4636,50 +4635,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128791576</v>
+        <v>128790580</v>
       </c>
       <c r="B42" t="n">
-        <v>86828</v>
+        <v>86985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723743</v>
+        <v>723964</v>
       </c>
       <c r="R42" t="n">
-        <v>6384328</v>
+        <v>6384262</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,61 +4722,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128791593</v>
+        <v>128791646</v>
       </c>
       <c r="B43" t="n">
-        <v>86782</v>
+        <v>86901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723736</v>
+        <v>723732</v>
       </c>
       <c r="R43" t="n">
-        <v>6384250</v>
+        <v>6384330</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,10 +4859,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790580</v>
+        <v>128790593</v>
       </c>
       <c r="B44" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723964</v>
+        <v>723955</v>
       </c>
       <c r="R44" t="n">
-        <v>6384262</v>
+        <v>6384354</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4918,7 +4929,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4928,7 +4939,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4967,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128791646</v>
+        <v>128790578</v>
       </c>
       <c r="B45" t="n">
-        <v>86897</v>
+        <v>86985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +5002,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723732</v>
+        <v>723890</v>
       </c>
       <c r="R45" t="n">
-        <v>6384330</v>
+        <v>6384224</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5024,61 +5035,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128790593</v>
+        <v>128791576</v>
       </c>
       <c r="B46" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723955</v>
+        <v>723743</v>
       </c>
       <c r="R46" t="n">
-        <v>6384354</v>
+        <v>6384328</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,72 +5143,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128790578</v>
+        <v>128791593</v>
       </c>
       <c r="B47" t="n">
-        <v>86981</v>
+        <v>86786</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723890</v>
+        <v>723736</v>
       </c>
       <c r="R47" t="n">
-        <v>6384224</v>
+        <v>6384250</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5229,85 +5240,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B48" t="n">
-        <v>86828</v>
+        <v>106995</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R48" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B49" t="n">
-        <v>106985</v>
+        <v>86832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R49" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
         <v>128784521</v>
       </c>
       <c r="B50" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,45 +5561,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128784554</v>
+        <v>128790629</v>
       </c>
       <c r="B51" t="n">
-        <v>98661</v>
+        <v>87042</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723982</v>
+        <v>723637</v>
       </c>
       <c r="R51" t="n">
-        <v>6384442</v>
+        <v>6384245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,9 +5625,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5646,42 +5652,46 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128790629</v>
+        <v>128791648</v>
       </c>
       <c r="B52" t="n">
-        <v>87038</v>
+        <v>90991</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>433</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5689,10 +5699,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723637</v>
+        <v>723664</v>
       </c>
       <c r="R52" t="n">
-        <v>6384245</v>
+        <v>6384233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,19 +5732,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5749,57 +5749,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128791648</v>
+        <v>128784554</v>
       </c>
       <c r="B53" t="n">
-        <v>90987</v>
+        <v>98671</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3286</v>
+        <v>219811</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723664</v>
+        <v>723982</v>
       </c>
       <c r="R53" t="n">
-        <v>6384233</v>
+        <v>6384442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,57 +5846,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128784539</v>
+        <v>128790589</v>
       </c>
       <c r="B54" t="n">
-        <v>91061</v>
+        <v>86985</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723615</v>
+        <v>723770</v>
       </c>
       <c r="R54" t="n">
-        <v>6384240</v>
+        <v>6384248</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,29 +5926,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5958,7 +5969,7 @@
         <v>128784549</v>
       </c>
       <c r="B55" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6052,45 +6063,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128790589</v>
+        <v>128784539</v>
       </c>
       <c r="B56" t="n">
-        <v>86981</v>
+        <v>91065</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723770</v>
+        <v>723615</v>
       </c>
       <c r="R56" t="n">
-        <v>6384248</v>
+        <v>6384240</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6120,50 +6131,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128784526</v>
+        <v>128784545</v>
       </c>
       <c r="B57" t="n">
-        <v>86981</v>
+        <v>107584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6171,21 +6171,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723962</v>
+        <v>723768</v>
       </c>
       <c r="R57" t="n">
-        <v>6384357</v>
+        <v>6384301</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,7 +6239,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6258,32 +6257,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784523</v>
+        <v>128784551</v>
       </c>
       <c r="B58" t="n">
-        <v>86981</v>
+        <v>98671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6293,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723878</v>
+        <v>723631</v>
       </c>
       <c r="R58" t="n">
-        <v>6384241</v>
+        <v>6384236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,7 +6336,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6356,10 +6354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784545</v>
+        <v>128784526</v>
       </c>
       <c r="B59" t="n">
-        <v>107574</v>
+        <v>86985</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6367,21 +6365,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6391,10 +6389,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723768</v>
+        <v>723962</v>
       </c>
       <c r="R59" t="n">
-        <v>6384301</v>
+        <v>6384357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6435,6 +6433,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6453,32 +6452,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784551</v>
+        <v>128784523</v>
       </c>
       <c r="B60" t="n">
-        <v>98661</v>
+        <v>86985</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6488,10 +6487,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723631</v>
+        <v>723878</v>
       </c>
       <c r="R60" t="n">
-        <v>6384236</v>
+        <v>6384241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6532,6 +6531,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>128785778</v>
       </c>
       <c r="B61" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>128790565</v>
       </c>
       <c r="B62" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6754,45 +6754,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128785779</v>
+        <v>128791601</v>
       </c>
       <c r="B63" t="n">
-        <v>86828</v>
+        <v>86786</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723790</v>
+        <v>723723</v>
       </c>
       <c r="R63" t="n">
-        <v>6384287</v>
+        <v>6384387</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6839,57 +6839,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128790556</v>
+        <v>128784525</v>
       </c>
       <c r="B64" t="n">
-        <v>86782</v>
+        <v>86985</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723703</v>
+        <v>723945</v>
       </c>
       <c r="R64" t="n">
-        <v>6384275</v>
+        <v>6384300</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6919,84 +6919,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791601</v>
+        <v>128784516</v>
       </c>
       <c r="B65" t="n">
-        <v>86782</v>
+        <v>86985</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723723</v>
+        <v>723922</v>
       </c>
       <c r="R65" t="n">
-        <v>6384387</v>
+        <v>6384267</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7037,28 +7028,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128784525</v>
+        <v>128784527</v>
       </c>
       <c r="B66" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7090,10 +7082,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723945</v>
+        <v>723949</v>
       </c>
       <c r="R66" t="n">
-        <v>6384300</v>
+        <v>6384442</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,10 +7145,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128784516</v>
+        <v>128785782</v>
       </c>
       <c r="B67" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7184,14 +7176,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723922</v>
+        <v>723777</v>
       </c>
       <c r="R67" t="n">
-        <v>6384267</v>
+        <v>6384287</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,57 +7231,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128784527</v>
+        <v>128785779</v>
       </c>
       <c r="B68" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723949</v>
+        <v>723790</v>
       </c>
       <c r="R68" t="n">
-        <v>6384442</v>
+        <v>6384287</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7330,64 +7322,63 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128785782</v>
+        <v>128790556</v>
       </c>
       <c r="B69" t="n">
-        <v>86981</v>
+        <v>86786</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723777</v>
+        <v>723703</v>
       </c>
       <c r="R69" t="n">
-        <v>6384287</v>
+        <v>6384275</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7417,30 +7408,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7450,7 +7450,7 @@
         <v>128784510</v>
       </c>
       <c r="B70" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>128785795</v>
       </c>
       <c r="B71" t="n">
-        <v>90987</v>
+        <v>90991</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128790555</v>
+        <v>128784542</v>
       </c>
       <c r="B72" t="n">
-        <v>86782</v>
+        <v>105719</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7652,34 +7652,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>224098</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723944</v>
+        <v>723833</v>
       </c>
       <c r="R72" t="n">
-        <v>6384278</v>
+        <v>6384211</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7709,40 +7709,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7752,7 +7741,7 @@
         <v>128790611</v>
       </c>
       <c r="B73" t="n">
-        <v>105709</v>
+        <v>105719</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7856,10 +7845,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128784542</v>
+        <v>128790555</v>
       </c>
       <c r="B74" t="n">
-        <v>105709</v>
+        <v>86786</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7867,34 +7856,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224098</v>
+        <v>3762</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723833</v>
+        <v>723944</v>
       </c>
       <c r="R74" t="n">
-        <v>6384211</v>
+        <v>6384278</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7924,29 +7913,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
         <v>128784529</v>
       </c>
       <c r="B75" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>128790592</v>
       </c>
       <c r="B76" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>128791626</v>
       </c>
       <c r="B77" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128790597</v>
       </c>
       <c r="B78" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>128790588</v>
       </c>
       <c r="B79" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>128784519</v>
       </c>
       <c r="B81" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>128791643</v>
       </c>
       <c r="B82" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>128790576</v>
       </c>
       <c r="B83" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>128784540</v>
       </c>
       <c r="B84" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>128784524</v>
       </c>
       <c r="B85" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>128784522</v>
       </c>
       <c r="B86" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>128791635</v>
       </c>
       <c r="B87" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>128785775</v>
       </c>
       <c r="B88" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128791597</v>
       </c>
       <c r="B89" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9456,32 +9456,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791655</v>
+        <v>128791578</v>
       </c>
       <c r="B90" t="n">
-        <v>90987</v>
+        <v>86832</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723728</v>
+        <v>723775</v>
       </c>
       <c r="R90" t="n">
-        <v>6384262</v>
+        <v>6384432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9527,6 +9527,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9553,10 +9558,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791578</v>
+        <v>128784508</v>
       </c>
       <c r="B91" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,14 +9589,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723775</v>
+        <v>723789</v>
       </c>
       <c r="R91" t="n">
-        <v>6384432</v>
+        <v>6384293</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,11 +9631,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>2 st</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9643,57 +9643,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784508</v>
+        <v>128791655</v>
       </c>
       <c r="B92" t="n">
-        <v>86828</v>
+        <v>90991</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723789</v>
+        <v>723728</v>
       </c>
       <c r="R92" t="n">
-        <v>6384293</v>
+        <v>6384262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9740,53 +9740,61 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B93" t="n">
-        <v>87038</v>
+        <v>98671</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R93" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9816,78 +9824,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B94" t="n">
-        <v>98661</v>
+        <v>87042</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R94" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9917,40 +9928,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
         <v>128814496</v>
       </c>
       <c r="B95" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128790626</v>
       </c>
       <c r="B96" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128790644</v>
       </c>
       <c r="B97" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128790612</v>
       </c>
       <c r="B98" t="n">
-        <v>107574</v>
+        <v>107584</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>128790630</v>
       </c>
       <c r="B99" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>128790570</v>
       </c>
       <c r="B100" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>128814749</v>
       </c>
       <c r="B101" t="n">
-        <v>86868</v>
+        <v>86872</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>128814809</v>
       </c>
       <c r="B102" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>128790638</v>
       </c>
       <c r="B103" t="n">
-        <v>87175</v>
+        <v>87179</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>128790568</v>
       </c>
       <c r="B104" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>128790569</v>
       </c>
       <c r="B105" t="n">
-        <v>92833</v>
+        <v>92840</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11140,48 +11140,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128790618</v>
+        <v>128790561</v>
       </c>
       <c r="B106" t="n">
-        <v>86897</v>
+        <v>90297</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723602</v>
+        <v>723960</v>
       </c>
       <c r="R106" t="n">
-        <v>6384277</v>
+        <v>6384272</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11213,7 +11210,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11223,12 +11220,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11256,45 +11248,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128790561</v>
+        <v>128790618</v>
       </c>
       <c r="B107" t="n">
-        <v>90293</v>
+        <v>86901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723960</v>
+        <v>723602</v>
       </c>
       <c r="R107" t="n">
-        <v>6384272</v>
+        <v>6384277</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11326,7 +11321,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11336,7 +11331,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Svagt rosa reaktion på bulb. Gul mycelsträng. Samlad för sekvensering.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11367,7 +11367,7 @@
         <v>128814781</v>
       </c>
       <c r="B108" t="n">
-        <v>86947</v>
+        <v>86951</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>128790622</v>
       </c>
       <c r="B109" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>128790619</v>
       </c>
       <c r="B110" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>128790631</v>
       </c>
       <c r="B111" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>128784561</v>
       </c>
       <c r="B112" t="n">
-        <v>86947</v>
+        <v>86951</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -1978,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128784509</v>
+        <v>128791663</v>
       </c>
       <c r="B15" t="n">
-        <v>86832</v>
+        <v>87042</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,34 +1989,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723618</v>
+        <v>723971</v>
       </c>
       <c r="R15" t="n">
-        <v>6384286</v>
+        <v>6384460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,22 +2059,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128791663</v>
+        <v>128784509</v>
       </c>
       <c r="B16" t="n">
-        <v>87042</v>
+        <v>86832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,30 +2082,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723971</v>
+        <v>723618</v>
       </c>
       <c r="R16" t="n">
-        <v>6384460</v>
+        <v>6384286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2156,12 +2156,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128791595</v>
+        <v>128785770</v>
       </c>
       <c r="B40" t="n">
-        <v>86786</v>
+        <v>92840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,34 +4474,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723737</v>
+        <v>723675</v>
       </c>
       <c r="R40" t="n">
-        <v>6384262</v>
+        <v>6384246</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,28 +4538,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128785770</v>
+        <v>128791595</v>
       </c>
       <c r="B41" t="n">
-        <v>92840</v>
+        <v>86786</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,30 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723675</v>
+        <v>723737</v>
       </c>
       <c r="R41" t="n">
-        <v>6384246</v>
+        <v>6384262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,19 +4636,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5075,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128791576</v>
+        <v>128791593</v>
       </c>
       <c r="B46" t="n">
-        <v>86832</v>
+        <v>86786</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723743</v>
+        <v>723736</v>
       </c>
       <c r="R46" t="n">
-        <v>6384328</v>
+        <v>6384250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5172,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128791593</v>
+        <v>128791576</v>
       </c>
       <c r="B47" t="n">
-        <v>86786</v>
+        <v>86832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723736</v>
+        <v>723743</v>
       </c>
       <c r="R47" t="n">
-        <v>6384250</v>
+        <v>6384328</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,45 +5269,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128784562</v>
+        <v>128791574</v>
       </c>
       <c r="B48" t="n">
-        <v>106995</v>
+        <v>86832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723639</v>
+        <v>723611</v>
       </c>
       <c r="R48" t="n">
-        <v>6384269</v>
+        <v>6384260</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5354,57 +5354,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128791574</v>
+        <v>128784562</v>
       </c>
       <c r="B49" t="n">
-        <v>86832</v>
+        <v>106995</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723611</v>
+        <v>723639</v>
       </c>
       <c r="R49" t="n">
-        <v>6384260</v>
+        <v>6384269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5451,12 +5451,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6160,45 +6160,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128784545</v>
+        <v>128785778</v>
       </c>
       <c r="B57" t="n">
-        <v>107584</v>
+        <v>86832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723768</v>
+        <v>723760</v>
       </c>
       <c r="R57" t="n">
-        <v>6384301</v>
+        <v>6384211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6245,44 +6245,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128784551</v>
+        <v>128784526</v>
       </c>
       <c r="B58" t="n">
-        <v>98671</v>
+        <v>86985</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219811</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723631</v>
+        <v>723962</v>
       </c>
       <c r="R58" t="n">
-        <v>6384236</v>
+        <v>6384357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6336,6 +6336,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6354,7 +6355,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784526</v>
+        <v>128784523</v>
       </c>
       <c r="B59" t="n">
         <v>86985</v>
@@ -6389,10 +6390,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723962</v>
+        <v>723878</v>
       </c>
       <c r="R59" t="n">
-        <v>6384357</v>
+        <v>6384241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6452,45 +6453,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128784523</v>
+        <v>128790565</v>
       </c>
       <c r="B60" t="n">
-        <v>86985</v>
+        <v>86810</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723878</v>
+        <v>723921</v>
       </c>
       <c r="R60" t="n">
-        <v>6384241</v>
+        <v>6384444</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,75 +6521,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128785778</v>
+        <v>128784545</v>
       </c>
       <c r="B61" t="n">
-        <v>86832</v>
+        <v>107584</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>424</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723760</v>
+        <v>723768</v>
       </c>
       <c r="R61" t="n">
-        <v>6384211</v>
+        <v>6384301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,22 +6645,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128790565</v>
+        <v>128784551</v>
       </c>
       <c r="B62" t="n">
-        <v>86810</v>
+        <v>98671</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6658,34 +6668,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>219811</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723921</v>
+        <v>723631</v>
       </c>
       <c r="R62" t="n">
-        <v>6384444</v>
+        <v>6384236</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,19 +6725,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6742,12 +6742,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -9752,49 +9752,41 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128790634</v>
+        <v>128784548</v>
       </c>
       <c r="B93" t="n">
-        <v>98671</v>
+        <v>87042</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>433</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723928</v>
+        <v>723687</v>
       </c>
       <c r="R93" t="n">
-        <v>6384313</v>
+        <v>6384221</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9824,81 +9816,78 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128784548</v>
+        <v>128790634</v>
       </c>
       <c r="B94" t="n">
-        <v>87042</v>
+        <v>98671</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723687</v>
+        <v>723928</v>
       </c>
       <c r="R94" t="n">
-        <v>6384221</v>
+        <v>6384313</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9928,29 +9917,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 40235-2025 artfynd.xlsx
+++ b/artfynd/A 40235-2025 artfynd.xlsx
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128784512</v>
+        <v>128791651</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>90998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723641</v>
+        <v>723674</v>
       </c>
       <c r="R2" t="n">
-        <v>6384196</v>
+        <v>6384225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -771,7 +775,7 @@
         <v>128790598</v>
       </c>
       <c r="B3" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,45 +880,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128791651</v>
+        <v>128784512</v>
       </c>
       <c r="B4" t="n">
-        <v>90991</v>
+        <v>92847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723674</v>
+        <v>723641</v>
       </c>
       <c r="R4" t="n">
-        <v>6384225</v>
+        <v>6384196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -976,7 +976,7 @@
         <v>128784544</v>
       </c>
       <c r="B5" t="n">
-        <v>107584</v>
+        <v>107591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,32 +1070,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128790645</v>
+        <v>128790574</v>
       </c>
       <c r="B6" t="n">
-        <v>86832</v>
+        <v>86992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723788</v>
+        <v>723609</v>
       </c>
       <c r="R6" t="n">
-        <v>6384286</v>
+        <v>6384278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1159,6 +1159,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>128784517</v>
       </c>
       <c r="B7" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1279,7 @@
         <v>128785784</v>
       </c>
       <c r="B8" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1377,7 @@
         <v>128791638</v>
       </c>
       <c r="B9" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790574</v>
+        <v>128790645</v>
       </c>
       <c r="B10" t="n">
-        <v>86985</v>
+        <v>86839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723609</v>
+        <v>723788</v>
       </c>
       <c r="R10" t="n">
-        <v>6384278</v>
+        <v>6384286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,7 +1541,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1550,7 +1551,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790554</v>
+        <v>128785783</v>
       </c>
       <c r="B11" t="n">
-        <v>86786</v>
+        <v>86992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723848</v>
+        <v>723974</v>
       </c>
       <c r="R11" t="n">
-        <v>6384240</v>
+        <v>6384345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,22 +1664,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128791599</v>
+        <v>128790554</v>
       </c>
       <c r="B12" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723734</v>
+        <v>723848</v>
       </c>
       <c r="R12" t="n">
-        <v>6384367</v>
+        <v>6384240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,74 +1744,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128785783</v>
+        <v>128791599</v>
       </c>
       <c r="B13" t="n">
-        <v>86985</v>
+        <v>86793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723974</v>
+        <v>723734</v>
       </c>
       <c r="R13" t="n">
-        <v>6384345</v>
+        <v>6384367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,64 +1863,59 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128784506</v>
+        <v>128791663</v>
       </c>
       <c r="B14" t="n">
-        <v>88720</v>
+        <v>87049</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4379</v>
+        <v>433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723922</v>
+        <v>723971</v>
       </c>
       <c r="R14" t="n">
-        <v>6384266</v>
+        <v>6384460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,22 +1962,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128791663</v>
+        <v>128784509</v>
       </c>
       <c r="B15" t="n">
-        <v>87042</v>
+        <v>86839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,30 +1985,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723971</v>
+        <v>723618</v>
       </c>
       <c r="R15" t="n">
-        <v>6384460</v>
+        <v>6384286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,44 +2059,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128784509</v>
+        <v>128784506</v>
       </c>
       <c r="B16" t="n">
-        <v>86832</v>
+        <v>88727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>424</v>
+        <v>4379</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723618</v>
+        <v>723922</v>
       </c>
       <c r="R16" t="n">
-        <v>6384286</v>
+        <v>6384266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,48 +2161,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Ulla Sebestyen, Martin Axegård, Anna Helmersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128784511</v>
+        <v>128790583</v>
       </c>
       <c r="B17" t="n">
-        <v>92840</v>
+        <v>86992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723600</v>
+        <v>723986</v>
       </c>
       <c r="R17" t="n">
-        <v>6384247</v>
+        <v>6384358</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,74 +2236,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790595</v>
+        <v>128784511</v>
       </c>
       <c r="B18" t="n">
-        <v>86985</v>
+        <v>92847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723931</v>
+        <v>723600</v>
       </c>
       <c r="R18" t="n">
-        <v>6384427</v>
+        <v>6384247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,50 +2340,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790583</v>
+        <v>128790595</v>
       </c>
       <c r="B19" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723986</v>
+        <v>723931</v>
       </c>
       <c r="R19" t="n">
-        <v>6384358</v>
+        <v>6384427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128784520</v>
+        <v>128790590</v>
       </c>
       <c r="B20" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,14 +2508,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723922</v>
+        <v>723779</v>
       </c>
       <c r="R20" t="n">
-        <v>6384266</v>
+        <v>6384209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,9 +2545,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2563,22 +2573,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128790590</v>
+        <v>128784520</v>
       </c>
       <c r="B21" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2606,14 +2616,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723779</v>
+        <v>723922</v>
       </c>
       <c r="R21" t="n">
-        <v>6384209</v>
+        <v>6384266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,19 +2653,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,22 +2671,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128784550</v>
+        <v>128791633</v>
       </c>
       <c r="B22" t="n">
-        <v>86872</v>
+        <v>86908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>442</v>
+        <v>248956</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723644</v>
+        <v>723767</v>
       </c>
       <c r="R22" t="n">
-        <v>6384278</v>
+        <v>6384282</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,57 +2768,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128784553</v>
+        <v>128791624</v>
       </c>
       <c r="B23" t="n">
-        <v>98671</v>
+        <v>86908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219811</v>
+        <v>248956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrskog O Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723659</v>
+        <v>723724</v>
       </c>
       <c r="R23" t="n">
-        <v>6384257</v>
+        <v>6384209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,22 +2865,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791624</v>
+        <v>128791629</v>
       </c>
       <c r="B24" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723724</v>
+        <v>723745</v>
       </c>
       <c r="R24" t="n">
-        <v>6384209</v>
+        <v>6384273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,45 +2974,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128790581</v>
+        <v>128784550</v>
       </c>
       <c r="B25" t="n">
-        <v>86985</v>
+        <v>86879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723930</v>
+        <v>723644</v>
       </c>
       <c r="R25" t="n">
-        <v>6384314</v>
+        <v>6384278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,72 +3042,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128791633</v>
+        <v>128790581</v>
       </c>
       <c r="B26" t="n">
-        <v>86901</v>
+        <v>86992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3117,10 +3106,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723767</v>
+        <v>723930</v>
       </c>
       <c r="R26" t="n">
-        <v>6384282</v>
+        <v>6384314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,74 +3139,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790594</v>
+        <v>128784553</v>
       </c>
       <c r="B27" t="n">
-        <v>86985</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>219811</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Barrskog O Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723948</v>
+        <v>723659</v>
       </c>
       <c r="R27" t="n">
-        <v>6384417</v>
+        <v>6384257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,72 +3247,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128791629</v>
+        <v>128790594</v>
       </c>
       <c r="B28" t="n">
-        <v>86901</v>
+        <v>86992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723745</v>
+        <v>723948</v>
       </c>
       <c r="R28" t="n">
-        <v>6384273</v>
+        <v>6384417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,29 +3344,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>128790627</v>
       </c>
       <c r="B29" t="n">
-        <v>87042</v>
+        <v>87049</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128785781</v>
+        <v>128785780</v>
       </c>
       <c r="B30" t="n">
-        <v>86786</v>
+        <v>92847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,23 +3498,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>6047725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3522,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723744</v>
+        <v>723935</v>
       </c>
       <c r="R30" t="n">
-        <v>6384205</v>
+        <v>6384247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,6 +3562,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3584,10 +3581,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128791591</v>
+        <v>128785781</v>
       </c>
       <c r="B31" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3615,14 +3612,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gothem Vaters, Gtl</t>
+          <t>Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723617</v>
+        <v>723744</v>
       </c>
       <c r="R31" t="n">
-        <v>6384247</v>
+        <v>6384205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,22 +3666,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128785780</v>
+        <v>128791591</v>
       </c>
       <c r="B32" t="n">
-        <v>92840</v>
+        <v>86793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,27 +3689,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6047725</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vaters, Gtl</t>
+          <t>Gothem Vaters, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723935</v>
+        <v>723617</v>
       </c>
       <c r="R32" t="n">
         <v>6384247</v>
@@ -3756,19 +3757,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3778,7 +3778,7 @@
         <v>128791642</v>
       </c>
       <c r="B33" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,45 +3872,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128784530</v>
+        <v>128791566</v>
       </c>
       <c r="B34" t="n">